--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0F6358-23C6-4158-A4CB-9141493F4C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8276C35D-3E2B-463A-8523-8A7256BFE470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,144 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_18.08.2025</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 18.08.2025</t>
+  </si>
+  <si>
+    <t>133799756</t>
+  </si>
+  <si>
+    <t>133808799</t>
+  </si>
+  <si>
+    <t>133840379</t>
+  </si>
+  <si>
+    <t>133841390</t>
+  </si>
+  <si>
+    <t>133838033</t>
+  </si>
+  <si>
+    <t>133849204</t>
+  </si>
+  <si>
+    <t>133853259</t>
+  </si>
+  <si>
+    <t>133848887</t>
+  </si>
+  <si>
+    <t>133839162</t>
+  </si>
+  <si>
+    <t>133841502</t>
+  </si>
+  <si>
+    <t>133849413</t>
+  </si>
+  <si>
+    <t>133817540</t>
+  </si>
+  <si>
+    <t>133146459</t>
+  </si>
+  <si>
+    <t>132362706</t>
+  </si>
+  <si>
+    <t>133901194</t>
+  </si>
+  <si>
+    <t>133889372</t>
+  </si>
+  <si>
+    <t>133899095</t>
+  </si>
+  <si>
+    <t>133898376</t>
+  </si>
+  <si>
+    <t>133921995</t>
+  </si>
+  <si>
+    <t>133911461</t>
+  </si>
+  <si>
+    <t>133934396</t>
+  </si>
+  <si>
+    <t>133954816</t>
+  </si>
+  <si>
+    <t>133929292</t>
+  </si>
+  <si>
+    <t>133598759</t>
+  </si>
+  <si>
+    <t>133847880</t>
+  </si>
+  <si>
+    <t>132510451</t>
+  </si>
+  <si>
+    <t>133837540</t>
+  </si>
+  <si>
+    <t>132114230</t>
+  </si>
+  <si>
+    <t>133898165</t>
+  </si>
+  <si>
+    <t>131852795</t>
+  </si>
+  <si>
+    <t>133835986</t>
+  </si>
+  <si>
+    <t>133837527</t>
+  </si>
+  <si>
+    <t>133839188</t>
+  </si>
+  <si>
+    <t>133843657</t>
+  </si>
+  <si>
+    <t>133845271</t>
+  </si>
+  <si>
+    <t>133846194</t>
+  </si>
+  <si>
+    <t>133987285</t>
+  </si>
+  <si>
+    <t>133849538</t>
+  </si>
+  <si>
+    <t>133851065</t>
+  </si>
+  <si>
+    <t>133807037</t>
+  </si>
+  <si>
+    <t>133808472</t>
+  </si>
+  <si>
+    <t>133844530</t>
+  </si>
+  <si>
+    <t>133908947</t>
   </si>
 </sst>
 </file>
@@ -484,139 +622,795 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>133762395</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8276C35D-3E2B-463A-8523-8A7256BFE470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58027216-CE40-4E8B-B269-F6708D11881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,142 +51,145 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_18.08.2025</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 18.08.2025</t>
-  </si>
-  <si>
-    <t>133799756</t>
-  </si>
-  <si>
-    <t>133808799</t>
-  </si>
-  <si>
-    <t>133840379</t>
-  </si>
-  <si>
-    <t>133841390</t>
-  </si>
-  <si>
-    <t>133838033</t>
-  </si>
-  <si>
-    <t>133849204</t>
-  </si>
-  <si>
-    <t>133853259</t>
-  </si>
-  <si>
-    <t>133848887</t>
-  </si>
-  <si>
-    <t>133839162</t>
-  </si>
-  <si>
-    <t>133841502</t>
-  </si>
-  <si>
-    <t>133849413</t>
-  </si>
-  <si>
-    <t>133817540</t>
-  </si>
-  <si>
-    <t>133146459</t>
-  </si>
-  <si>
-    <t>132362706</t>
-  </si>
-  <si>
-    <t>133901194</t>
-  </si>
-  <si>
-    <t>133889372</t>
-  </si>
-  <si>
-    <t>133899095</t>
-  </si>
-  <si>
-    <t>133898376</t>
-  </si>
-  <si>
-    <t>133921995</t>
-  </si>
-  <si>
-    <t>133911461</t>
-  </si>
-  <si>
-    <t>133934396</t>
-  </si>
-  <si>
-    <t>133954816</t>
-  </si>
-  <si>
-    <t>133929292</t>
-  </si>
-  <si>
-    <t>133598759</t>
-  </si>
-  <si>
-    <t>133847880</t>
-  </si>
-  <si>
-    <t>132510451</t>
-  </si>
-  <si>
-    <t>133837540</t>
-  </si>
-  <si>
-    <t>132114230</t>
-  </si>
-  <si>
-    <t>133898165</t>
-  </si>
-  <si>
-    <t>131852795</t>
-  </si>
-  <si>
-    <t>133835986</t>
-  </si>
-  <si>
-    <t>133837527</t>
-  </si>
-  <si>
-    <t>133839188</t>
-  </si>
-  <si>
-    <t>133843657</t>
-  </si>
-  <si>
-    <t>133845271</t>
-  </si>
-  <si>
-    <t>133846194</t>
-  </si>
-  <si>
-    <t>133987285</t>
-  </si>
-  <si>
-    <t>133849538</t>
-  </si>
-  <si>
-    <t>133851065</t>
-  </si>
-  <si>
-    <t>133807037</t>
-  </si>
-  <si>
-    <t>133808472</t>
-  </si>
-  <si>
-    <t>133844530</t>
-  </si>
-  <si>
-    <t>133908947</t>
+    <t>Relatório Recusa _ SICREDI_19.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 19.08.2025</t>
+  </si>
+  <si>
+    <t>133787152</t>
+  </si>
+  <si>
+    <t>133795795</t>
+  </si>
+  <si>
+    <t>133814494</t>
+  </si>
+  <si>
+    <t>133872990</t>
+  </si>
+  <si>
+    <t>133868677</t>
+  </si>
+  <si>
+    <t>133870627</t>
+  </si>
+  <si>
+    <t>133861099</t>
+  </si>
+  <si>
+    <t>133874132</t>
+  </si>
+  <si>
+    <t>133901013</t>
+  </si>
+  <si>
+    <t>133888944</t>
+  </si>
+  <si>
+    <t>132176874</t>
+  </si>
+  <si>
+    <t>133907661</t>
+  </si>
+  <si>
+    <t>133912375</t>
+  </si>
+  <si>
+    <t>133922370</t>
+  </si>
+  <si>
+    <t>133911174</t>
+  </si>
+  <si>
+    <t>133920137</t>
+  </si>
+  <si>
+    <t>133936034</t>
+  </si>
+  <si>
+    <t>133949818</t>
+  </si>
+  <si>
+    <t>133962723</t>
+  </si>
+  <si>
+    <t>133956189</t>
+  </si>
+  <si>
+    <t>133956700</t>
+  </si>
+  <si>
+    <t>133878610</t>
+  </si>
+  <si>
+    <t>133986164</t>
+  </si>
+  <si>
+    <t>133989792</t>
+  </si>
+  <si>
+    <t>133980860</t>
+  </si>
+  <si>
+    <t>133774055</t>
+  </si>
+  <si>
+    <t>133870852</t>
+  </si>
+  <si>
+    <t>133996653</t>
+  </si>
+  <si>
+    <t>133041270</t>
+  </si>
+  <si>
+    <t>133827217</t>
+  </si>
+  <si>
+    <t>133866716</t>
+  </si>
+  <si>
+    <t>133868309</t>
+  </si>
+  <si>
+    <t>133299323</t>
+  </si>
+  <si>
+    <t>133875272</t>
+  </si>
+  <si>
+    <t>133876269</t>
+  </si>
+  <si>
+    <t>133876571</t>
+  </si>
+  <si>
+    <t>133885812</t>
+  </si>
+  <si>
+    <t>133897632</t>
+  </si>
+  <si>
+    <t>133919905</t>
+  </si>
+  <si>
+    <t>130328007</t>
+  </si>
+  <si>
+    <t>133896942</t>
+  </si>
+  <si>
+    <t>133921247</t>
+  </si>
+  <si>
+    <t>133932158</t>
+  </si>
+  <si>
+    <t>134011891</t>
   </si>
 </sst>
 </file>
@@ -591,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -623,16 +626,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133762395</v>
+        <v>131905435</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -644,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -662,13 +665,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -680,13 +683,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -698,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -716,13 +719,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -734,13 +737,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -752,13 +755,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -770,13 +773,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -788,13 +791,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -806,13 +809,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -824,13 +827,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -842,13 +845,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -860,13 +863,13 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -878,13 +881,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -896,13 +899,13 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -914,13 +917,13 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -932,13 +935,13 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -950,13 +953,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -968,13 +971,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -986,13 +989,13 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1004,13 +1007,13 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1022,13 +1025,13 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1040,13 +1043,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1058,13 +1061,13 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1076,13 +1079,13 @@
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1094,13 +1097,13 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1112,13 +1115,13 @@
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1130,13 +1133,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1148,13 +1151,13 @@
         <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1166,13 +1169,13 @@
         <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1184,13 +1187,13 @@
         <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1202,13 +1205,13 @@
         <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1220,13 +1223,13 @@
         <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1238,13 +1241,13 @@
         <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1256,13 +1259,13 @@
         <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1274,13 +1277,13 @@
         <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1292,13 +1295,13 @@
         <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1310,13 +1313,13 @@
         <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1328,13 +1331,13 @@
         <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1346,13 +1349,13 @@
         <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1364,13 +1367,13 @@
         <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1382,13 +1385,13 @@
         <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1400,18 +1403,35 @@
         <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58027216-CE40-4E8B-B269-F6708D11881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57AE5A-E0C3-4560-B038-6432B9260C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,142 +54,124 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_19.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 19.08.2025</t>
-  </si>
-  <si>
-    <t>133787152</t>
-  </si>
-  <si>
-    <t>133795795</t>
-  </si>
-  <si>
-    <t>133814494</t>
-  </si>
-  <si>
-    <t>133872990</t>
-  </si>
-  <si>
-    <t>133868677</t>
-  </si>
-  <si>
-    <t>133870627</t>
-  </si>
-  <si>
-    <t>133861099</t>
-  </si>
-  <si>
-    <t>133874132</t>
-  </si>
-  <si>
-    <t>133901013</t>
-  </si>
-  <si>
-    <t>133888944</t>
-  </si>
-  <si>
-    <t>132176874</t>
-  </si>
-  <si>
-    <t>133907661</t>
-  </si>
-  <si>
-    <t>133912375</t>
-  </si>
-  <si>
-    <t>133922370</t>
-  </si>
-  <si>
-    <t>133911174</t>
-  </si>
-  <si>
-    <t>133920137</t>
-  </si>
-  <si>
-    <t>133936034</t>
-  </si>
-  <si>
-    <t>133949818</t>
-  </si>
-  <si>
-    <t>133962723</t>
-  </si>
-  <si>
-    <t>133956189</t>
-  </si>
-  <si>
-    <t>133956700</t>
-  </si>
-  <si>
-    <t>133878610</t>
-  </si>
-  <si>
-    <t>133986164</t>
-  </si>
-  <si>
-    <t>133989792</t>
-  </si>
-  <si>
-    <t>133980860</t>
-  </si>
-  <si>
-    <t>133774055</t>
-  </si>
-  <si>
-    <t>133870852</t>
-  </si>
-  <si>
-    <t>133996653</t>
-  </si>
-  <si>
-    <t>133041270</t>
-  </si>
-  <si>
-    <t>133827217</t>
-  </si>
-  <si>
-    <t>133866716</t>
-  </si>
-  <si>
-    <t>133868309</t>
-  </si>
-  <si>
-    <t>133299323</t>
-  </si>
-  <si>
-    <t>133875272</t>
-  </si>
-  <si>
-    <t>133876269</t>
-  </si>
-  <si>
-    <t>133876571</t>
-  </si>
-  <si>
-    <t>133885812</t>
-  </si>
-  <si>
-    <t>133897632</t>
-  </si>
-  <si>
-    <t>133919905</t>
-  </si>
-  <si>
-    <t>130328007</t>
-  </si>
-  <si>
-    <t>133896942</t>
-  </si>
-  <si>
-    <t>133921247</t>
-  </si>
-  <si>
-    <t>133932158</t>
-  </si>
-  <si>
-    <t>134011891</t>
+    <t>Relatório Recusa _ SICREDI_20.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 20.08.2025</t>
+  </si>
+  <si>
+    <t>130183532</t>
+  </si>
+  <si>
+    <t>133777612</t>
+  </si>
+  <si>
+    <t>133802339</t>
+  </si>
+  <si>
+    <t>133854973</t>
+  </si>
+  <si>
+    <t>133899182</t>
+  </si>
+  <si>
+    <t>133899184</t>
+  </si>
+  <si>
+    <t>133917301</t>
+  </si>
+  <si>
+    <t>133881777</t>
+  </si>
+  <si>
+    <t>133890569</t>
+  </si>
+  <si>
+    <t>133926393</t>
+  </si>
+  <si>
+    <t>133928086</t>
+  </si>
+  <si>
+    <t>133944870</t>
+  </si>
+  <si>
+    <t>133927498</t>
+  </si>
+  <si>
+    <t>133939983</t>
+  </si>
+  <si>
+    <t>133965630</t>
+  </si>
+  <si>
+    <t>133996665</t>
+  </si>
+  <si>
+    <t>133999991</t>
+  </si>
+  <si>
+    <t>134005397</t>
+  </si>
+  <si>
+    <t>134012426</t>
+  </si>
+  <si>
+    <t>133876322</t>
+  </si>
+  <si>
+    <t>134010660</t>
+  </si>
+  <si>
+    <t>133994933</t>
+  </si>
+  <si>
+    <t>133795822</t>
+  </si>
+  <si>
+    <t>133803234</t>
+  </si>
+  <si>
+    <t>133805828</t>
+  </si>
+  <si>
+    <t>134018821</t>
+  </si>
+  <si>
+    <t>133830491</t>
+  </si>
+  <si>
+    <t>133998012</t>
+  </si>
+  <si>
+    <t>133945317</t>
+  </si>
+  <si>
+    <t>130337253</t>
+  </si>
+  <si>
+    <t>129924947</t>
+  </si>
+  <si>
+    <t>133927886</t>
+  </si>
+  <si>
+    <t>130893193</t>
+  </si>
+  <si>
+    <t>133888607</t>
+  </si>
+  <si>
+    <t>133891621</t>
+  </si>
+  <si>
+    <t>133892056</t>
+  </si>
+  <si>
+    <t>133898723</t>
+  </si>
+  <si>
+    <t>133830704</t>
   </si>
 </sst>
 </file>
@@ -594,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -626,7 +608,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>131905435</v>
+        <v>130186761</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1327,111 +1309,19 @@
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F45"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57AE5A-E0C3-4560-B038-6432B9260C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FE8805-B849-4FC3-928F-9693A4CC3F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,124 +54,133 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_20.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 20.08.2025</t>
-  </si>
-  <si>
-    <t>130183532</t>
-  </si>
-  <si>
-    <t>133777612</t>
-  </si>
-  <si>
-    <t>133802339</t>
-  </si>
-  <si>
-    <t>133854973</t>
-  </si>
-  <si>
-    <t>133899182</t>
-  </si>
-  <si>
-    <t>133899184</t>
-  </si>
-  <si>
-    <t>133917301</t>
-  </si>
-  <si>
-    <t>133881777</t>
-  </si>
-  <si>
-    <t>133890569</t>
-  </si>
-  <si>
-    <t>133926393</t>
-  </si>
-  <si>
-    <t>133928086</t>
-  </si>
-  <si>
-    <t>133944870</t>
-  </si>
-  <si>
-    <t>133927498</t>
-  </si>
-  <si>
-    <t>133939983</t>
-  </si>
-  <si>
-    <t>133965630</t>
-  </si>
-  <si>
-    <t>133996665</t>
-  </si>
-  <si>
-    <t>133999991</t>
-  </si>
-  <si>
-    <t>134005397</t>
-  </si>
-  <si>
-    <t>134012426</t>
-  </si>
-  <si>
-    <t>133876322</t>
-  </si>
-  <si>
-    <t>134010660</t>
-  </si>
-  <si>
-    <t>133994933</t>
-  </si>
-  <si>
-    <t>133795822</t>
-  </si>
-  <si>
-    <t>133803234</t>
-  </si>
-  <si>
-    <t>133805828</t>
-  </si>
-  <si>
-    <t>134018821</t>
-  </si>
-  <si>
-    <t>133830491</t>
-  </si>
-  <si>
-    <t>133998012</t>
-  </si>
-  <si>
-    <t>133945317</t>
-  </si>
-  <si>
-    <t>130337253</t>
-  </si>
-  <si>
-    <t>129924947</t>
-  </si>
-  <si>
-    <t>133927886</t>
-  </si>
-  <si>
-    <t>130893193</t>
-  </si>
-  <si>
-    <t>133888607</t>
-  </si>
-  <si>
-    <t>133891621</t>
-  </si>
-  <si>
-    <t>133892056</t>
-  </si>
-  <si>
-    <t>133898723</t>
-  </si>
-  <si>
-    <t>133830704</t>
+    <t>Relatório Recusa _ SICREDI_21.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 21.08.2025</t>
+  </si>
+  <si>
+    <t>133905743</t>
+  </si>
+  <si>
+    <t>133921555</t>
+  </si>
+  <si>
+    <t>133918968</t>
+  </si>
+  <si>
+    <t>133904506</t>
+  </si>
+  <si>
+    <t>133912129</t>
+  </si>
+  <si>
+    <t>133935234</t>
+  </si>
+  <si>
+    <t>133938682</t>
+  </si>
+  <si>
+    <t>133964355</t>
+  </si>
+  <si>
+    <t>133957456</t>
+  </si>
+  <si>
+    <t>133950184</t>
+  </si>
+  <si>
+    <t>133966379</t>
+  </si>
+  <si>
+    <t>133922730</t>
+  </si>
+  <si>
+    <t>133965675</t>
+  </si>
+  <si>
+    <t>134006862</t>
+  </si>
+  <si>
+    <t>134030018</t>
+  </si>
+  <si>
+    <t>129492762</t>
+  </si>
+  <si>
+    <t>134035520</t>
+  </si>
+  <si>
+    <t>134019469</t>
+  </si>
+  <si>
+    <t>134020384</t>
+  </si>
+  <si>
+    <t>134038128</t>
+  </si>
+  <si>
+    <t>133805336</t>
+  </si>
+  <si>
+    <t>133854664</t>
+  </si>
+  <si>
+    <t>133390639</t>
+  </si>
+  <si>
+    <t>133919878</t>
+  </si>
+  <si>
+    <t>133867340</t>
+  </si>
+  <si>
+    <t>133920143</t>
+  </si>
+  <si>
+    <t>133841723</t>
+  </si>
+  <si>
+    <t>134047114</t>
+  </si>
+  <si>
+    <t>131844306</t>
+  </si>
+  <si>
+    <t>133951283</t>
+  </si>
+  <si>
+    <t>131283053</t>
+  </si>
+  <si>
+    <t>133946113</t>
+  </si>
+  <si>
+    <t>129329162</t>
+  </si>
+  <si>
+    <t>133910841</t>
+  </si>
+  <si>
+    <t>133912158</t>
+  </si>
+  <si>
+    <t>133912977</t>
+  </si>
+  <si>
+    <t>133916220</t>
+  </si>
+  <si>
+    <t>133920780</t>
+  </si>
+  <si>
+    <t>134056220</t>
+  </si>
+  <si>
+    <t>133922918</t>
+  </si>
+  <si>
+    <t>133967484</t>
   </si>
 </sst>
 </file>
@@ -608,7 +617,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130186761</v>
+        <v>133921236</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1309,12 +1318,57 @@
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FE8805-B849-4FC3-928F-9693A4CC3F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE5336-DBB1-49EB-9679-BF151FB8F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="106">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,298 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_21.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 21.08.2025</t>
-  </si>
-  <si>
-    <t>133905743</t>
-  </si>
-  <si>
-    <t>133921555</t>
-  </si>
-  <si>
-    <t>133918968</t>
-  </si>
-  <si>
-    <t>133904506</t>
-  </si>
-  <si>
-    <t>133912129</t>
-  </si>
-  <si>
-    <t>133935234</t>
-  </si>
-  <si>
-    <t>133938682</t>
-  </si>
-  <si>
-    <t>133964355</t>
-  </si>
-  <si>
-    <t>133957456</t>
-  </si>
-  <si>
-    <t>133950184</t>
-  </si>
-  <si>
-    <t>133966379</t>
-  </si>
-  <si>
-    <t>133922730</t>
-  </si>
-  <si>
-    <t>133965675</t>
-  </si>
-  <si>
-    <t>134006862</t>
-  </si>
-  <si>
-    <t>134030018</t>
-  </si>
-  <si>
-    <t>129492762</t>
-  </si>
-  <si>
-    <t>134035520</t>
-  </si>
-  <si>
-    <t>134019469</t>
-  </si>
-  <si>
-    <t>134020384</t>
-  </si>
-  <si>
-    <t>134038128</t>
-  </si>
-  <si>
-    <t>133805336</t>
-  </si>
-  <si>
-    <t>133854664</t>
-  </si>
-  <si>
-    <t>133390639</t>
-  </si>
-  <si>
-    <t>133919878</t>
-  </si>
-  <si>
-    <t>133867340</t>
-  </si>
-  <si>
-    <t>133920143</t>
-  </si>
-  <si>
-    <t>133841723</t>
-  </si>
-  <si>
-    <t>134047114</t>
-  </si>
-  <si>
-    <t>131844306</t>
-  </si>
-  <si>
-    <t>133951283</t>
-  </si>
-  <si>
-    <t>131283053</t>
-  </si>
-  <si>
-    <t>133946113</t>
-  </si>
-  <si>
-    <t>129329162</t>
-  </si>
-  <si>
-    <t>133910841</t>
-  </si>
-  <si>
-    <t>133912158</t>
-  </si>
-  <si>
-    <t>133912977</t>
-  </si>
-  <si>
-    <t>133916220</t>
-  </si>
-  <si>
-    <t>133920780</t>
-  </si>
-  <si>
-    <t>134056220</t>
-  </si>
-  <si>
-    <t>133922918</t>
-  </si>
-  <si>
-    <t>133967484</t>
+    <t>Relatório de Recusa Sicredi 22.08.2025</t>
+  </si>
+  <si>
+    <t>133838744</t>
+  </si>
+  <si>
+    <t>133929250</t>
+  </si>
+  <si>
+    <t>133945254</t>
+  </si>
+  <si>
+    <t>133949843</t>
+  </si>
+  <si>
+    <t>133843847</t>
+  </si>
+  <si>
+    <t>133912536</t>
+  </si>
+  <si>
+    <t>133960681</t>
+  </si>
+  <si>
+    <t>133949815</t>
+  </si>
+  <si>
+    <t>133961235</t>
+  </si>
+  <si>
+    <t>133966969</t>
+  </si>
+  <si>
+    <t>134003249</t>
+  </si>
+  <si>
+    <t>134037204</t>
+  </si>
+  <si>
+    <t>134035288</t>
+  </si>
+  <si>
+    <t>134043494</t>
+  </si>
+  <si>
+    <t>134050624</t>
+  </si>
+  <si>
+    <t>134059180</t>
+  </si>
+  <si>
+    <t>133844933</t>
+  </si>
+  <si>
+    <t>133851904</t>
+  </si>
+  <si>
+    <t>133852028</t>
+  </si>
+  <si>
+    <t>133147354</t>
+  </si>
+  <si>
+    <t>133967004</t>
+  </si>
+  <si>
+    <t>133898032</t>
+  </si>
+  <si>
+    <t>134073152</t>
+  </si>
+  <si>
+    <t>133847152</t>
+  </si>
+  <si>
+    <t>131001194</t>
+  </si>
+  <si>
+    <t>134075721</t>
+  </si>
+  <si>
+    <t>134076969</t>
+  </si>
+  <si>
+    <t>134076187</t>
+  </si>
+  <si>
+    <t>133977219</t>
+  </si>
+  <si>
+    <t>131999260</t>
+  </si>
+  <si>
+    <t>130126461</t>
+  </si>
+  <si>
+    <t>132932631</t>
+  </si>
+  <si>
+    <t>134080130</t>
+  </si>
+  <si>
+    <t>134080518</t>
+  </si>
+  <si>
+    <t>134081369</t>
+  </si>
+  <si>
+    <t>134082550</t>
+  </si>
+  <si>
+    <t>133138526</t>
+  </si>
+  <si>
+    <t>134006549</t>
+  </si>
+  <si>
+    <t>134070111</t>
+  </si>
+  <si>
+    <t>133940900</t>
+  </si>
+  <si>
+    <t>133929112</t>
+  </si>
+  <si>
+    <t>133932814</t>
+  </si>
+  <si>
+    <t>133939136</t>
+  </si>
+  <si>
+    <t>133979354</t>
+  </si>
+  <si>
+    <t>133943156</t>
+  </si>
+  <si>
+    <t>133944603</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2026</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2027</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2028</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2029</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2030</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2031</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2032</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2033</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2034</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2035</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2036</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2037</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2038</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2039</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2040</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2041</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2042</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2043</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2044</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2045</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2046</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2047</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2048</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2049</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2050</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2051</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2052</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2053</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2054</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2055</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2056</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2057</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2058</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2059</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2060</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2061</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2062</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2063</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2064</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.08.2065</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_23.08.2025</t>
+  </si>
+  <si>
+    <t>133866982</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 23.08.2025</t>
+  </si>
+  <si>
+    <t>134074081</t>
+  </si>
+  <si>
+    <t>133870592</t>
+  </si>
+  <si>
+    <t>133846139</t>
+  </si>
+  <si>
+    <t>133889832</t>
+  </si>
+  <si>
+    <t>133958126</t>
+  </si>
+  <si>
+    <t>129411974</t>
+  </si>
+  <si>
+    <t>132540767</t>
   </si>
 </sst>
 </file>
@@ -585,7 +750,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,16 +782,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133921236</v>
+        <v>132977103</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -635,16 +800,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -653,16 +818,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +836,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -689,16 +854,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -707,16 +872,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -725,16 +890,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -743,16 +908,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -761,16 +926,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -779,16 +944,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -797,16 +962,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -815,16 +980,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -833,16 +998,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -851,16 +1016,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -869,16 +1034,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -887,16 +1052,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -905,16 +1070,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -923,16 +1088,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -941,16 +1106,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -959,16 +1124,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -977,16 +1142,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -995,16 +1160,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1178,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1031,16 +1196,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1214,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1232,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1085,16 +1250,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1103,16 +1268,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1121,16 +1286,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1139,16 +1304,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1157,16 +1322,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1175,16 +1340,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1193,16 +1358,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1211,16 +1376,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1229,16 +1394,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1247,16 +1412,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1265,16 +1430,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1283,16 +1448,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1301,16 +1466,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1319,16 +1484,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1337,16 +1502,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1355,27 +1520,244 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE5336-DBB1-49EB-9679-BF151FB8F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B72FE5E-0174-41FA-9BD9-925CFE8113B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="118">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,298 +54,334 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 22.08.2025</t>
-  </si>
-  <si>
-    <t>133838744</t>
-  </si>
-  <si>
-    <t>133929250</t>
-  </si>
-  <si>
-    <t>133945254</t>
-  </si>
-  <si>
-    <t>133949843</t>
-  </si>
-  <si>
-    <t>133843847</t>
-  </si>
-  <si>
-    <t>133912536</t>
-  </si>
-  <si>
-    <t>133960681</t>
-  </si>
-  <si>
-    <t>133949815</t>
-  </si>
-  <si>
-    <t>133961235</t>
-  </si>
-  <si>
-    <t>133966969</t>
-  </si>
-  <si>
-    <t>134003249</t>
-  </si>
-  <si>
-    <t>134037204</t>
-  </si>
-  <si>
-    <t>134035288</t>
-  </si>
-  <si>
-    <t>134043494</t>
-  </si>
-  <si>
-    <t>134050624</t>
-  </si>
-  <si>
-    <t>134059180</t>
-  </si>
-  <si>
-    <t>133844933</t>
-  </si>
-  <si>
-    <t>133851904</t>
-  </si>
-  <si>
-    <t>133852028</t>
-  </si>
-  <si>
-    <t>133147354</t>
-  </si>
-  <si>
-    <t>133967004</t>
-  </si>
-  <si>
-    <t>133898032</t>
-  </si>
-  <si>
-    <t>134073152</t>
-  </si>
-  <si>
-    <t>133847152</t>
-  </si>
-  <si>
-    <t>131001194</t>
-  </si>
-  <si>
-    <t>134075721</t>
-  </si>
-  <si>
-    <t>134076969</t>
-  </si>
-  <si>
-    <t>134076187</t>
-  </si>
-  <si>
-    <t>133977219</t>
-  </si>
-  <si>
-    <t>131999260</t>
-  </si>
-  <si>
-    <t>130126461</t>
-  </si>
-  <si>
-    <t>132932631</t>
-  </si>
-  <si>
-    <t>134080130</t>
-  </si>
-  <si>
-    <t>134080518</t>
-  </si>
-  <si>
-    <t>134081369</t>
-  </si>
-  <si>
-    <t>134082550</t>
-  </si>
-  <si>
-    <t>133138526</t>
-  </si>
-  <si>
-    <t>134006549</t>
-  </si>
-  <si>
-    <t>134070111</t>
-  </si>
-  <si>
-    <t>133940900</t>
-  </si>
-  <si>
-    <t>133929112</t>
-  </si>
-  <si>
-    <t>133932814</t>
-  </si>
-  <si>
-    <t>133939136</t>
-  </si>
-  <si>
-    <t>133979354</t>
-  </si>
-  <si>
-    <t>133943156</t>
-  </si>
-  <si>
-    <t>133944603</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2026</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2027</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2028</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2029</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2030</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2031</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2032</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2033</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2034</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2035</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2036</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2037</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2038</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2039</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2040</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2041</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2042</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2043</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2044</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2045</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2046</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2047</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2048</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2049</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2050</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2051</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2052</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2053</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2054</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2055</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2056</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2057</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2058</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2059</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2060</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2061</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2062</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2063</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2064</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.08.2065</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_23.08.2025</t>
-  </si>
-  <si>
-    <t>133866982</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 23.08.2025</t>
-  </si>
-  <si>
-    <t>134074081</t>
-  </si>
-  <si>
-    <t>133870592</t>
-  </si>
-  <si>
-    <t>133846139</t>
-  </si>
-  <si>
-    <t>133889832</t>
-  </si>
-  <si>
-    <t>133958126</t>
-  </si>
-  <si>
-    <t>129411974</t>
-  </si>
-  <si>
-    <t>132540767</t>
+    <t>Relatório Recusa _ SICREDI_25.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2026</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2027</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2028</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2029</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2030</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2031</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2032</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2033</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2034</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2035</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2036</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2037</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2038</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2039</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2040</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2041</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2042</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2043</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2044</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2045</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2046</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2047</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2048</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2049</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2050</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2051</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2052</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2053</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2054</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2055</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2056</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2057</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2058</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2059</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2060</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2061</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2062</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2063</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2064</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2065</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2066</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2067</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2068</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2069</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2070</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2071</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2072</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2073</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2074</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2075</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 25.08.2025</t>
+  </si>
+  <si>
+    <t>133889264</t>
+  </si>
+  <si>
+    <t>130576763</t>
+  </si>
+  <si>
+    <t>133910459</t>
+  </si>
+  <si>
+    <t>133394297</t>
+  </si>
+  <si>
+    <t>133955421</t>
+  </si>
+  <si>
+    <t>133957093</t>
+  </si>
+  <si>
+    <t>133955031</t>
+  </si>
+  <si>
+    <t>133965118</t>
+  </si>
+  <si>
+    <t>133963814</t>
+  </si>
+  <si>
+    <t>133955570</t>
+  </si>
+  <si>
+    <t>133985710</t>
+  </si>
+  <si>
+    <t>134013995</t>
+  </si>
+  <si>
+    <t>134012764</t>
+  </si>
+  <si>
+    <t>134005752</t>
+  </si>
+  <si>
+    <t>133998817</t>
+  </si>
+  <si>
+    <t>133995262</t>
+  </si>
+  <si>
+    <t>134003105</t>
+  </si>
+  <si>
+    <t>134013430</t>
+  </si>
+  <si>
+    <t>133998572</t>
+  </si>
+  <si>
+    <t>134024228</t>
+  </si>
+  <si>
+    <t>134031432</t>
+  </si>
+  <si>
+    <t>134037875</t>
+  </si>
+  <si>
+    <t>134045114</t>
+  </si>
+  <si>
+    <t>134049116</t>
+  </si>
+  <si>
+    <t>133981311</t>
+  </si>
+  <si>
+    <t>134053774</t>
+  </si>
+  <si>
+    <t>134029540</t>
+  </si>
+  <si>
+    <t>134079955</t>
+  </si>
+  <si>
+    <t>134083871</t>
+  </si>
+  <si>
+    <t>134082660</t>
+  </si>
+  <si>
+    <t>133883156</t>
+  </si>
+  <si>
+    <t>133885953</t>
+  </si>
+  <si>
+    <t>133966506</t>
+  </si>
+  <si>
+    <t>131345100</t>
+  </si>
+  <si>
+    <t>133966257</t>
+  </si>
+  <si>
+    <t>134092724</t>
+  </si>
+  <si>
+    <t>133075468</t>
+  </si>
+  <si>
+    <t>133981988</t>
+  </si>
+  <si>
+    <t>133988818</t>
+  </si>
+  <si>
+    <t>133920587</t>
+  </si>
+  <si>
+    <t>133982757</t>
+  </si>
+  <si>
+    <t>133095443</t>
+  </si>
+  <si>
+    <t>134092378</t>
+  </si>
+  <si>
+    <t>133932676</t>
+  </si>
+  <si>
+    <t>133951237</t>
+  </si>
+  <si>
+    <t>133941587</t>
+  </si>
+  <si>
+    <t>134026119</t>
+  </si>
+  <si>
+    <t>133960435</t>
+  </si>
+  <si>
+    <t>133964246</t>
+  </si>
+  <si>
+    <t>133964670</t>
+  </si>
+  <si>
+    <t>133966664</t>
+  </si>
+  <si>
+    <t>133966875</t>
+  </si>
+  <si>
+    <t>134000930</t>
+  </si>
+  <si>
+    <t>133983250</t>
+  </si>
+  <si>
+    <t>133874361</t>
+  </si>
+  <si>
+    <t>133934879</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2076</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.08.2077</t>
   </si>
 </sst>
 </file>
@@ -750,7 +786,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -782,16 +818,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>132977103</v>
+        <v>130664580</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -800,16 +836,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -818,16 +854,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -836,16 +872,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -854,16 +890,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -872,16 +908,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -890,16 +926,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -908,16 +944,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -926,16 +962,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -944,16 +980,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -962,16 +998,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -980,16 +1016,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -998,16 +1034,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1052,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1070,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1088,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1106,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1088,16 +1124,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1142,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1160,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1178,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1160,16 +1196,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1178,16 +1214,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1196,16 +1232,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1214,16 +1250,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1268,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1250,16 +1286,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1304,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1286,16 +1322,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1304,16 +1340,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1322,16 +1358,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1340,16 +1376,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1358,16 +1394,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1376,16 +1412,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1394,16 +1430,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1412,16 +1448,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1430,16 +1466,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1448,16 +1484,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1466,16 +1502,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1484,16 +1520,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1502,16 +1538,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1520,16 +1556,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1538,16 +1574,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1556,16 +1592,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1574,16 +1610,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1591,16 +1627,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1608,16 +1644,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1625,16 +1661,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1642,16 +1678,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1659,16 +1695,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1676,16 +1712,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1693,16 +1729,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1710,16 +1746,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1727,16 +1763,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1744,18 +1780,52 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B72FE5E-0174-41FA-9BD9-925CFE8113B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DA4555-E99E-44EE-9D95-A81A384CE95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,156 +57,6 @@
     <t>Relatório Recusa _ SICREDI_25.08.2025</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2026</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2027</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2028</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2029</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2030</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2031</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2032</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2033</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2034</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2035</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2036</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2037</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2038</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2039</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2040</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2041</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2042</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2043</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2044</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2045</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2046</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2047</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2048</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2049</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2050</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2051</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2052</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2053</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2054</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2055</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2056</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2057</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2058</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2059</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2060</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2061</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2062</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2063</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2064</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2065</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2066</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2067</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2068</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2069</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2070</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2071</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2072</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2073</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2074</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2075</t>
-  </si>
-  <si>
     <t>Relatório de Recusa Sicredi 25.08.2025</t>
   </si>
   <si>
@@ -376,12 +226,6 @@
   </si>
   <si>
     <t>133934879</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2076</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2077</t>
   </si>
 </sst>
 </file>
@@ -824,7 +668,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -836,13 +680,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -854,13 +698,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -872,13 +716,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -890,13 +734,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -908,16 +752,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -926,16 +770,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -944,16 +788,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -962,16 +806,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -980,16 +824,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -998,16 +842,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1016,16 +860,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1034,16 +878,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1052,16 +896,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1070,16 +914,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1088,16 +932,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1106,16 +950,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1124,16 +968,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1142,16 +986,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1160,16 +1004,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1178,16 +1022,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1196,16 +1040,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1214,16 +1058,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1076,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1250,16 +1094,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1112,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1286,16 +1130,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1304,16 +1148,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1322,16 +1166,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1340,16 +1184,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1358,16 +1202,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1376,16 +1220,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1394,16 +1238,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1412,16 +1256,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1430,16 +1274,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1448,16 +1292,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1466,16 +1310,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1484,16 +1328,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1502,16 +1346,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1520,16 +1364,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1538,16 +1382,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1556,16 +1400,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1574,16 +1418,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1592,16 +1436,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1610,16 +1454,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1627,16 +1471,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1644,16 +1488,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1661,16 +1505,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1678,16 +1522,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1695,16 +1539,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1712,16 +1556,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1729,16 +1573,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1746,16 +1590,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1763,16 +1607,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1780,16 +1624,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1797,16 +1641,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1814,16 +1658,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DA4555-E99E-44EE-9D95-A81A384CE95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862980FE-EC1A-4FB2-B91D-7CFFFB93D1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,178 +54,106 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_25.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 25.08.2025</t>
-  </si>
-  <si>
-    <t>133889264</t>
-  </si>
-  <si>
-    <t>130576763</t>
-  </si>
-  <si>
-    <t>133910459</t>
-  </si>
-  <si>
-    <t>133394297</t>
-  </si>
-  <si>
-    <t>133955421</t>
-  </si>
-  <si>
-    <t>133957093</t>
-  </si>
-  <si>
-    <t>133955031</t>
-  </si>
-  <si>
-    <t>133965118</t>
-  </si>
-  <si>
-    <t>133963814</t>
-  </si>
-  <si>
-    <t>133955570</t>
-  </si>
-  <si>
-    <t>133985710</t>
-  </si>
-  <si>
-    <t>134013995</t>
-  </si>
-  <si>
-    <t>134012764</t>
-  </si>
-  <si>
-    <t>134005752</t>
-  </si>
-  <si>
-    <t>133998817</t>
-  </si>
-  <si>
-    <t>133995262</t>
-  </si>
-  <si>
-    <t>134003105</t>
-  </si>
-  <si>
-    <t>134013430</t>
-  </si>
-  <si>
-    <t>133998572</t>
-  </si>
-  <si>
-    <t>134024228</t>
-  </si>
-  <si>
-    <t>134031432</t>
-  </si>
-  <si>
-    <t>134037875</t>
-  </si>
-  <si>
-    <t>134045114</t>
-  </si>
-  <si>
-    <t>134049116</t>
-  </si>
-  <si>
-    <t>133981311</t>
-  </si>
-  <si>
-    <t>134053774</t>
-  </si>
-  <si>
-    <t>134029540</t>
-  </si>
-  <si>
-    <t>134079955</t>
-  </si>
-  <si>
-    <t>134083871</t>
-  </si>
-  <si>
-    <t>134082660</t>
-  </si>
-  <si>
-    <t>133883156</t>
-  </si>
-  <si>
-    <t>133885953</t>
-  </si>
-  <si>
-    <t>133966506</t>
-  </si>
-  <si>
-    <t>131345100</t>
-  </si>
-  <si>
-    <t>133966257</t>
-  </si>
-  <si>
-    <t>134092724</t>
-  </si>
-  <si>
-    <t>133075468</t>
-  </si>
-  <si>
-    <t>133981988</t>
-  </si>
-  <si>
-    <t>133988818</t>
-  </si>
-  <si>
-    <t>133920587</t>
-  </si>
-  <si>
-    <t>133982757</t>
-  </si>
-  <si>
     <t>133095443</t>
   </si>
   <si>
-    <t>134092378</t>
-  </si>
-  <si>
-    <t>133932676</t>
-  </si>
-  <si>
-    <t>133951237</t>
-  </si>
-  <si>
-    <t>133941587</t>
-  </si>
-  <si>
-    <t>134026119</t>
-  </si>
-  <si>
-    <t>133960435</t>
-  </si>
-  <si>
-    <t>133964246</t>
-  </si>
-  <si>
-    <t>133964670</t>
-  </si>
-  <si>
-    <t>133966664</t>
-  </si>
-  <si>
-    <t>133966875</t>
-  </si>
-  <si>
-    <t>134000930</t>
-  </si>
-  <si>
-    <t>133983250</t>
-  </si>
-  <si>
-    <t>133874361</t>
-  </si>
-  <si>
-    <t>133934879</t>
+    <t>Relatório Recusa _ SICREDI_26.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 26.08.2025</t>
+  </si>
+  <si>
+    <t>133978689</t>
+  </si>
+  <si>
+    <t>133991201</t>
+  </si>
+  <si>
+    <t>133983548</t>
+  </si>
+  <si>
+    <t>133978563</t>
+  </si>
+  <si>
+    <t>133982277</t>
+  </si>
+  <si>
+    <t>133041270</t>
+  </si>
+  <si>
+    <t>134015195</t>
+  </si>
+  <si>
+    <t>134060783</t>
+  </si>
+  <si>
+    <t>134072853</t>
+  </si>
+  <si>
+    <t>134069887</t>
+  </si>
+  <si>
+    <t>134084775</t>
+  </si>
+  <si>
+    <t>134101664</t>
+  </si>
+  <si>
+    <t>134102653</t>
+  </si>
+  <si>
+    <t>133919396</t>
+  </si>
+  <si>
+    <t>134093884</t>
+  </si>
+  <si>
+    <t>134099667</t>
+  </si>
+  <si>
+    <t>134111646</t>
+  </si>
+  <si>
+    <t>134106275</t>
+  </si>
+  <si>
+    <t>134114593</t>
+  </si>
+  <si>
+    <t>133940973</t>
+  </si>
+  <si>
+    <t>133980864</t>
+  </si>
+  <si>
+    <t>134118499</t>
+  </si>
+  <si>
+    <t>134034179</t>
+  </si>
+  <si>
+    <t>133975998</t>
+  </si>
+  <si>
+    <t>134002685</t>
+  </si>
+  <si>
+    <t>134007938</t>
+  </si>
+  <si>
+    <t>133987812</t>
+  </si>
+  <si>
+    <t>134034394</t>
+  </si>
+  <si>
+    <t>133984459</t>
+  </si>
+  <si>
+    <t>134008114</t>
+  </si>
+  <si>
+    <t>132792847</t>
   </si>
 </sst>
 </file>
@@ -630,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -662,16 +590,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130664580</v>
+        <v>133927969</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -680,16 +608,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -698,16 +626,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -716,16 +644,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -734,16 +662,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -752,16 +680,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -770,16 +698,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -788,16 +716,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -806,16 +734,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -824,16 +752,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -842,16 +770,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -860,16 +788,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -878,16 +806,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -896,16 +824,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -914,16 +842,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -938,10 +866,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -956,10 +884,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -974,10 +902,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -992,10 +920,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1010,10 +938,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1028,10 +956,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1046,10 +974,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1064,10 +992,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1082,10 +1010,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1100,10 +1028,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1118,10 +1046,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1136,10 +1064,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1154,10 +1082,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1172,10 +1100,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1190,10 +1118,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1208,10 +1136,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1226,10 +1154,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1244,434 +1172,15 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862980FE-EC1A-4FB2-B91D-7CFFFB93D1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C70D2FB-F5B8-42E2-ACEA-FECF50126494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,127 @@
     <t>971</t>
   </si>
   <si>
-    <t>133095443</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_26.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 26.08.2025</t>
-  </si>
-  <si>
-    <t>133978689</t>
-  </si>
-  <si>
-    <t>133991201</t>
-  </si>
-  <si>
-    <t>133983548</t>
-  </si>
-  <si>
-    <t>133978563</t>
-  </si>
-  <si>
-    <t>133982277</t>
-  </si>
-  <si>
-    <t>133041270</t>
-  </si>
-  <si>
-    <t>134015195</t>
-  </si>
-  <si>
-    <t>134060783</t>
-  </si>
-  <si>
-    <t>134072853</t>
-  </si>
-  <si>
-    <t>134069887</t>
-  </si>
-  <si>
-    <t>134084775</t>
-  </si>
-  <si>
-    <t>134101664</t>
-  </si>
-  <si>
-    <t>134102653</t>
-  </si>
-  <si>
-    <t>133919396</t>
-  </si>
-  <si>
-    <t>134093884</t>
-  </si>
-  <si>
-    <t>134099667</t>
-  </si>
-  <si>
-    <t>134111646</t>
-  </si>
-  <si>
-    <t>134106275</t>
-  </si>
-  <si>
-    <t>134114593</t>
-  </si>
-  <si>
-    <t>133940973</t>
-  </si>
-  <si>
-    <t>133980864</t>
-  </si>
-  <si>
-    <t>134118499</t>
-  </si>
-  <si>
-    <t>134034179</t>
-  </si>
-  <si>
-    <t>133975998</t>
-  </si>
-  <si>
-    <t>134002685</t>
-  </si>
-  <si>
-    <t>134007938</t>
-  </si>
-  <si>
-    <t>133987812</t>
-  </si>
-  <si>
-    <t>134034394</t>
-  </si>
-  <si>
-    <t>133984459</t>
-  </si>
-  <si>
-    <t>134008114</t>
-  </si>
-  <si>
-    <t>132792847</t>
+    <t>Relatório de Recusa Sicredi 27.08.2025</t>
+  </si>
+  <si>
+    <t>134014030</t>
+  </si>
+  <si>
+    <t>134012012</t>
+  </si>
+  <si>
+    <t>134001281</t>
+  </si>
+  <si>
+    <t>134065483</t>
+  </si>
+  <si>
+    <t>134079178</t>
+  </si>
+  <si>
+    <t>133995750</t>
+  </si>
+  <si>
+    <t>134073807</t>
+  </si>
+  <si>
+    <t>134076284</t>
+  </si>
+  <si>
+    <t>133115071</t>
+  </si>
+  <si>
+    <t>134102153</t>
+  </si>
+  <si>
+    <t>134059303</t>
+  </si>
+  <si>
+    <t>134122412</t>
+  </si>
+  <si>
+    <t>134126642</t>
+  </si>
+  <si>
+    <t>134132313</t>
+  </si>
+  <si>
+    <t>134130498</t>
+  </si>
+  <si>
+    <t>134121555</t>
+  </si>
+  <si>
+    <t>134121310</t>
+  </si>
+  <si>
+    <t>134127529</t>
+  </si>
+  <si>
+    <t>134129540</t>
+  </si>
+  <si>
+    <t>133893977</t>
+  </si>
+  <si>
+    <t>133909617</t>
+  </si>
+  <si>
+    <t>133909972</t>
+  </si>
+  <si>
+    <t>133917488</t>
+  </si>
+  <si>
+    <t>133920282</t>
+  </si>
+  <si>
+    <t>134138838</t>
+  </si>
+  <si>
+    <t>134124241</t>
+  </si>
+  <si>
+    <t>133999897</t>
+  </si>
+  <si>
+    <t>130703872</t>
+  </si>
+  <si>
+    <t>132362706</t>
+  </si>
+  <si>
+    <t>133996801</t>
+  </si>
+  <si>
+    <t>133999029</t>
+  </si>
+  <si>
+    <t>134004763</t>
+  </si>
+  <si>
+    <t>134006186</t>
+  </si>
+  <si>
+    <t>134008350</t>
+  </si>
+  <si>
+    <t>134008382</t>
+  </si>
+  <si>
+    <t>134011013</t>
+  </si>
+  <si>
+    <t>133979885</t>
+  </si>
+  <si>
+    <t>134075238</t>
+  </si>
+  <si>
+    <t>134038665</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_27.08.2025</t>
   </si>
 </sst>
 </file>
@@ -558,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +611,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133927969</v>
+        <v>131852795</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,16 +629,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,16 +647,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,16 +665,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,16 +683,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,16 +701,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,16 +719,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,16 +737,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -734,16 +755,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -752,16 +773,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -770,16 +791,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -788,16 +809,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,16 +827,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -824,16 +845,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -842,16 +863,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,16 +881,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -878,16 +899,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -896,16 +917,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -914,16 +935,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -932,16 +953,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -950,16 +971,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -968,16 +989,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -986,16 +1007,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1025,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1043,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1040,16 +1061,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1058,16 +1079,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1076,16 +1097,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1094,16 +1115,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1112,16 +1133,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1151,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1148,16 +1169,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1166,21 +1187,140 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C70D2FB-F5B8-42E2-ACEA-FECF50126494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C2AF2-1E7F-4494-9A80-D1D9485485A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,133 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 27.08.2025</t>
-  </si>
-  <si>
-    <t>134014030</t>
-  </si>
-  <si>
-    <t>134012012</t>
-  </si>
-  <si>
-    <t>134001281</t>
-  </si>
-  <si>
-    <t>134065483</t>
-  </si>
-  <si>
-    <t>134079178</t>
-  </si>
-  <si>
-    <t>133995750</t>
-  </si>
-  <si>
-    <t>134073807</t>
-  </si>
-  <si>
-    <t>134076284</t>
-  </si>
-  <si>
-    <t>133115071</t>
-  </si>
-  <si>
-    <t>134102153</t>
-  </si>
-  <si>
-    <t>134059303</t>
-  </si>
-  <si>
-    <t>134122412</t>
-  </si>
-  <si>
-    <t>134126642</t>
-  </si>
-  <si>
-    <t>134132313</t>
-  </si>
-  <si>
-    <t>134130498</t>
-  </si>
-  <si>
-    <t>134121555</t>
-  </si>
-  <si>
-    <t>134121310</t>
-  </si>
-  <si>
-    <t>134127529</t>
-  </si>
-  <si>
-    <t>134129540</t>
-  </si>
-  <si>
-    <t>133893977</t>
-  </si>
-  <si>
-    <t>133909617</t>
-  </si>
-  <si>
-    <t>133909972</t>
-  </si>
-  <si>
-    <t>133917488</t>
-  </si>
-  <si>
-    <t>133920282</t>
-  </si>
-  <si>
-    <t>134138838</t>
-  </si>
-  <si>
-    <t>134124241</t>
-  </si>
-  <si>
-    <t>133999897</t>
-  </si>
-  <si>
-    <t>130703872</t>
-  </si>
-  <si>
-    <t>132362706</t>
-  </si>
-  <si>
-    <t>133996801</t>
-  </si>
-  <si>
-    <t>133999029</t>
-  </si>
-  <si>
-    <t>134004763</t>
-  </si>
-  <si>
-    <t>134006186</t>
-  </si>
-  <si>
-    <t>134008350</t>
-  </si>
-  <si>
-    <t>134008382</t>
-  </si>
-  <si>
-    <t>134011013</t>
-  </si>
-  <si>
-    <t>133979885</t>
-  </si>
-  <si>
-    <t>134075238</t>
-  </si>
-  <si>
-    <t>134038665</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_27.08.2025</t>
+    <t>Relatório Recusa _ SICREDI_28.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 28.08.2025</t>
+  </si>
+  <si>
+    <t>133968296</t>
+  </si>
+  <si>
+    <t>134029337</t>
+  </si>
+  <si>
+    <t>134037371</t>
+  </si>
+  <si>
+    <t>134039181</t>
+  </si>
+  <si>
+    <t>134024038</t>
+  </si>
+  <si>
+    <t>134084027</t>
+  </si>
+  <si>
+    <t>134036835</t>
+  </si>
+  <si>
+    <t>134109780</t>
+  </si>
+  <si>
+    <t>134109352</t>
+  </si>
+  <si>
+    <t>134115998</t>
+  </si>
+  <si>
+    <t>134126775</t>
+  </si>
+  <si>
+    <t>134039013</t>
+  </si>
+  <si>
+    <t>134114534</t>
+  </si>
+  <si>
+    <t>134145395</t>
+  </si>
+  <si>
+    <t>134146776</t>
+  </si>
+  <si>
+    <t>134108919</t>
+  </si>
+  <si>
+    <t>134143072</t>
+  </si>
+  <si>
+    <t>134156835</t>
+  </si>
+  <si>
+    <t>134141139</t>
+  </si>
+  <si>
+    <t>133955426</t>
+  </si>
+  <si>
+    <t>134071908</t>
+  </si>
+  <si>
+    <t>134034136</t>
+  </si>
+  <si>
+    <t>133965834</t>
+  </si>
+  <si>
+    <t>134028400</t>
+  </si>
+  <si>
+    <t>134083914</t>
+  </si>
+  <si>
+    <t>134018874</t>
+  </si>
+  <si>
+    <t>134022444</t>
+  </si>
+  <si>
+    <t>131369526</t>
+  </si>
+  <si>
+    <t>134027130</t>
+  </si>
+  <si>
+    <t>134021214</t>
+  </si>
+  <si>
+    <t>134034746</t>
+  </si>
+  <si>
+    <t>134081258</t>
+  </si>
+  <si>
+    <t>134036841</t>
+  </si>
+  <si>
+    <t>134037718</t>
+  </si>
+  <si>
+    <t>134176503</t>
+  </si>
+  <si>
+    <t>134076539</t>
+  </si>
+  <si>
+    <t>132722223</t>
+  </si>
+  <si>
+    <t>134180876</t>
+  </si>
+  <si>
+    <t>134173155</t>
+  </si>
+  <si>
+    <t>134070116</t>
+  </si>
+  <si>
+    <t>134076455</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -611,16 +617,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>131852795</v>
+        <v>130183532</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,16 +635,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,16 +653,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,16 +671,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -683,16 +689,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,16 +707,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -719,16 +725,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -737,16 +743,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -755,16 +761,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -773,16 +779,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -791,16 +797,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -809,16 +815,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -827,16 +833,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -845,16 +851,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -863,16 +869,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,16 +887,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -899,16 +905,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -917,16 +923,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -935,16 +941,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -953,16 +959,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -971,16 +977,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -989,16 +995,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1007,16 +1013,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1025,16 +1031,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1049,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1061,16 +1067,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1085,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1097,16 +1103,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1121,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1139,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1157,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1169,16 +1175,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1187,16 +1193,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1205,16 +1211,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1222,16 +1228,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1239,16 +1245,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1256,16 +1262,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1273,16 +1279,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1290,16 +1296,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1307,18 +1313,52 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C2AF2-1E7F-4494-9A80-D1D9485485A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B84623-2E69-4A4A-9435-43C88EED7383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="64">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,172 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_28.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 28.08.2025</t>
-  </si>
-  <si>
-    <t>133968296</t>
-  </si>
-  <si>
-    <t>134029337</t>
-  </si>
-  <si>
-    <t>134037371</t>
-  </si>
-  <si>
-    <t>134039181</t>
-  </si>
-  <si>
-    <t>134024038</t>
-  </si>
-  <si>
-    <t>134084027</t>
-  </si>
-  <si>
-    <t>134036835</t>
-  </si>
-  <si>
-    <t>134109780</t>
-  </si>
-  <si>
-    <t>134109352</t>
-  </si>
-  <si>
-    <t>134115998</t>
-  </si>
-  <si>
-    <t>134126775</t>
-  </si>
-  <si>
-    <t>134039013</t>
-  </si>
-  <si>
-    <t>134114534</t>
-  </si>
-  <si>
-    <t>134145395</t>
-  </si>
-  <si>
-    <t>134146776</t>
-  </si>
-  <si>
-    <t>134108919</t>
-  </si>
-  <si>
-    <t>134143072</t>
-  </si>
-  <si>
-    <t>134156835</t>
-  </si>
-  <si>
-    <t>134141139</t>
-  </si>
-  <si>
-    <t>133955426</t>
-  </si>
-  <si>
-    <t>134071908</t>
-  </si>
-  <si>
-    <t>134034136</t>
-  </si>
-  <si>
-    <t>133965834</t>
-  </si>
-  <si>
-    <t>134028400</t>
-  </si>
-  <si>
-    <t>134083914</t>
-  </si>
-  <si>
-    <t>134018874</t>
-  </si>
-  <si>
-    <t>134022444</t>
-  </si>
-  <si>
-    <t>131369526</t>
-  </si>
-  <si>
-    <t>134027130</t>
-  </si>
-  <si>
-    <t>134021214</t>
-  </si>
-  <si>
-    <t>134034746</t>
-  </si>
-  <si>
-    <t>134081258</t>
-  </si>
-  <si>
-    <t>134036841</t>
-  </si>
-  <si>
-    <t>134037718</t>
-  </si>
-  <si>
-    <t>134176503</t>
-  </si>
-  <si>
-    <t>134076539</t>
-  </si>
-  <si>
-    <t>132722223</t>
-  </si>
-  <si>
-    <t>134180876</t>
-  </si>
-  <si>
-    <t>134173155</t>
-  </si>
-  <si>
-    <t>134070116</t>
-  </si>
-  <si>
-    <t>134076455</t>
+    <t>Relatório de Recusa Sicredi 31.08.2025</t>
+  </si>
+  <si>
+    <t>133978885</t>
+  </si>
+  <si>
+    <t>134076478</t>
+  </si>
+  <si>
+    <t>134059934</t>
+  </si>
+  <si>
+    <t>134069879</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 29.08.2025</t>
+  </si>
+  <si>
+    <t>134100132</t>
+  </si>
+  <si>
+    <t>134099537</t>
+  </si>
+  <si>
+    <t>134128777</t>
+  </si>
+  <si>
+    <t>134114760</t>
+  </si>
+  <si>
+    <t>134144298</t>
+  </si>
+  <si>
+    <t>134157954</t>
+  </si>
+  <si>
+    <t>134142736</t>
+  </si>
+  <si>
+    <t>134155310</t>
+  </si>
+  <si>
+    <t>129876847</t>
+  </si>
+  <si>
+    <t>134165004</t>
+  </si>
+  <si>
+    <t>134163722</t>
+  </si>
+  <si>
+    <t>134173776</t>
+  </si>
+  <si>
+    <t>133824863</t>
+  </si>
+  <si>
+    <t>134174511</t>
+  </si>
+  <si>
+    <t>134182179</t>
+  </si>
+  <si>
+    <t>134180194</t>
+  </si>
+  <si>
+    <t>134171242</t>
+  </si>
+  <si>
+    <t>133964622</t>
+  </si>
+  <si>
+    <t>133981867</t>
+  </si>
+  <si>
+    <t>134059174</t>
+  </si>
+  <si>
+    <t>134079932</t>
+  </si>
+  <si>
+    <t>134097571</t>
+  </si>
+  <si>
+    <t>134191706</t>
+  </si>
+  <si>
+    <t>134193576</t>
+  </si>
+  <si>
+    <t>133115071</t>
+  </si>
+  <si>
+    <t>134196947</t>
+  </si>
+  <si>
+    <t>134101897</t>
+  </si>
+  <si>
+    <t>134201636</t>
+  </si>
+  <si>
+    <t>131847504</t>
+  </si>
+  <si>
+    <t>134204751</t>
+  </si>
+  <si>
+    <t>134205260</t>
+  </si>
+  <si>
+    <t>134043652</t>
+  </si>
+  <si>
+    <t>134053321</t>
+  </si>
+  <si>
+    <t>134204543</t>
+  </si>
+  <si>
+    <t>134059422</t>
+  </si>
+  <si>
+    <t>134060334</t>
+  </si>
+  <si>
+    <t>134060554</t>
+  </si>
+  <si>
+    <t>134207605</t>
+  </si>
+  <si>
+    <t>134176368</t>
+  </si>
+  <si>
+    <t>134117569</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_29.08.2025</t>
+  </si>
+  <si>
+    <t>134117326</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 30.08.2025</t>
+  </si>
+  <si>
+    <t>134072075</t>
+  </si>
+  <si>
+    <t>134190180</t>
+  </si>
+  <si>
+    <t>134200361</t>
+  </si>
+  <si>
+    <t>134207090</t>
+  </si>
+  <si>
+    <t>134061015</t>
+  </si>
+  <si>
+    <t>131283053</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_30.08.2025</t>
   </si>
 </sst>
 </file>
@@ -585,7 +624,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,16 +656,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130183532</v>
+        <v>133959307</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -635,16 +674,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -653,16 +692,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +710,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -689,16 +728,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -713,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -731,10 +770,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -749,10 +788,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -767,10 +806,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -785,10 +824,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -803,10 +842,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,10 +860,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,10 +896,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,10 +914,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,10 +950,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,10 +968,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,10 +986,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,10 +1004,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,10 +1040,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,10 +1058,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,10 +1076,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,10 +1094,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,10 +1112,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,10 +1130,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1109,10 +1148,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1127,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1145,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1163,10 +1202,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1181,10 +1220,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1199,10 +1238,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1217,10 +1256,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1234,10 +1273,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1251,10 +1290,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1268,10 +1307,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1285,10 +1324,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1302,10 +1341,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1319,10 +1358,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1336,10 +1375,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1353,12 +1392,182 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B84623-2E69-4A4A-9435-43C88EED7383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ECCBFC-2FC9-4B63-A8A2-6D41AC807286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,172 +54,91 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 31.08.2025</t>
-  </si>
-  <si>
-    <t>133978885</t>
-  </si>
-  <si>
-    <t>134076478</t>
-  </si>
-  <si>
-    <t>134059934</t>
-  </si>
-  <si>
-    <t>134069879</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 29.08.2025</t>
-  </si>
-  <si>
-    <t>134100132</t>
-  </si>
-  <si>
-    <t>134099537</t>
-  </si>
-  <si>
-    <t>134128777</t>
-  </si>
-  <si>
-    <t>134114760</t>
-  </si>
-  <si>
-    <t>134144298</t>
-  </si>
-  <si>
-    <t>134157954</t>
-  </si>
-  <si>
-    <t>134142736</t>
-  </si>
-  <si>
-    <t>134155310</t>
-  </si>
-  <si>
-    <t>129876847</t>
-  </si>
-  <si>
-    <t>134165004</t>
-  </si>
-  <si>
-    <t>134163722</t>
-  </si>
-  <si>
-    <t>134173776</t>
-  </si>
-  <si>
-    <t>133824863</t>
-  </si>
-  <si>
-    <t>134174511</t>
-  </si>
-  <si>
-    <t>134182179</t>
-  </si>
-  <si>
-    <t>134180194</t>
-  </si>
-  <si>
-    <t>134171242</t>
-  </si>
-  <si>
-    <t>133964622</t>
-  </si>
-  <si>
-    <t>133981867</t>
-  </si>
-  <si>
-    <t>134059174</t>
-  </si>
-  <si>
-    <t>134079932</t>
-  </si>
-  <si>
-    <t>134097571</t>
-  </si>
-  <si>
-    <t>134191706</t>
-  </si>
-  <si>
-    <t>134193576</t>
-  </si>
-  <si>
-    <t>133115071</t>
-  </si>
-  <si>
-    <t>134196947</t>
-  </si>
-  <si>
-    <t>134101897</t>
-  </si>
-  <si>
-    <t>134201636</t>
-  </si>
-  <si>
-    <t>131847504</t>
-  </si>
-  <si>
-    <t>134204751</t>
-  </si>
-  <si>
-    <t>134205260</t>
-  </si>
-  <si>
-    <t>134043652</t>
-  </si>
-  <si>
-    <t>134053321</t>
-  </si>
-  <si>
-    <t>134204543</t>
-  </si>
-  <si>
-    <t>134059422</t>
-  </si>
-  <si>
-    <t>134060334</t>
-  </si>
-  <si>
-    <t>134060554</t>
-  </si>
-  <si>
-    <t>134207605</t>
-  </si>
-  <si>
-    <t>134176368</t>
-  </si>
-  <si>
-    <t>134117569</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_29.08.2025</t>
-  </si>
-  <si>
-    <t>134117326</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 30.08.2025</t>
-  </si>
-  <si>
-    <t>134072075</t>
-  </si>
-  <si>
-    <t>134190180</t>
-  </si>
-  <si>
-    <t>134200361</t>
-  </si>
-  <si>
-    <t>134207090</t>
-  </si>
-  <si>
-    <t>134061015</t>
-  </si>
-  <si>
-    <t>131283053</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_30.08.2025</t>
+    <t>Relatório Recusa _ SICREDI_01.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 01/09/2025</t>
+  </si>
+  <si>
+    <t>134008709</t>
+  </si>
+  <si>
+    <t>131345100</t>
+  </si>
+  <si>
+    <t>134102418</t>
+  </si>
+  <si>
+    <t>134129014</t>
+  </si>
+  <si>
+    <t>134139957</t>
+  </si>
+  <si>
+    <t>134149543</t>
+  </si>
+  <si>
+    <t>134148663</t>
+  </si>
+  <si>
+    <t>134153732</t>
+  </si>
+  <si>
+    <t>134172016</t>
+  </si>
+  <si>
+    <t>134171296</t>
+  </si>
+  <si>
+    <t>134175002</t>
+  </si>
+  <si>
+    <t>134202915</t>
+  </si>
+  <si>
+    <t>131979212</t>
+  </si>
+  <si>
+    <t>134206795</t>
+  </si>
+  <si>
+    <t>134205531</t>
+  </si>
+  <si>
+    <t>134216441</t>
+  </si>
+  <si>
+    <t>134052680</t>
+  </si>
+  <si>
+    <t>134216133</t>
+  </si>
+  <si>
+    <t>134083308</t>
+  </si>
+  <si>
+    <t>130926264</t>
+  </si>
+  <si>
+    <t>134082284</t>
+  </si>
+  <si>
+    <t>134224221</t>
+  </si>
+  <si>
+    <t>134224824</t>
+  </si>
+  <si>
+    <t>133564240</t>
+  </si>
+  <si>
+    <t>134107273</t>
+  </si>
+  <si>
+    <t>134228410</t>
+  </si>
+  <si>
+    <t>134230230</t>
   </si>
 </sst>
 </file>
@@ -624,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -656,16 +575,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133959307</v>
+        <v>129773860</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -674,16 +593,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -692,16 +611,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -710,16 +629,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -728,16 +647,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -752,10 +671,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -770,10 +689,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -788,10 +707,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -806,10 +725,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -824,10 +743,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -842,10 +761,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -860,10 +779,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -878,10 +797,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -896,10 +815,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -914,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -932,10 +851,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -950,10 +869,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -968,10 +887,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -986,10 +905,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1004,10 +923,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1022,10 +941,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1040,10 +959,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1058,10 +977,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1076,10 +995,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1094,10 +1013,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1112,10 +1031,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1130,10 +1049,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1148,428 +1067,15 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ECCBFC-2FC9-4B63-A8A2-6D41AC807286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233539E9-0CF8-4007-BD84-F28364155E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,124 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_01.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 01/09/2025</t>
-  </si>
-  <si>
     <t>134008709</t>
   </si>
   <si>
-    <t>131345100</t>
-  </si>
-  <si>
-    <t>134102418</t>
-  </si>
-  <si>
-    <t>134129014</t>
-  </si>
-  <si>
-    <t>134139957</t>
-  </si>
-  <si>
-    <t>134149543</t>
-  </si>
-  <si>
-    <t>134148663</t>
-  </si>
-  <si>
-    <t>134153732</t>
-  </si>
-  <si>
-    <t>134172016</t>
-  </si>
-  <si>
-    <t>134171296</t>
-  </si>
-  <si>
-    <t>134175002</t>
-  </si>
-  <si>
-    <t>134202915</t>
-  </si>
-  <si>
-    <t>131979212</t>
-  </si>
-  <si>
-    <t>134206795</t>
-  </si>
-  <si>
-    <t>134205531</t>
-  </si>
-  <si>
-    <t>134216441</t>
-  </si>
-  <si>
-    <t>134052680</t>
-  </si>
-  <si>
-    <t>134216133</t>
-  </si>
-  <si>
-    <t>134083308</t>
-  </si>
-  <si>
-    <t>130926264</t>
-  </si>
-  <si>
-    <t>134082284</t>
-  </si>
-  <si>
-    <t>134224221</t>
-  </si>
-  <si>
-    <t>134224824</t>
-  </si>
-  <si>
-    <t>133564240</t>
-  </si>
-  <si>
-    <t>134107273</t>
-  </si>
-  <si>
-    <t>134228410</t>
-  </si>
-  <si>
-    <t>134230230</t>
+    <t>Relatório de Recusa Sicredi 02/09/2025</t>
+  </si>
+  <si>
+    <t>133999579</t>
+  </si>
+  <si>
+    <t>134109105</t>
+  </si>
+  <si>
+    <t>134102739</t>
+  </si>
+  <si>
+    <t>134105661</t>
+  </si>
+  <si>
+    <t>134108018</t>
+  </si>
+  <si>
+    <t>134156619</t>
+  </si>
+  <si>
+    <t>134103332</t>
+  </si>
+  <si>
+    <t>134176421</t>
+  </si>
+  <si>
+    <t>134208371</t>
+  </si>
+  <si>
+    <t>134116865</t>
+  </si>
+  <si>
+    <t>134221066</t>
+  </si>
+  <si>
+    <t>134228813</t>
+  </si>
+  <si>
+    <t>134231949</t>
+  </si>
+  <si>
+    <t>134229525</t>
+  </si>
+  <si>
+    <t>134227901</t>
+  </si>
+  <si>
+    <t>131692803</t>
+  </si>
+  <si>
+    <t>131999260</t>
+  </si>
+  <si>
+    <t>134098747</t>
+  </si>
+  <si>
+    <t>134095482</t>
+  </si>
+  <si>
+    <t>134096751</t>
+  </si>
+  <si>
+    <t>134098254</t>
+  </si>
+  <si>
+    <t>134102089</t>
+  </si>
+  <si>
+    <t>134102105</t>
+  </si>
+  <si>
+    <t>134104641</t>
+  </si>
+  <si>
+    <t>134105094</t>
+  </si>
+  <si>
+    <t>134106467</t>
+  </si>
+  <si>
+    <t>134107118</t>
+  </si>
+  <si>
+    <t>134107630</t>
+  </si>
+  <si>
+    <t>134108390</t>
+  </si>
+  <si>
+    <t>134109926</t>
+  </si>
+  <si>
+    <t>134122269</t>
+  </si>
+  <si>
+    <t>134155205</t>
+  </si>
+  <si>
+    <t>134246000</t>
+  </si>
+  <si>
+    <t>134250171</t>
+  </si>
+  <si>
+    <t>134177079</t>
+  </si>
+  <si>
+    <t>133972272</t>
+  </si>
+  <si>
+    <t>134253733</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_02.09.2025</t>
   </si>
 </sst>
 </file>
@@ -543,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,7 +608,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>129773860</v>
+        <v>130186761</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -584,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -602,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -611,7 +644,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -620,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -629,7 +662,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -638,7 +671,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -647,7 +680,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -656,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -665,7 +698,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -674,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -683,7 +716,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -692,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -701,7 +734,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -710,7 +743,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -719,7 +752,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -728,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,7 +770,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -746,7 +779,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -755,7 +788,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -764,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -773,7 +806,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -782,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -791,7 +824,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -800,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -809,7 +842,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -818,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -827,7 +860,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -836,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,7 +878,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -854,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -863,7 +896,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -872,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -881,7 +914,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -890,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,7 +932,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -908,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -917,7 +950,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -926,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -935,7 +968,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -944,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,7 +986,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -962,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -971,7 +1004,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -980,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -989,7 +1022,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -998,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1007,7 +1040,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1016,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1025,7 +1058,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1034,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1076,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1052,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,21 +1094,208 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233539E9-0CF8-4007-BD84-F28364155E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C35BFE-22A4-4688-B69B-91A5101D63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,124 +54,133 @@
     <t>971</t>
   </si>
   <si>
-    <t>134008709</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 02/09/2025</t>
-  </si>
-  <si>
-    <t>133999579</t>
-  </si>
-  <si>
-    <t>134109105</t>
-  </si>
-  <si>
-    <t>134102739</t>
-  </si>
-  <si>
-    <t>134105661</t>
-  </si>
-  <si>
-    <t>134108018</t>
-  </si>
-  <si>
-    <t>134156619</t>
-  </si>
-  <si>
-    <t>134103332</t>
-  </si>
-  <si>
-    <t>134176421</t>
-  </si>
-  <si>
-    <t>134208371</t>
-  </si>
-  <si>
-    <t>134116865</t>
-  </si>
-  <si>
-    <t>134221066</t>
-  </si>
-  <si>
-    <t>134228813</t>
-  </si>
-  <si>
-    <t>134231949</t>
-  </si>
-  <si>
-    <t>134229525</t>
-  </si>
-  <si>
-    <t>134227901</t>
-  </si>
-  <si>
-    <t>131692803</t>
-  </si>
-  <si>
-    <t>131999260</t>
-  </si>
-  <si>
-    <t>134098747</t>
-  </si>
-  <si>
-    <t>134095482</t>
-  </si>
-  <si>
-    <t>134096751</t>
-  </si>
-  <si>
-    <t>134098254</t>
-  </si>
-  <si>
-    <t>134102089</t>
-  </si>
-  <si>
-    <t>134102105</t>
-  </si>
-  <si>
-    <t>134104641</t>
-  </si>
-  <si>
-    <t>134105094</t>
-  </si>
-  <si>
-    <t>134106467</t>
-  </si>
-  <si>
-    <t>134107118</t>
-  </si>
-  <si>
-    <t>134107630</t>
-  </si>
-  <si>
-    <t>134108390</t>
-  </si>
-  <si>
-    <t>134109926</t>
-  </si>
-  <si>
-    <t>134122269</t>
-  </si>
-  <si>
-    <t>134155205</t>
-  </si>
-  <si>
-    <t>134246000</t>
-  </si>
-  <si>
-    <t>134250171</t>
-  </si>
-  <si>
-    <t>134177079</t>
-  </si>
-  <si>
-    <t>133972272</t>
-  </si>
-  <si>
-    <t>134253733</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_02.09.2025</t>
+    <t>Relatório de Recusa Sicredi 03/09/2025</t>
+  </si>
+  <si>
+    <t>131577582</t>
+  </si>
+  <si>
+    <t>134142804</t>
+  </si>
+  <si>
+    <t>134155344</t>
+  </si>
+  <si>
+    <t>134167553</t>
+  </si>
+  <si>
+    <t>134173925</t>
+  </si>
+  <si>
+    <t>134172837</t>
+  </si>
+  <si>
+    <t>134202543</t>
+  </si>
+  <si>
+    <t>134167040</t>
+  </si>
+  <si>
+    <t>134237713</t>
+  </si>
+  <si>
+    <t>134241800</t>
+  </si>
+  <si>
+    <t>134174668</t>
+  </si>
+  <si>
+    <t>134236252</t>
+  </si>
+  <si>
+    <t>134252507</t>
+  </si>
+  <si>
+    <t>134023260</t>
+  </si>
+  <si>
+    <t>134024352</t>
+  </si>
+  <si>
+    <t>133202586</t>
+  </si>
+  <si>
+    <t>134180033</t>
+  </si>
+  <si>
+    <t>134072282</t>
+  </si>
+  <si>
+    <t>132932631</t>
+  </si>
+  <si>
+    <t>134052655</t>
+  </si>
+  <si>
+    <t>134054046</t>
+  </si>
+  <si>
+    <t>134126708</t>
+  </si>
+  <si>
+    <t>134265235</t>
+  </si>
+  <si>
+    <t>134084445</t>
+  </si>
+  <si>
+    <t>134084911</t>
+  </si>
+  <si>
+    <t>134144111</t>
+  </si>
+  <si>
+    <t>134153744</t>
+  </si>
+  <si>
+    <t>131852795</t>
+  </si>
+  <si>
+    <t>134098481</t>
+  </si>
+  <si>
+    <t>134123255</t>
+  </si>
+  <si>
+    <t>134256527</t>
+  </si>
+  <si>
+    <t>134268708</t>
+  </si>
+  <si>
+    <t>134174551</t>
+  </si>
+  <si>
+    <t>134156107</t>
+  </si>
+  <si>
+    <t>134195167</t>
+  </si>
+  <si>
+    <t>134194674</t>
+  </si>
+  <si>
+    <t>134181821</t>
+  </si>
+  <si>
+    <t>134270438</t>
+  </si>
+  <si>
+    <t>134261476</t>
+  </si>
+  <si>
+    <t>134274161</t>
+  </si>
+  <si>
+    <t>134274535</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_03.09.2025</t>
   </si>
 </sst>
 </file>
@@ -576,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -608,16 +617,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130186761</v>
+        <v>133860214</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -626,16 +635,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -644,16 +653,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -668,10 +677,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -686,10 +695,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -704,10 +713,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,10 +731,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -740,10 +749,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -758,10 +767,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -776,10 +785,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -794,10 +803,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -812,10 +821,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,10 +839,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -848,10 +857,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -866,10 +875,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -884,10 +893,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -902,10 +911,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -920,10 +929,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -938,10 +947,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -956,10 +965,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -974,10 +983,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -992,10 +1001,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1010,10 +1019,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1028,10 +1037,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1046,10 +1055,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1064,10 +1073,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1082,10 +1091,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1100,10 +1109,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1118,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1135,10 +1144,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1152,10 +1161,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1169,10 +1178,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1186,10 +1195,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1203,10 +1212,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1220,10 +1229,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1237,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1254,10 +1263,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1271,10 +1280,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1288,12 +1297,63 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C35BFE-22A4-4688-B69B-91A5101D63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E89EE6-C48C-4281-87AD-CA4568D9F7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="65">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,175 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 03/09/2025</t>
-  </si>
-  <si>
-    <t>131577582</t>
-  </si>
-  <si>
-    <t>134142804</t>
-  </si>
-  <si>
-    <t>134155344</t>
-  </si>
-  <si>
-    <t>134167553</t>
-  </si>
-  <si>
-    <t>134173925</t>
-  </si>
-  <si>
-    <t>134172837</t>
-  </si>
-  <si>
-    <t>134202543</t>
-  </si>
-  <si>
-    <t>134167040</t>
-  </si>
-  <si>
-    <t>134237713</t>
-  </si>
-  <si>
-    <t>134241800</t>
-  </si>
-  <si>
-    <t>134174668</t>
-  </si>
-  <si>
-    <t>134236252</t>
-  </si>
-  <si>
-    <t>134252507</t>
-  </si>
-  <si>
-    <t>134023260</t>
-  </si>
-  <si>
-    <t>134024352</t>
-  </si>
-  <si>
-    <t>133202586</t>
-  </si>
-  <si>
-    <t>134180033</t>
-  </si>
-  <si>
-    <t>134072282</t>
-  </si>
-  <si>
-    <t>132932631</t>
-  </si>
-  <si>
-    <t>134052655</t>
-  </si>
-  <si>
-    <t>134054046</t>
-  </si>
-  <si>
-    <t>134126708</t>
-  </si>
-  <si>
-    <t>134265235</t>
-  </si>
-  <si>
-    <t>134084445</t>
-  </si>
-  <si>
-    <t>134084911</t>
-  </si>
-  <si>
-    <t>134144111</t>
-  </si>
-  <si>
-    <t>134153744</t>
-  </si>
-  <si>
-    <t>131852795</t>
-  </si>
-  <si>
-    <t>134098481</t>
-  </si>
-  <si>
-    <t>134123255</t>
-  </si>
-  <si>
-    <t>134256527</t>
-  </si>
-  <si>
-    <t>134268708</t>
-  </si>
-  <si>
-    <t>134174551</t>
-  </si>
-  <si>
-    <t>134156107</t>
-  </si>
-  <si>
-    <t>134195167</t>
-  </si>
-  <si>
-    <t>134194674</t>
-  </si>
-  <si>
-    <t>134181821</t>
-  </si>
-  <si>
-    <t>134270438</t>
-  </si>
-  <si>
-    <t>134261476</t>
-  </si>
-  <si>
-    <t>134274161</t>
-  </si>
-  <si>
-    <t>134274535</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_03.09.2025</t>
+    <t>Relatório Recusa _ SICREDI_04.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 04/09/2025</t>
+  </si>
+  <si>
+    <t>134076741</t>
+  </si>
+  <si>
+    <t>134084292</t>
+  </si>
+  <si>
+    <t>134082000</t>
+  </si>
+  <si>
+    <t>134081555</t>
+  </si>
+  <si>
+    <t>134078318</t>
+  </si>
+  <si>
+    <t>134145083</t>
+  </si>
+  <si>
+    <t>134158945</t>
+  </si>
+  <si>
+    <t>134156599</t>
+  </si>
+  <si>
+    <t>134158100</t>
+  </si>
+  <si>
+    <t>134159282</t>
+  </si>
+  <si>
+    <t>134145193</t>
+  </si>
+  <si>
+    <t>134157419</t>
+  </si>
+  <si>
+    <t>134126449</t>
+  </si>
+  <si>
+    <t>134187441</t>
+  </si>
+  <si>
+    <t>134131898</t>
+  </si>
+  <si>
+    <t>131790293</t>
+  </si>
+  <si>
+    <t>134227723</t>
+  </si>
+  <si>
+    <t>134239578</t>
+  </si>
+  <si>
+    <t>134253858</t>
+  </si>
+  <si>
+    <t>134260957</t>
+  </si>
+  <si>
+    <t>134273383</t>
+  </si>
+  <si>
+    <t>134273642</t>
+  </si>
+  <si>
+    <t>134256730</t>
+  </si>
+  <si>
+    <t>134272871</t>
+  </si>
+  <si>
+    <t>134069940</t>
+  </si>
+  <si>
+    <t>134083724</t>
+  </si>
+  <si>
+    <t>134085035</t>
+  </si>
+  <si>
+    <t>132091196</t>
+  </si>
+  <si>
+    <t>129551839</t>
+  </si>
+  <si>
+    <t>134281118</t>
+  </si>
+  <si>
+    <t>134284934</t>
+  </si>
+  <si>
+    <t>129809381</t>
+  </si>
+  <si>
+    <t>134287468</t>
+  </si>
+  <si>
+    <t>134124014</t>
+  </si>
+  <si>
+    <t>134129816</t>
+  </si>
+  <si>
+    <t>134129965</t>
+  </si>
+  <si>
+    <t>134132709</t>
+  </si>
+  <si>
+    <t>134288628</t>
+  </si>
+  <si>
+    <t>132169738</t>
+  </si>
+  <si>
+    <t>134194438</t>
+  </si>
+  <si>
+    <t>134066105</t>
+  </si>
+  <si>
+    <t>133394297</t>
+  </si>
+  <si>
+    <t>134149538</t>
+  </si>
+  <si>
+    <t>134149740</t>
+  </si>
+  <si>
+    <t>134151281</t>
+  </si>
+  <si>
+    <t>134076536</t>
+  </si>
+  <si>
+    <t>134154140</t>
+  </si>
+  <si>
+    <t>134154958</t>
+  </si>
+  <si>
+    <t>134156327</t>
+  </si>
+  <si>
+    <t>134156435</t>
+  </si>
+  <si>
+    <t>134080146</t>
+  </si>
+  <si>
+    <t>134158896</t>
+  </si>
+  <si>
+    <t>134288766</t>
+  </si>
+  <si>
+    <t>134294275</t>
+  </si>
+  <si>
+    <t>134273127</t>
   </si>
 </sst>
 </file>
@@ -585,7 +627,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,16 +659,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133860214</v>
+        <v>130469710</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -635,16 +677,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -653,16 +695,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +713,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -689,16 +731,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -707,16 +749,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -725,16 +767,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -743,16 +785,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -761,16 +803,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -779,16 +821,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -797,16 +839,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -815,16 +857,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -833,16 +875,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -851,16 +893,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -869,16 +911,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -887,16 +929,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -905,16 +947,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -923,16 +965,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -941,16 +983,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -959,16 +1001,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -977,16 +1019,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -995,16 +1037,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1055,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1031,16 +1073,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1091,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1109,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1085,16 +1127,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1103,16 +1145,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1121,16 +1163,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1138,16 +1180,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1155,16 +1197,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1172,16 +1214,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1189,16 +1231,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1206,16 +1248,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1223,16 +1265,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1240,16 +1282,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1257,16 +1299,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1274,16 +1316,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1291,16 +1333,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1308,16 +1350,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1325,16 +1367,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1342,18 +1384,256 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E89EE6-C48C-4281-87AD-CA4568D9F7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AFADCB-01DE-452F-BEB1-AD03965BDFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,175 +54,127 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_04.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 04/09/2025</t>
-  </si>
-  <si>
-    <t>134076741</t>
-  </si>
-  <si>
-    <t>134084292</t>
-  </si>
-  <si>
-    <t>134082000</t>
-  </si>
-  <si>
-    <t>134081555</t>
-  </si>
-  <si>
-    <t>134078318</t>
-  </si>
-  <si>
-    <t>134145083</t>
-  </si>
-  <si>
-    <t>134158945</t>
-  </si>
-  <si>
-    <t>134156599</t>
-  </si>
-  <si>
-    <t>134158100</t>
-  </si>
-  <si>
-    <t>134159282</t>
-  </si>
-  <si>
-    <t>134145193</t>
-  </si>
-  <si>
-    <t>134157419</t>
-  </si>
-  <si>
-    <t>134126449</t>
-  </si>
-  <si>
-    <t>134187441</t>
-  </si>
-  <si>
-    <t>134131898</t>
-  </si>
-  <si>
-    <t>131790293</t>
-  </si>
-  <si>
-    <t>134227723</t>
-  </si>
-  <si>
-    <t>134239578</t>
-  </si>
-  <si>
-    <t>134253858</t>
-  </si>
-  <si>
-    <t>134260957</t>
-  </si>
-  <si>
-    <t>134273383</t>
-  </si>
-  <si>
-    <t>134273642</t>
-  </si>
-  <si>
-    <t>134256730</t>
-  </si>
-  <si>
-    <t>134272871</t>
-  </si>
-  <si>
-    <t>134069940</t>
-  </si>
-  <si>
-    <t>134083724</t>
-  </si>
-  <si>
-    <t>134085035</t>
-  </si>
-  <si>
-    <t>132091196</t>
-  </si>
-  <si>
-    <t>129551839</t>
-  </si>
-  <si>
-    <t>134281118</t>
-  </si>
-  <si>
-    <t>134284934</t>
-  </si>
-  <si>
-    <t>129809381</t>
-  </si>
-  <si>
-    <t>134287468</t>
-  </si>
-  <si>
-    <t>134124014</t>
-  </si>
-  <si>
-    <t>134129816</t>
-  </si>
-  <si>
-    <t>134129965</t>
-  </si>
-  <si>
-    <t>134132709</t>
-  </si>
-  <si>
-    <t>134288628</t>
-  </si>
-  <si>
-    <t>132169738</t>
-  </si>
-  <si>
-    <t>134194438</t>
-  </si>
-  <si>
-    <t>134066105</t>
-  </si>
-  <si>
-    <t>133394297</t>
-  </si>
-  <si>
-    <t>134149538</t>
-  </si>
-  <si>
-    <t>134149740</t>
-  </si>
-  <si>
-    <t>134151281</t>
-  </si>
-  <si>
-    <t>134076536</t>
-  </si>
-  <si>
-    <t>134154140</t>
-  </si>
-  <si>
-    <t>134154958</t>
-  </si>
-  <si>
-    <t>134156327</t>
-  </si>
-  <si>
-    <t>134156435</t>
-  </si>
-  <si>
-    <t>134080146</t>
-  </si>
-  <si>
-    <t>134158896</t>
-  </si>
-  <si>
-    <t>134288766</t>
-  </si>
-  <si>
-    <t>134294275</t>
-  </si>
-  <si>
-    <t>134273127</t>
+    <t>Relatório Recusa _ SICREDI_06.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 06.09.2025</t>
+  </si>
+  <si>
+    <t>134124808</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_05.09.2025</t>
+  </si>
+  <si>
+    <t>134234931</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>NUP Indexações  05.09.2025</t>
+  </si>
+  <si>
+    <t>134234823</t>
+  </si>
+  <si>
+    <t>129567687</t>
+  </si>
+  <si>
+    <t>134281027</t>
+  </si>
+  <si>
+    <t>134166703</t>
+  </si>
+  <si>
+    <t>134328187</t>
+  </si>
+  <si>
+    <t>134280707</t>
+  </si>
+  <si>
+    <t>129256614</t>
+  </si>
+  <si>
+    <t>129521545</t>
+  </si>
+  <si>
+    <t>133706154</t>
+  </si>
+  <si>
+    <t>129590345</t>
+  </si>
+  <si>
+    <t>134090741</t>
+  </si>
+  <si>
+    <t>129316056</t>
+  </si>
+  <si>
+    <t>129288685</t>
+  </si>
+  <si>
+    <t>134165386</t>
+  </si>
+  <si>
+    <t>134236465</t>
+  </si>
+  <si>
+    <t>134283389</t>
+  </si>
+  <si>
+    <t>129580322</t>
+  </si>
+  <si>
+    <t>130588533</t>
+  </si>
+  <si>
+    <t>134167913</t>
+  </si>
+  <si>
+    <t>134288439</t>
+  </si>
+  <si>
+    <t>134241585</t>
+  </si>
+  <si>
+    <t>134157346</t>
+  </si>
+  <si>
+    <t>134213813</t>
+  </si>
+  <si>
+    <t>129444982</t>
+  </si>
+  <si>
+    <t>134164802</t>
+  </si>
+  <si>
+    <t>129636698</t>
+  </si>
+  <si>
+    <t>133860261</t>
+  </si>
+  <si>
+    <t>134135029</t>
+  </si>
+  <si>
+    <t>133785579</t>
+  </si>
+  <si>
+    <t>129587364</t>
+  </si>
+  <si>
+    <t>134114510</t>
+  </si>
+  <si>
+    <t>134059481</t>
+  </si>
+  <si>
+    <t>134050485</t>
+  </si>
+  <si>
+    <t>133994271</t>
   </si>
 </sst>
 </file>
@@ -627,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -659,7 +611,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130469710</v>
+        <v>134092737</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -695,518 +647,492 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1214,16 +1140,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1231,16 +1157,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1248,16 +1174,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1265,16 +1191,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1282,16 +1208,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1299,16 +1225,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1316,16 +1242,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1333,307 +1259,18 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AFADCB-01DE-452F-BEB1-AD03965BDFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE98EC2F-1592-45E7-A34A-CC7DA58D7AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="73">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,199 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_06.09.2025</t>
-  </si>
-  <si>
     <t>Relatório de Recusa Sicredi 06.09.2025</t>
   </si>
   <si>
     <t>134124808</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_05.09.2025</t>
-  </si>
-  <si>
-    <t>134234931</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>NUP Indexações  05.09.2025</t>
-  </si>
-  <si>
-    <t>134234823</t>
-  </si>
-  <si>
-    <t>129567687</t>
-  </si>
-  <si>
-    <t>134281027</t>
-  </si>
-  <si>
-    <t>134166703</t>
-  </si>
-  <si>
-    <t>134328187</t>
-  </si>
-  <si>
-    <t>134280707</t>
-  </si>
-  <si>
-    <t>129256614</t>
-  </si>
-  <si>
-    <t>129521545</t>
-  </si>
-  <si>
-    <t>133706154</t>
-  </si>
-  <si>
-    <t>129590345</t>
-  </si>
-  <si>
-    <t>134090741</t>
-  </si>
-  <si>
-    <t>129316056</t>
-  </si>
-  <si>
-    <t>129288685</t>
-  </si>
-  <si>
-    <t>134165386</t>
-  </si>
-  <si>
-    <t>134236465</t>
-  </si>
-  <si>
-    <t>134283389</t>
-  </si>
-  <si>
-    <t>129580322</t>
-  </si>
-  <si>
-    <t>130588533</t>
-  </si>
-  <si>
-    <t>134167913</t>
-  </si>
-  <si>
-    <t>134288439</t>
-  </si>
-  <si>
-    <t>134241585</t>
-  </si>
-  <si>
-    <t>134157346</t>
-  </si>
-  <si>
-    <t>134213813</t>
-  </si>
-  <si>
-    <t>129444982</t>
-  </si>
-  <si>
-    <t>134164802</t>
-  </si>
-  <si>
-    <t>129636698</t>
-  </si>
-  <si>
-    <t>133860261</t>
-  </si>
-  <si>
-    <t>134135029</t>
-  </si>
-  <si>
-    <t>133785579</t>
-  </si>
-  <si>
-    <t>129587364</t>
-  </si>
-  <si>
-    <t>134114510</t>
-  </si>
-  <si>
-    <t>134059481</t>
-  </si>
-  <si>
-    <t>134050485</t>
-  </si>
-  <si>
-    <t>133994271</t>
+    <t>Relatório Recusa _ SICREDI_06.09.2025.xlsx</t>
+  </si>
+  <si>
+    <t>130457650</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 05.09.2025</t>
+  </si>
+  <si>
+    <t>131738740</t>
+  </si>
+  <si>
+    <t>134175897</t>
+  </si>
+  <si>
+    <t>134179594</t>
+  </si>
+  <si>
+    <t>134182035</t>
+  </si>
+  <si>
+    <t>134169989</t>
+  </si>
+  <si>
+    <t>134195711</t>
+  </si>
+  <si>
+    <t>134193991</t>
+  </si>
+  <si>
+    <t>134220924</t>
+  </si>
+  <si>
+    <t>134228900</t>
+  </si>
+  <si>
+    <t>134230113</t>
+  </si>
+  <si>
+    <t>134221049</t>
+  </si>
+  <si>
+    <t>134222066</t>
+  </si>
+  <si>
+    <t>134248162</t>
+  </si>
+  <si>
+    <t>134266356</t>
+  </si>
+  <si>
+    <t>134271509</t>
+  </si>
+  <si>
+    <t>132840380</t>
+  </si>
+  <si>
+    <t>134292495</t>
+  </si>
+  <si>
+    <t>134290386</t>
+  </si>
+  <si>
+    <t>134296010</t>
+  </si>
+  <si>
+    <t>134296014</t>
+  </si>
+  <si>
+    <t>134290239</t>
+  </si>
+  <si>
+    <t>133228541</t>
+  </si>
+  <si>
+    <t>134179346</t>
+  </si>
+  <si>
+    <t>130126461</t>
+  </si>
+  <si>
+    <t>134306485</t>
+  </si>
+  <si>
+    <t>134305208</t>
+  </si>
+  <si>
+    <t>134307492</t>
+  </si>
+  <si>
+    <t>134307520</t>
+  </si>
+  <si>
+    <t>134308152</t>
+  </si>
+  <si>
+    <t>134175557</t>
+  </si>
+  <si>
+    <t>134310509</t>
+  </si>
+  <si>
+    <t>134310218</t>
+  </si>
+  <si>
+    <t>134311322</t>
+  </si>
+  <si>
+    <t>134199610</t>
+  </si>
+  <si>
+    <t>134081146</t>
+  </si>
+  <si>
+    <t>134077378</t>
+  </si>
+  <si>
+    <t>134168562</t>
+  </si>
+  <si>
+    <t>134175153</t>
+  </si>
+  <si>
+    <t>134198915</t>
+  </si>
+  <si>
+    <t>134314829</t>
+  </si>
+  <si>
+    <t>134315998</t>
+  </si>
+  <si>
+    <t>134224375</t>
+  </si>
+  <si>
+    <t>134310894</t>
+  </si>
+  <si>
+    <t>130917854</t>
+  </si>
+  <si>
+    <t>134163042</t>
+  </si>
+  <si>
+    <t>134164610</t>
+  </si>
+  <si>
+    <t>134321994</t>
+  </si>
+  <si>
+    <t>134170221</t>
+  </si>
+  <si>
+    <t>134321403</t>
+  </si>
+  <si>
+    <t>134174611</t>
+  </si>
+  <si>
+    <t>134176042</t>
+  </si>
+  <si>
+    <t>134177281</t>
+  </si>
+  <si>
+    <t>134177699</t>
+  </si>
+  <si>
+    <t>134179042</t>
+  </si>
+  <si>
+    <t>134179176</t>
+  </si>
+  <si>
+    <t>134179634</t>
+  </si>
+  <si>
+    <t>134179819</t>
+  </si>
+  <si>
+    <t>134180008</t>
+  </si>
+  <si>
+    <t>134206581</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_05.09.2025.xlsx</t>
   </si>
 </sst>
 </file>
@@ -579,7 +651,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,10 +689,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,16 +701,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,16 +719,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -664,16 +736,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -681,16 +753,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -698,16 +770,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -715,16 +787,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -732,16 +804,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -749,16 +821,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -766,16 +838,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -783,16 +855,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -800,16 +872,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -817,16 +889,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -834,16 +906,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -851,16 +923,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -868,16 +940,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -885,16 +957,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -902,16 +974,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -919,16 +991,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -936,16 +1008,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -953,16 +1025,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -970,16 +1042,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -987,16 +1059,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1076,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1021,16 +1093,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1038,16 +1110,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1055,16 +1127,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1072,16 +1144,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1089,16 +1161,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1178,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1123,16 +1195,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1140,16 +1212,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1157,16 +1229,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1174,16 +1246,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1191,16 +1263,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1208,16 +1280,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1225,16 +1297,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1242,16 +1314,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1259,18 +1331,409 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC07D23-3257-4303-8AB9-C2257B8CC482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C459AD-A2BB-4E81-8CF1-FB38A4DC2A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,169 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 06.09.2025</t>
-  </si>
-  <si>
-    <t>134124808</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_06.09.2025</t>
+    <t>Relatório de Recusa Sicredi 08/09/2025</t>
+  </si>
+  <si>
+    <t>134099057</t>
+  </si>
+  <si>
+    <t>134188577</t>
+  </si>
+  <si>
+    <t>134202519</t>
+  </si>
+  <si>
+    <t>134192795</t>
+  </si>
+  <si>
+    <t>134190824</t>
+  </si>
+  <si>
+    <t>134197852</t>
+  </si>
+  <si>
+    <t>134229376</t>
+  </si>
+  <si>
+    <t>134252050</t>
+  </si>
+  <si>
+    <t>134245596</t>
+  </si>
+  <si>
+    <t>134240118</t>
+  </si>
+  <si>
+    <t>134264695</t>
+  </si>
+  <si>
+    <t>134198786</t>
+  </si>
+  <si>
+    <t>134273066</t>
+  </si>
+  <si>
+    <t>134262621</t>
+  </si>
+  <si>
+    <t>134292007</t>
+  </si>
+  <si>
+    <t>134297650</t>
+  </si>
+  <si>
+    <t>134286171</t>
+  </si>
+  <si>
+    <t>134304341</t>
+  </si>
+  <si>
+    <t>134305553</t>
+  </si>
+  <si>
+    <t>134284852</t>
+  </si>
+  <si>
+    <t>134306368</t>
+  </si>
+  <si>
+    <t>134307478</t>
+  </si>
+  <si>
+    <t>134320075</t>
+  </si>
+  <si>
+    <t>134320061</t>
+  </si>
+  <si>
+    <t>134315337</t>
+  </si>
+  <si>
+    <t>129836220</t>
+  </si>
+  <si>
+    <t>134304261</t>
+  </si>
+  <si>
+    <t>132350461</t>
+  </si>
+  <si>
+    <t>134117788</t>
+  </si>
+  <si>
+    <t>134148330</t>
+  </si>
+  <si>
+    <t>134154575</t>
+  </si>
+  <si>
+    <t>134156139</t>
+  </si>
+  <si>
+    <t>134157812</t>
+  </si>
+  <si>
+    <t>129908901</t>
+  </si>
+  <si>
+    <t>134339885</t>
+  </si>
+  <si>
+    <t>134340132</t>
+  </si>
+  <si>
+    <t>134270493</t>
+  </si>
+  <si>
+    <t>134202432</t>
+  </si>
+  <si>
+    <t>134204341</t>
+  </si>
+  <si>
+    <t>134198666</t>
+  </si>
+  <si>
+    <t>134224001</t>
+  </si>
+  <si>
+    <t>134186237</t>
+  </si>
+  <si>
+    <t>134187012</t>
+  </si>
+  <si>
+    <t>134190143</t>
+  </si>
+  <si>
+    <t>134193561</t>
+  </si>
+  <si>
+    <t>134194819</t>
+  </si>
+  <si>
+    <t>134194867</t>
+  </si>
+  <si>
+    <t>134195629</t>
+  </si>
+  <si>
+    <t>134197241</t>
+  </si>
+  <si>
+    <t>134203536</t>
+  </si>
+  <si>
+    <t>134205801</t>
+  </si>
+  <si>
+    <t>134206248</t>
+  </si>
+  <si>
+    <t>134207961</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_08.09.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,7 +653,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134092737</v>
+        <v>130183532</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -506,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,12 +680,896 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C459AD-A2BB-4E81-8CF1-FB38A4DC2A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90327D31-5D67-4793-BE0E-4A5148527B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,130 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 08/09/2025</t>
-  </si>
-  <si>
-    <t>134099057</t>
-  </si>
-  <si>
-    <t>134188577</t>
-  </si>
-  <si>
-    <t>134202519</t>
-  </si>
-  <si>
-    <t>134192795</t>
-  </si>
-  <si>
-    <t>134190824</t>
-  </si>
-  <si>
-    <t>134197852</t>
-  </si>
-  <si>
-    <t>134229376</t>
-  </si>
-  <si>
-    <t>134252050</t>
-  </si>
-  <si>
-    <t>134245596</t>
-  </si>
-  <si>
-    <t>134240118</t>
-  </si>
-  <si>
-    <t>134264695</t>
-  </si>
-  <si>
-    <t>134198786</t>
-  </si>
-  <si>
-    <t>134273066</t>
-  </si>
-  <si>
-    <t>134262621</t>
-  </si>
-  <si>
-    <t>134292007</t>
-  </si>
-  <si>
-    <t>134297650</t>
-  </si>
-  <si>
-    <t>134286171</t>
-  </si>
-  <si>
-    <t>134304341</t>
-  </si>
-  <si>
-    <t>134305553</t>
-  </si>
-  <si>
-    <t>134284852</t>
-  </si>
-  <si>
-    <t>134306368</t>
-  </si>
-  <si>
-    <t>134307478</t>
-  </si>
-  <si>
-    <t>134320075</t>
-  </si>
-  <si>
-    <t>134320061</t>
-  </si>
-  <si>
-    <t>134315337</t>
-  </si>
-  <si>
-    <t>129836220</t>
-  </si>
-  <si>
-    <t>134304261</t>
-  </si>
-  <si>
-    <t>132350461</t>
-  </si>
-  <si>
-    <t>134117788</t>
-  </si>
-  <si>
-    <t>134148330</t>
-  </si>
-  <si>
-    <t>134154575</t>
-  </si>
-  <si>
-    <t>134156139</t>
-  </si>
-  <si>
-    <t>134157812</t>
-  </si>
-  <si>
-    <t>129908901</t>
-  </si>
-  <si>
-    <t>134339885</t>
-  </si>
-  <si>
-    <t>134340132</t>
-  </si>
-  <si>
-    <t>134270493</t>
-  </si>
-  <si>
-    <t>134202432</t>
-  </si>
-  <si>
-    <t>134204341</t>
-  </si>
-  <si>
-    <t>134198666</t>
-  </si>
-  <si>
-    <t>134224001</t>
-  </si>
-  <si>
-    <t>134186237</t>
-  </si>
-  <si>
-    <t>134187012</t>
-  </si>
-  <si>
-    <t>134190143</t>
-  </si>
-  <si>
-    <t>134193561</t>
-  </si>
-  <si>
-    <t>134194819</t>
-  </si>
-  <si>
-    <t>134194867</t>
-  </si>
-  <si>
-    <t>134195629</t>
-  </si>
-  <si>
-    <t>134197241</t>
-  </si>
-  <si>
-    <t>134203536</t>
-  </si>
-  <si>
-    <t>134205801</t>
-  </si>
-  <si>
-    <t>134206248</t>
-  </si>
-  <si>
-    <t>134207961</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_08.09.2025</t>
+    <t>Relatório Recusa _ SICREDI_09.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 09/09/2025</t>
+  </si>
+  <si>
+    <t>134216796</t>
+  </si>
+  <si>
+    <t>134225182</t>
+  </si>
+  <si>
+    <t>134237518</t>
+  </si>
+  <si>
+    <t>134269715</t>
+  </si>
+  <si>
+    <t>134268404</t>
+  </si>
+  <si>
+    <t>134285260</t>
+  </si>
+  <si>
+    <t>134285424</t>
+  </si>
+  <si>
+    <t>134295025</t>
+  </si>
+  <si>
+    <t>134288767</t>
+  </si>
+  <si>
+    <t>134258845</t>
+  </si>
+  <si>
+    <t>134303491</t>
+  </si>
+  <si>
+    <t>134297676</t>
+  </si>
+  <si>
+    <t>134321668</t>
+  </si>
+  <si>
+    <t>134306938</t>
+  </si>
+  <si>
+    <t>134203205</t>
+  </si>
+  <si>
+    <t>134329015</t>
+  </si>
+  <si>
+    <t>134343960</t>
+  </si>
+  <si>
+    <t>134345132</t>
+  </si>
+  <si>
+    <t>134123909</t>
+  </si>
+  <si>
+    <t>134125796</t>
+  </si>
+  <si>
+    <t>134109918</t>
+  </si>
+  <si>
+    <t>133864943</t>
+  </si>
+  <si>
+    <t>134247078</t>
+  </si>
+  <si>
+    <t>131512255</t>
+  </si>
+  <si>
+    <t>134227994</t>
+  </si>
+  <si>
+    <t>134251037</t>
+  </si>
+  <si>
+    <t>134275181</t>
+  </si>
+  <si>
+    <t>131701835</t>
+  </si>
+  <si>
+    <t>132037741</t>
+  </si>
+  <si>
+    <t>131906701</t>
+  </si>
+  <si>
+    <t>134265404</t>
+  </si>
+  <si>
+    <t>134311377</t>
+  </si>
+  <si>
+    <t>134361978</t>
+  </si>
+  <si>
+    <t>131450066</t>
+  </si>
+  <si>
+    <t>134224148</t>
+  </si>
+  <si>
+    <t>134225783</t>
+  </si>
+  <si>
+    <t>134180311</t>
+  </si>
+  <si>
+    <t>134267437</t>
+  </si>
+  <si>
+    <t>133691378</t>
+  </si>
+  <si>
+    <t>134252121</t>
   </si>
 </sst>
 </file>
@@ -621,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -653,16 +614,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130183532</v>
+        <v>130186761</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -671,16 +632,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -689,16 +650,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -706,16 +667,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -723,16 +684,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -740,16 +701,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -757,16 +718,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -774,16 +735,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -791,16 +752,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -808,16 +769,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -825,16 +786,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -842,16 +803,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -859,16 +820,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -876,16 +837,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -893,16 +854,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -910,16 +871,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -927,16 +888,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -944,16 +905,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -961,16 +922,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -978,16 +939,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,16 +956,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1012,16 +973,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1029,16 +990,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1046,16 +1007,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1063,16 +1024,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1080,16 +1041,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1097,16 +1058,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1114,16 +1075,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1131,16 +1092,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1148,16 +1109,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1165,16 +1126,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1182,16 +1143,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1199,16 +1160,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1216,16 +1177,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1233,16 +1194,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1250,16 +1211,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1267,16 +1228,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1284,16 +1245,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1301,16 +1262,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1318,16 +1279,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1335,239 +1296,18 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90327D31-5D67-4793-BE0E-4A5148527B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38374880-C238-4677-AECC-B1C758C252CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,85 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_09.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 09/09/2025</t>
-  </si>
-  <si>
-    <t>134216796</t>
-  </si>
-  <si>
-    <t>134225182</t>
-  </si>
-  <si>
-    <t>134237518</t>
-  </si>
-  <si>
-    <t>134269715</t>
-  </si>
-  <si>
-    <t>134268404</t>
-  </si>
-  <si>
-    <t>134285260</t>
-  </si>
-  <si>
-    <t>134285424</t>
-  </si>
-  <si>
-    <t>134295025</t>
-  </si>
-  <si>
-    <t>134288767</t>
-  </si>
-  <si>
-    <t>134258845</t>
-  </si>
-  <si>
-    <t>134303491</t>
-  </si>
-  <si>
-    <t>134297676</t>
-  </si>
-  <si>
-    <t>134321668</t>
-  </si>
-  <si>
-    <t>134306938</t>
-  </si>
-  <si>
-    <t>134203205</t>
-  </si>
-  <si>
-    <t>134329015</t>
-  </si>
-  <si>
-    <t>134343960</t>
-  </si>
-  <si>
-    <t>134345132</t>
-  </si>
-  <si>
-    <t>134123909</t>
-  </si>
-  <si>
-    <t>134125796</t>
-  </si>
-  <si>
-    <t>134109918</t>
-  </si>
-  <si>
-    <t>133864943</t>
-  </si>
-  <si>
-    <t>134247078</t>
-  </si>
-  <si>
-    <t>131512255</t>
-  </si>
-  <si>
-    <t>134227994</t>
-  </si>
-  <si>
-    <t>134251037</t>
-  </si>
-  <si>
-    <t>134275181</t>
-  </si>
-  <si>
-    <t>131701835</t>
-  </si>
-  <si>
-    <t>132037741</t>
-  </si>
-  <si>
-    <t>131906701</t>
-  </si>
-  <si>
-    <t>134265404</t>
-  </si>
-  <si>
-    <t>134311377</t>
-  </si>
-  <si>
-    <t>134361978</t>
-  </si>
-  <si>
-    <t>131450066</t>
-  </si>
-  <si>
-    <t>134224148</t>
-  </si>
-  <si>
-    <t>134225783</t>
-  </si>
-  <si>
-    <t>134180311</t>
-  </si>
-  <si>
-    <t>134267437</t>
-  </si>
-  <si>
-    <t>133691378</t>
-  </si>
-  <si>
-    <t>134252121</t>
+    <t>Relatório de Recusa Sicredi 10.09.2025</t>
+  </si>
+  <si>
+    <t>132540767</t>
+  </si>
+  <si>
+    <t>134253280</t>
+  </si>
+  <si>
+    <t>134230421</t>
+  </si>
+  <si>
+    <t>134290673</t>
+  </si>
+  <si>
+    <t>134308481</t>
+  </si>
+  <si>
+    <t>134252071</t>
+  </si>
+  <si>
+    <t>134322362</t>
+  </si>
+  <si>
+    <t>134311582</t>
+  </si>
+  <si>
+    <t>134355845</t>
+  </si>
+  <si>
+    <t>134360096</t>
+  </si>
+  <si>
+    <t>134365710</t>
+  </si>
+  <si>
+    <t>134367319</t>
+  </si>
+  <si>
+    <t>134355279</t>
+  </si>
+  <si>
+    <t>134149461</t>
+  </si>
+  <si>
+    <t>134152674</t>
+  </si>
+  <si>
+    <t>134265010</t>
+  </si>
+  <si>
+    <t>134288864</t>
+  </si>
+  <si>
+    <t>134180057</t>
+  </si>
+  <si>
+    <t>134249379</t>
+  </si>
+  <si>
+    <t>134291879</t>
+  </si>
+  <si>
+    <t>134271760</t>
+  </si>
+  <si>
+    <t>134252359</t>
+  </si>
+  <si>
+    <t>133710663</t>
+  </si>
+  <si>
+    <t>134202038</t>
+  </si>
+  <si>
+    <t>134389725</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_10.09.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +569,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130186761</v>
+        <v>129730047</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -632,16 +587,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -650,16 +605,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -667,16 +622,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -684,16 +639,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,16 +656,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -718,16 +673,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -735,16 +690,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -752,16 +707,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -769,16 +724,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -786,16 +741,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -803,16 +758,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -820,16 +775,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -837,16 +792,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,16 +809,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -871,16 +826,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -888,16 +843,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -905,16 +860,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -922,16 +877,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -939,16 +894,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -956,16 +911,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -973,16 +928,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -990,16 +945,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1007,16 +962,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1024,16 +979,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1041,273 +996,18 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38374880-C238-4677-AECC-B1C758C252CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAE5B30-7576-4032-B101-D8727CA365FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,85 +54,109 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 10.09.2025</t>
-  </si>
-  <si>
-    <t>132540767</t>
-  </si>
-  <si>
-    <t>134253280</t>
-  </si>
-  <si>
-    <t>134230421</t>
-  </si>
-  <si>
-    <t>134290673</t>
-  </si>
-  <si>
-    <t>134308481</t>
-  </si>
-  <si>
-    <t>134252071</t>
-  </si>
-  <si>
-    <t>134322362</t>
-  </si>
-  <si>
-    <t>134311582</t>
-  </si>
-  <si>
-    <t>134355845</t>
-  </si>
-  <si>
-    <t>134360096</t>
-  </si>
-  <si>
-    <t>134365710</t>
-  </si>
-  <si>
-    <t>134367319</t>
-  </si>
-  <si>
-    <t>134355279</t>
-  </si>
-  <si>
-    <t>134149461</t>
-  </si>
-  <si>
-    <t>134152674</t>
-  </si>
-  <si>
-    <t>134265010</t>
-  </si>
-  <si>
-    <t>134288864</t>
-  </si>
-  <si>
-    <t>134180057</t>
-  </si>
-  <si>
-    <t>134249379</t>
-  </si>
-  <si>
-    <t>134291879</t>
-  </si>
-  <si>
-    <t>134271760</t>
-  </si>
-  <si>
-    <t>134252359</t>
-  </si>
-  <si>
-    <t>133710663</t>
-  </si>
-  <si>
-    <t>134202038</t>
-  </si>
-  <si>
-    <t>134389725</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_10.09.2025</t>
+    <t>Relatório de Recusa Sicredi 11.09.2025</t>
+  </si>
+  <si>
+    <t>134264220</t>
+  </si>
+  <si>
+    <t>134274145</t>
+  </si>
+  <si>
+    <t>134260172</t>
+  </si>
+  <si>
+    <t>134193430</t>
+  </si>
+  <si>
+    <t>134316933</t>
+  </si>
+  <si>
+    <t>134311430</t>
+  </si>
+  <si>
+    <t>134197035</t>
+  </si>
+  <si>
+    <t>134263558</t>
+  </si>
+  <si>
+    <t>134271861</t>
+  </si>
+  <si>
+    <t>134274153</t>
+  </si>
+  <si>
+    <t>134313343</t>
+  </si>
+  <si>
+    <t>134206060</t>
+  </si>
+  <si>
+    <t>134378687</t>
+  </si>
+  <si>
+    <t>134389997</t>
+  </si>
+  <si>
+    <t>134386217</t>
+  </si>
+  <si>
+    <t>134197197</t>
+  </si>
+  <si>
+    <t>134228188</t>
+  </si>
+  <si>
+    <t>134280284</t>
+  </si>
+  <si>
+    <t>134294928</t>
+  </si>
+  <si>
+    <t>134315991</t>
+  </si>
+  <si>
+    <t>134402442</t>
+  </si>
+  <si>
+    <t>134297712</t>
+  </si>
+  <si>
+    <t>134260281</t>
+  </si>
+  <si>
+    <t>134405661</t>
+  </si>
+  <si>
+    <t>134249607</t>
+  </si>
+  <si>
+    <t>134401405</t>
+  </si>
+  <si>
+    <t>131669470</t>
+  </si>
+  <si>
+    <t>130950538</t>
+  </si>
+  <si>
+    <t>131577582</t>
+  </si>
+  <si>
+    <t>133596773</t>
+  </si>
+  <si>
+    <t>134259893</t>
+  </si>
+  <si>
+    <t>134269841</t>
+  </si>
+  <si>
+    <t>134271186</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_11.09.2025</t>
   </si>
 </sst>
 </file>
@@ -537,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,7 +593,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>129730047</v>
+        <v>134273829</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -578,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -596,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -614,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +655,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -648,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -665,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -682,7 +706,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -699,7 +723,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +757,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -750,7 +774,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -784,7 +808,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -801,7 +825,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -818,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -835,7 +859,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -852,7 +876,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -869,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -886,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -903,7 +927,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -920,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -937,7 +961,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -954,7 +978,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -971,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -988,7 +1012,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1005,9 +1029,145 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAE5B30-7576-4032-B101-D8727CA365FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59784AE4-50BE-4680-8FD0-5B5CD37F9663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="74">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,109 +54,202 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 11.09.2025</t>
-  </si>
-  <si>
-    <t>134264220</t>
-  </si>
-  <si>
-    <t>134274145</t>
-  </si>
-  <si>
-    <t>134260172</t>
-  </si>
-  <si>
-    <t>134193430</t>
-  </si>
-  <si>
-    <t>134316933</t>
-  </si>
-  <si>
-    <t>134311430</t>
-  </si>
-  <si>
-    <t>134197035</t>
-  </si>
-  <si>
-    <t>134263558</t>
-  </si>
-  <si>
-    <t>134271861</t>
-  </si>
-  <si>
-    <t>134274153</t>
-  </si>
-  <si>
-    <t>134313343</t>
-  </si>
-  <si>
-    <t>134206060</t>
-  </si>
-  <si>
-    <t>134378687</t>
-  </si>
-  <si>
-    <t>134389997</t>
-  </si>
-  <si>
-    <t>134386217</t>
-  </si>
-  <si>
-    <t>134197197</t>
-  </si>
-  <si>
-    <t>134228188</t>
-  </si>
-  <si>
-    <t>134280284</t>
-  </si>
-  <si>
-    <t>134294928</t>
-  </si>
-  <si>
-    <t>134315991</t>
-  </si>
-  <si>
-    <t>134402442</t>
-  </si>
-  <si>
-    <t>134297712</t>
-  </si>
-  <si>
-    <t>134260281</t>
-  </si>
-  <si>
-    <t>134405661</t>
-  </si>
-  <si>
-    <t>134249607</t>
-  </si>
-  <si>
-    <t>134401405</t>
-  </si>
-  <si>
-    <t>131669470</t>
-  </si>
-  <si>
-    <t>130950538</t>
-  </si>
-  <si>
-    <t>131577582</t>
-  </si>
-  <si>
-    <t>133596773</t>
-  </si>
-  <si>
-    <t>134259893</t>
-  </si>
-  <si>
-    <t>134269841</t>
-  </si>
-  <si>
-    <t>134271186</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_11.09.2025</t>
+    <t>Relatório de Recusa Sicredi 12.09.2025</t>
+  </si>
+  <si>
+    <t>134237814</t>
+  </si>
+  <si>
+    <t>134280023</t>
+  </si>
+  <si>
+    <t>134280690</t>
+  </si>
+  <si>
+    <t>134294738</t>
+  </si>
+  <si>
+    <t>134309553</t>
+  </si>
+  <si>
+    <t>134319588</t>
+  </si>
+  <si>
+    <t>131402512</t>
+  </si>
+  <si>
+    <t>134318812</t>
+  </si>
+  <si>
+    <t>134311127</t>
+  </si>
+  <si>
+    <t>134303192</t>
+  </si>
+  <si>
+    <t>134344571</t>
+  </si>
+  <si>
+    <t>134346088</t>
+  </si>
+  <si>
+    <t>134331923</t>
+  </si>
+  <si>
+    <t>134366855</t>
+  </si>
+  <si>
+    <t>134338349</t>
+  </si>
+  <si>
+    <t>134380863</t>
+  </si>
+  <si>
+    <t>134389460</t>
+  </si>
+  <si>
+    <t>134397081</t>
+  </si>
+  <si>
+    <t>134295972</t>
+  </si>
+  <si>
+    <t>134405679</t>
+  </si>
+  <si>
+    <t>134197967</t>
+  </si>
+  <si>
+    <t>134199388</t>
+  </si>
+  <si>
+    <t>134230980</t>
+  </si>
+  <si>
+    <t>130906729</t>
+  </si>
+  <si>
+    <t>134224138</t>
+  </si>
+  <si>
+    <t>134335454</t>
+  </si>
+  <si>
+    <t>134355640</t>
+  </si>
+  <si>
+    <t>134283727</t>
+  </si>
+  <si>
+    <t>134286106</t>
+  </si>
+  <si>
+    <t>134286811</t>
+  </si>
+  <si>
+    <t>134294082</t>
+  </si>
+  <si>
+    <t>134298749</t>
+  </si>
+  <si>
+    <t>134309371</t>
+  </si>
+  <si>
+    <t>134307766</t>
+  </si>
+  <si>
+    <t>134343014</t>
+  </si>
+  <si>
+    <t>134237752</t>
+  </si>
+  <si>
+    <t>129670426</t>
+  </si>
+  <si>
+    <t>134200048</t>
+  </si>
+  <si>
+    <t>134198094</t>
+  </si>
+  <si>
+    <t>134206827</t>
+  </si>
+  <si>
+    <t>134366783</t>
+  </si>
+  <si>
+    <t>134428648</t>
+  </si>
+  <si>
+    <t>134429555</t>
+  </si>
+  <si>
+    <t>134424197</t>
+  </si>
+  <si>
+    <t>134282125</t>
+  </si>
+  <si>
+    <t>134431105</t>
+  </si>
+  <si>
+    <t>134434440</t>
+  </si>
+  <si>
+    <t>134319414</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_12.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_13.09.2025</t>
+  </si>
+  <si>
+    <t>134229903</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 13.09.2025</t>
+  </si>
+  <si>
+    <t>134240618</t>
+  </si>
+  <si>
+    <t>134409568</t>
+  </si>
+  <si>
+    <t>134228542</t>
+  </si>
+  <si>
+    <t>134191048</t>
+  </si>
+  <si>
+    <t>134230186</t>
+  </si>
+  <si>
+    <t>134222564</t>
+  </si>
+  <si>
+    <t>134220843</t>
+  </si>
+  <si>
+    <t>134235672</t>
+  </si>
+  <si>
+    <t>134236179</t>
+  </si>
+  <si>
+    <t>134243279</t>
+  </si>
+  <si>
+    <t>134244347</t>
+  </si>
+  <si>
+    <t>130657700</t>
+  </si>
+  <si>
+    <t>131905435</t>
   </si>
 </sst>
 </file>
@@ -561,7 +654,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -593,7 +686,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134273829</v>
+        <v>130469710</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -602,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -620,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -638,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -655,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -672,7 +765,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -689,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -706,7 +799,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -723,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -740,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -757,7 +850,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -774,7 +867,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -791,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -808,7 +901,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -825,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -842,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -859,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -876,7 +969,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -893,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -910,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -927,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -944,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -961,7 +1054,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -978,7 +1071,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -995,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1012,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1029,7 +1122,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1046,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1063,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1080,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1114,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1131,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1165,9 +1258,502 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59784AE4-50BE-4680-8FD0-5B5CD37F9663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7DEFBB-40EC-46C6-9D55-6825E83F635F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="56">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,202 +54,148 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 12.09.2025</t>
-  </si>
-  <si>
-    <t>134237814</t>
-  </si>
-  <si>
-    <t>134280023</t>
-  </si>
-  <si>
-    <t>134280690</t>
-  </si>
-  <si>
-    <t>134294738</t>
-  </si>
-  <si>
-    <t>134309553</t>
-  </si>
-  <si>
-    <t>134319588</t>
-  </si>
-  <si>
-    <t>131402512</t>
-  </si>
-  <si>
-    <t>134318812</t>
-  </si>
-  <si>
-    <t>134311127</t>
-  </si>
-  <si>
-    <t>134303192</t>
-  </si>
-  <si>
-    <t>134344571</t>
-  </si>
-  <si>
-    <t>134346088</t>
-  </si>
-  <si>
-    <t>134331923</t>
-  </si>
-  <si>
-    <t>134366855</t>
-  </si>
-  <si>
-    <t>134338349</t>
-  </si>
-  <si>
-    <t>134380863</t>
-  </si>
-  <si>
-    <t>134389460</t>
-  </si>
-  <si>
-    <t>134397081</t>
-  </si>
-  <si>
-    <t>134295972</t>
-  </si>
-  <si>
-    <t>134405679</t>
-  </si>
-  <si>
-    <t>134197967</t>
-  </si>
-  <si>
-    <t>134199388</t>
-  </si>
-  <si>
-    <t>134230980</t>
-  </si>
-  <si>
-    <t>130906729</t>
-  </si>
-  <si>
-    <t>134224138</t>
-  </si>
-  <si>
-    <t>134335454</t>
-  </si>
-  <si>
-    <t>134355640</t>
-  </si>
-  <si>
-    <t>134283727</t>
-  </si>
-  <si>
-    <t>134286106</t>
-  </si>
-  <si>
-    <t>134286811</t>
-  </si>
-  <si>
-    <t>134294082</t>
-  </si>
-  <si>
-    <t>134298749</t>
-  </si>
-  <si>
-    <t>134309371</t>
-  </si>
-  <si>
-    <t>134307766</t>
-  </si>
-  <si>
-    <t>134343014</t>
-  </si>
-  <si>
-    <t>134237752</t>
-  </si>
-  <si>
-    <t>129670426</t>
-  </si>
-  <si>
-    <t>134200048</t>
-  </si>
-  <si>
-    <t>134198094</t>
-  </si>
-  <si>
-    <t>134206827</t>
-  </si>
-  <si>
-    <t>134366783</t>
-  </si>
-  <si>
-    <t>134428648</t>
-  </si>
-  <si>
-    <t>134429555</t>
-  </si>
-  <si>
-    <t>134424197</t>
-  </si>
-  <si>
-    <t>134282125</t>
-  </si>
-  <si>
-    <t>134431105</t>
-  </si>
-  <si>
-    <t>134434440</t>
-  </si>
-  <si>
-    <t>134319414</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_12.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_13.09.2025</t>
-  </si>
-  <si>
-    <t>134229903</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 13.09.2025</t>
-  </si>
-  <si>
-    <t>134240618</t>
-  </si>
-  <si>
-    <t>134409568</t>
-  </si>
-  <si>
-    <t>134228542</t>
-  </si>
-  <si>
-    <t>134191048</t>
-  </si>
-  <si>
-    <t>134230186</t>
-  </si>
-  <si>
-    <t>134222564</t>
-  </si>
-  <si>
-    <t>134220843</t>
-  </si>
-  <si>
-    <t>134235672</t>
-  </si>
-  <si>
-    <t>134236179</t>
-  </si>
-  <si>
-    <t>134243279</t>
-  </si>
-  <si>
-    <t>134244347</t>
-  </si>
-  <si>
-    <t>130657700</t>
-  </si>
-  <si>
-    <t>131905435</t>
+    <t>Relatório Recusa _ SICREDI_15.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 15/09/2025</t>
+  </si>
+  <si>
+    <t>134316062</t>
+  </si>
+  <si>
+    <t>134351122</t>
+  </si>
+  <si>
+    <t>134353090</t>
+  </si>
+  <si>
+    <t>134356653</t>
+  </si>
+  <si>
+    <t>134362797</t>
+  </si>
+  <si>
+    <t>134354390</t>
+  </si>
+  <si>
+    <t>134319826</t>
+  </si>
+  <si>
+    <t>134294545</t>
+  </si>
+  <si>
+    <t>134360912</t>
+  </si>
+  <si>
+    <t>134319274</t>
+  </si>
+  <si>
+    <t>134338099</t>
+  </si>
+  <si>
+    <t>134410589</t>
+  </si>
+  <si>
+    <t>133480821</t>
+  </si>
+  <si>
+    <t>134418724</t>
+  </si>
+  <si>
+    <t>134435199</t>
+  </si>
+  <si>
+    <t>134315171</t>
+  </si>
+  <si>
+    <t>134404058</t>
+  </si>
+  <si>
+    <t>134446076</t>
+  </si>
+  <si>
+    <t>134343267</t>
+  </si>
+  <si>
+    <t>134274254</t>
+  </si>
+  <si>
+    <t>134448370</t>
+  </si>
+  <si>
+    <t>134451131</t>
+  </si>
+  <si>
+    <t>133394297</t>
+  </si>
+  <si>
+    <t>134303877</t>
+  </si>
+  <si>
+    <t>134305800</t>
+  </si>
+  <si>
+    <t>134307986</t>
+  </si>
+  <si>
+    <t>134310263</t>
+  </si>
+  <si>
+    <t>134312471</t>
+  </si>
+  <si>
+    <t>134361238</t>
+  </si>
+  <si>
+    <t>134335157</t>
+  </si>
+  <si>
+    <t>130126461</t>
+  </si>
+  <si>
+    <t>134309092</t>
+  </si>
+  <si>
+    <t>134354451</t>
+  </si>
+  <si>
+    <t>134455051</t>
+  </si>
+  <si>
+    <t>134357639</t>
+  </si>
+  <si>
+    <t>133445302</t>
+  </si>
+  <si>
+    <t>134381255</t>
+  </si>
+  <si>
+    <t>134457536</t>
+  </si>
+  <si>
+    <t>134357844</t>
+  </si>
+  <si>
+    <t>134458715</t>
+  </si>
+  <si>
+    <t>134331112</t>
+  </si>
+  <si>
+    <t>134253639</t>
+  </si>
+  <si>
+    <t>134258301</t>
+  </si>
+  <si>
+    <t>134270419</t>
+  </si>
+  <si>
+    <t>134283016</t>
+  </si>
+  <si>
+    <t>134329043</t>
   </si>
 </sst>
 </file>
@@ -654,7 +600,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -686,16 +632,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130469710</v>
+        <v>134303800</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -704,16 +650,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -722,16 +668,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -739,16 +685,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -756,16 +702,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -773,16 +719,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -790,16 +736,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -807,16 +753,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -824,16 +770,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -841,16 +787,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -858,16 +804,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -875,16 +821,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -892,16 +838,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -909,16 +855,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -926,16 +872,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -943,16 +889,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -960,16 +906,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -977,16 +923,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -994,16 +940,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1011,16 +957,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1028,16 +974,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1045,16 +991,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1062,16 +1008,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1025,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1096,16 +1042,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1113,16 +1059,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1076,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1147,16 +1093,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1164,16 +1110,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1181,16 +1127,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1198,16 +1144,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1215,16 +1161,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1178,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1249,16 +1195,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1266,16 +1212,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1283,16 +1229,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1300,16 +1246,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1317,16 +1263,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1334,16 +1280,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1351,16 +1297,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1368,16 +1314,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1385,16 +1331,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1402,16 +1348,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1419,16 +1365,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1436,16 +1382,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1453,16 +1399,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1470,290 +1416,18 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7DEFBB-40EC-46C6-9D55-6825E83F635F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607081AD-31F1-43E2-862F-12BAD66722BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,148 +54,154 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_15.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 15/09/2025</t>
-  </si>
-  <si>
-    <t>134316062</t>
-  </si>
-  <si>
-    <t>134351122</t>
-  </si>
-  <si>
-    <t>134353090</t>
-  </si>
-  <si>
-    <t>134356653</t>
-  </si>
-  <si>
-    <t>134362797</t>
-  </si>
-  <si>
-    <t>134354390</t>
-  </si>
-  <si>
-    <t>134319826</t>
-  </si>
-  <si>
-    <t>134294545</t>
-  </si>
-  <si>
-    <t>134360912</t>
-  </si>
-  <si>
-    <t>134319274</t>
-  </si>
-  <si>
-    <t>134338099</t>
-  </si>
-  <si>
-    <t>134410589</t>
-  </si>
-  <si>
-    <t>133480821</t>
-  </si>
-  <si>
-    <t>134418724</t>
-  </si>
-  <si>
-    <t>134435199</t>
-  </si>
-  <si>
-    <t>134315171</t>
-  </si>
-  <si>
-    <t>134404058</t>
-  </si>
-  <si>
-    <t>134446076</t>
-  </si>
-  <si>
-    <t>134343267</t>
-  </si>
-  <si>
-    <t>134274254</t>
-  </si>
-  <si>
-    <t>134448370</t>
-  </si>
-  <si>
-    <t>134451131</t>
-  </si>
-  <si>
-    <t>133394297</t>
-  </si>
-  <si>
-    <t>134303877</t>
-  </si>
-  <si>
-    <t>134305800</t>
-  </si>
-  <si>
-    <t>134307986</t>
-  </si>
-  <si>
-    <t>134310263</t>
-  </si>
-  <si>
-    <t>134312471</t>
-  </si>
-  <si>
-    <t>134361238</t>
-  </si>
-  <si>
-    <t>134335157</t>
-  </si>
-  <si>
-    <t>130126461</t>
-  </si>
-  <si>
-    <t>134309092</t>
-  </si>
-  <si>
-    <t>134354451</t>
-  </si>
-  <si>
-    <t>134455051</t>
-  </si>
-  <si>
-    <t>134357639</t>
-  </si>
-  <si>
-    <t>133445302</t>
-  </si>
-  <si>
-    <t>134381255</t>
-  </si>
-  <si>
-    <t>134457536</t>
-  </si>
-  <si>
-    <t>134357844</t>
-  </si>
-  <si>
-    <t>134458715</t>
-  </si>
-  <si>
-    <t>134331112</t>
-  </si>
-  <si>
-    <t>134253639</t>
-  </si>
-  <si>
-    <t>134258301</t>
-  </si>
-  <si>
-    <t>134270419</t>
-  </si>
-  <si>
-    <t>134283016</t>
-  </si>
-  <si>
-    <t>134329043</t>
+    <t>Relatório Recusa _ SICREDI_16.09.2025</t>
+  </si>
+  <si>
+    <t>vRelatório Recusa _ SICREDI_16.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 16.09.2025</t>
+  </si>
+  <si>
+    <t>134318576</t>
+  </si>
+  <si>
+    <t>134333024</t>
+  </si>
+  <si>
+    <t>134342475</t>
+  </si>
+  <si>
+    <t>134346355</t>
+  </si>
+  <si>
+    <t>134364320</t>
+  </si>
+  <si>
+    <t>134363765</t>
+  </si>
+  <si>
+    <t>134385494</t>
+  </si>
+  <si>
+    <t>134391070</t>
+  </si>
+  <si>
+    <t>134398855</t>
+  </si>
+  <si>
+    <t>134408656</t>
+  </si>
+  <si>
+    <t>134387920</t>
+  </si>
+  <si>
+    <t>134435484</t>
+  </si>
+  <si>
+    <t>134436971</t>
+  </si>
+  <si>
+    <t>134448454</t>
+  </si>
+  <si>
+    <t>134449468</t>
+  </si>
+  <si>
+    <t>134353741</t>
+  </si>
+  <si>
+    <t>134454888</t>
+  </si>
+  <si>
+    <t>134245350</t>
+  </si>
+  <si>
+    <t>134249359</t>
+  </si>
+  <si>
+    <t>134252813</t>
+  </si>
+  <si>
+    <t>134330660</t>
+  </si>
+  <si>
+    <t>134377006</t>
+  </si>
+  <si>
+    <t>134471200</t>
+  </si>
+  <si>
+    <t>134468222</t>
+  </si>
+  <si>
+    <t>134317364</t>
+  </si>
+  <si>
+    <t>134317561</t>
+  </si>
+  <si>
+    <t>134318813</t>
+  </si>
+  <si>
+    <t>134318850</t>
+  </si>
+  <si>
+    <t>134405509</t>
+  </si>
+  <si>
+    <t>134321004</t>
+  </si>
+  <si>
+    <t>134374065</t>
+  </si>
+  <si>
+    <t>134252750</t>
+  </si>
+  <si>
+    <t>134248978</t>
+  </si>
+  <si>
+    <t>134355878</t>
+  </si>
+  <si>
+    <t>134480253</t>
+  </si>
+  <si>
+    <t>130087031</t>
+  </si>
+  <si>
+    <t>134388053</t>
+  </si>
+  <si>
+    <t>134296334</t>
+  </si>
+  <si>
+    <t>134329184</t>
+  </si>
+  <si>
+    <t>134330700</t>
+  </si>
+  <si>
+    <t>134332669</t>
+  </si>
+  <si>
+    <t>134333015</t>
+  </si>
+  <si>
+    <t>134333758</t>
+  </si>
+  <si>
+    <t>134336539</t>
+  </si>
+  <si>
+    <t>134340054</t>
+  </si>
+  <si>
+    <t>134345466</t>
+  </si>
+  <si>
+    <t>134346112</t>
   </si>
 </sst>
 </file>
@@ -600,7 +606,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -632,13 +638,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134303800</v>
+        <v>134320964</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -650,13 +656,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -668,16 +674,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -685,13 +691,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -702,13 +708,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -719,13 +725,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -736,13 +742,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -753,13 +759,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -770,13 +776,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -787,13 +793,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -804,13 +810,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -821,16 +827,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -838,13 +844,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -855,13 +861,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -872,13 +878,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -889,13 +895,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
@@ -906,13 +912,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -923,13 +929,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -940,13 +946,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -957,13 +963,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -974,13 +980,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -991,13 +997,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -1008,13 +1014,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -1025,13 +1031,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
@@ -1042,13 +1048,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -1059,13 +1065,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
@@ -1076,16 +1082,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1093,13 +1099,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
@@ -1110,13 +1116,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -1127,13 +1133,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -1144,13 +1150,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -1161,13 +1167,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -1178,13 +1184,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
@@ -1195,13 +1201,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
@@ -1212,13 +1218,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
@@ -1229,13 +1235,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
@@ -1246,13 +1252,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -1263,13 +1269,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -1280,13 +1286,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -1297,13 +1303,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -1314,13 +1320,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -1331,16 +1337,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1348,13 +1354,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -1365,13 +1371,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
@@ -1382,13 +1388,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -1399,13 +1405,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -1416,18 +1422,35 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607081AD-31F1-43E2-862F-12BAD66722BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93A07AE-4746-4CD8-AB98-855D9496E76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,154 +54,169 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_16.09.2025</t>
-  </si>
-  <si>
-    <t>vRelatório Recusa _ SICREDI_16.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 16.09.2025</t>
-  </si>
-  <si>
-    <t>134318576</t>
-  </si>
-  <si>
-    <t>134333024</t>
-  </si>
-  <si>
-    <t>134342475</t>
-  </si>
-  <si>
-    <t>134346355</t>
-  </si>
-  <si>
-    <t>134364320</t>
-  </si>
-  <si>
-    <t>134363765</t>
-  </si>
-  <si>
-    <t>134385494</t>
-  </si>
-  <si>
-    <t>134391070</t>
-  </si>
-  <si>
-    <t>134398855</t>
-  </si>
-  <si>
-    <t>134408656</t>
-  </si>
-  <si>
-    <t>134387920</t>
-  </si>
-  <si>
-    <t>134435484</t>
-  </si>
-  <si>
-    <t>134436971</t>
-  </si>
-  <si>
-    <t>134448454</t>
-  </si>
-  <si>
-    <t>134449468</t>
-  </si>
-  <si>
-    <t>134353741</t>
-  </si>
-  <si>
-    <t>134454888</t>
-  </si>
-  <si>
-    <t>134245350</t>
-  </si>
-  <si>
-    <t>134249359</t>
-  </si>
-  <si>
-    <t>134252813</t>
-  </si>
-  <si>
-    <t>134330660</t>
-  </si>
-  <si>
-    <t>134377006</t>
-  </si>
-  <si>
-    <t>134471200</t>
-  </si>
-  <si>
-    <t>134468222</t>
-  </si>
-  <si>
-    <t>134317364</t>
-  </si>
-  <si>
-    <t>134317561</t>
-  </si>
-  <si>
-    <t>134318813</t>
-  </si>
-  <si>
-    <t>134318850</t>
-  </si>
-  <si>
-    <t>134405509</t>
-  </si>
-  <si>
-    <t>134321004</t>
-  </si>
-  <si>
-    <t>134374065</t>
-  </si>
-  <si>
-    <t>134252750</t>
-  </si>
-  <si>
-    <t>134248978</t>
-  </si>
-  <si>
-    <t>134355878</t>
-  </si>
-  <si>
-    <t>134480253</t>
-  </si>
-  <si>
-    <t>130087031</t>
-  </si>
-  <si>
-    <t>134388053</t>
-  </si>
-  <si>
-    <t>134296334</t>
-  </si>
-  <si>
-    <t>134329184</t>
-  </si>
-  <si>
-    <t>134330700</t>
-  </si>
-  <si>
-    <t>134332669</t>
-  </si>
-  <si>
-    <t>134333015</t>
-  </si>
-  <si>
-    <t>134333758</t>
-  </si>
-  <si>
-    <t>134336539</t>
-  </si>
-  <si>
-    <t>134340054</t>
-  </si>
-  <si>
-    <t>134345466</t>
-  </si>
-  <si>
-    <t>134346112</t>
+    <t>Relatório Recusa _ SICREDI_18.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 18.09.2025</t>
+  </si>
+  <si>
+    <t>134390715</t>
+  </si>
+  <si>
+    <t>134388426</t>
+  </si>
+  <si>
+    <t>134383735</t>
+  </si>
+  <si>
+    <t>134407141</t>
+  </si>
+  <si>
+    <t>134422426</t>
+  </si>
+  <si>
+    <t>134420766</t>
+  </si>
+  <si>
+    <t>134433048</t>
+  </si>
+  <si>
+    <t>134435255</t>
+  </si>
+  <si>
+    <t>134417628</t>
+  </si>
+  <si>
+    <t>134419163</t>
+  </si>
+  <si>
+    <t>134403329</t>
+  </si>
+  <si>
+    <t>134443967</t>
+  </si>
+  <si>
+    <t>134449181</t>
+  </si>
+  <si>
+    <t>134435606</t>
+  </si>
+  <si>
+    <t>134445954</t>
+  </si>
+  <si>
+    <t>134478432</t>
+  </si>
+  <si>
+    <t>134470083</t>
+  </si>
+  <si>
+    <t>134506645</t>
+  </si>
+  <si>
+    <t>134505108</t>
+  </si>
+  <si>
+    <t>134504377</t>
+  </si>
+  <si>
+    <t>134489246</t>
+  </si>
+  <si>
+    <t>134508290</t>
+  </si>
+  <si>
+    <t>134506838</t>
+  </si>
+  <si>
+    <t>134503135</t>
+  </si>
+  <si>
+    <t>134503565</t>
+  </si>
+  <si>
+    <t>134314145</t>
+  </si>
+  <si>
+    <t>134317631</t>
+  </si>
+  <si>
+    <t>133941065</t>
+  </si>
+  <si>
+    <t>134516294</t>
+  </si>
+  <si>
+    <t>134519914</t>
+  </si>
+  <si>
+    <t>134395990</t>
+  </si>
+  <si>
+    <t>134518772</t>
+  </si>
+  <si>
+    <t>134519486</t>
+  </si>
+  <si>
+    <t>132332975</t>
+  </si>
+  <si>
+    <t>134372522</t>
+  </si>
+  <si>
+    <t>134386985</t>
+  </si>
+  <si>
+    <t>134396730</t>
+  </si>
+  <si>
+    <t>134404080</t>
+  </si>
+  <si>
+    <t>134522765</t>
+  </si>
+  <si>
+    <t>134518627</t>
+  </si>
+  <si>
+    <t>134372583</t>
+  </si>
+  <si>
+    <t>134373254</t>
+  </si>
+  <si>
+    <t>134374247</t>
+  </si>
+  <si>
+    <t>134528401</t>
+  </si>
+  <si>
+    <t>134376359</t>
+  </si>
+  <si>
+    <t>134376747</t>
+  </si>
+  <si>
+    <t>134385718</t>
+  </si>
+  <si>
+    <t>134387624</t>
+  </si>
+  <si>
+    <t>134388311</t>
+  </si>
+  <si>
+    <t>134530191</t>
+  </si>
+  <si>
+    <t>134389645</t>
+  </si>
+  <si>
+    <t>134390576</t>
+  </si>
+  <si>
+    <t>134391306</t>
   </si>
 </sst>
 </file>
@@ -606,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -638,13 +653,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134320964</v>
+        <v>130119469</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -656,13 +671,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -674,16 +689,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -691,13 +706,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -708,13 +723,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -725,13 +740,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -742,13 +757,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -759,13 +774,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -776,13 +791,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -793,13 +808,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -810,13 +825,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -827,16 +842,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -844,13 +859,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -861,13 +876,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -878,13 +893,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -895,13 +910,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
@@ -912,13 +927,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -929,13 +944,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -946,13 +961,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -963,13 +978,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -980,13 +995,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -997,13 +1012,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -1014,13 +1029,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -1031,13 +1046,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
@@ -1048,13 +1063,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -1065,13 +1080,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
@@ -1082,16 +1097,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1099,13 +1114,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
@@ -1116,13 +1131,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -1133,13 +1148,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -1150,13 +1165,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -1167,13 +1182,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -1184,13 +1199,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
@@ -1201,13 +1216,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
@@ -1218,13 +1233,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
@@ -1235,13 +1250,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
@@ -1252,13 +1267,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -1269,13 +1284,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -1286,13 +1301,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -1303,13 +1318,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -1320,13 +1335,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -1337,16 +1352,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1354,13 +1369,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -1371,13 +1386,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
@@ -1388,13 +1403,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -1405,13 +1420,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -1422,13 +1437,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
@@ -1439,18 +1454,120 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93A07AE-4746-4CD8-AB98-855D9496E76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D99594A-FCAF-409A-B22F-C32B832248CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,127 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_18.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 18.09.2025</t>
-  </si>
-  <si>
-    <t>134390715</t>
-  </si>
-  <si>
-    <t>134388426</t>
-  </si>
-  <si>
-    <t>134383735</t>
-  </si>
-  <si>
-    <t>134407141</t>
-  </si>
-  <si>
-    <t>134422426</t>
-  </si>
-  <si>
-    <t>134420766</t>
-  </si>
-  <si>
-    <t>134433048</t>
-  </si>
-  <si>
-    <t>134435255</t>
-  </si>
-  <si>
-    <t>134417628</t>
-  </si>
-  <si>
-    <t>134419163</t>
-  </si>
-  <si>
-    <t>134403329</t>
-  </si>
-  <si>
-    <t>134443967</t>
-  </si>
-  <si>
-    <t>134449181</t>
-  </si>
-  <si>
-    <t>134435606</t>
-  </si>
-  <si>
-    <t>134445954</t>
-  </si>
-  <si>
-    <t>134478432</t>
-  </si>
-  <si>
-    <t>134470083</t>
-  </si>
-  <si>
-    <t>134506645</t>
-  </si>
-  <si>
-    <t>134505108</t>
-  </si>
-  <si>
-    <t>134504377</t>
-  </si>
-  <si>
-    <t>134489246</t>
-  </si>
-  <si>
-    <t>134508290</t>
-  </si>
-  <si>
-    <t>134506838</t>
-  </si>
-  <si>
-    <t>134503135</t>
-  </si>
-  <si>
-    <t>134503565</t>
-  </si>
-  <si>
-    <t>134314145</t>
-  </si>
-  <si>
-    <t>134317631</t>
-  </si>
-  <si>
-    <t>133941065</t>
-  </si>
-  <si>
-    <t>134516294</t>
-  </si>
-  <si>
-    <t>134519914</t>
-  </si>
-  <si>
-    <t>134395990</t>
-  </si>
-  <si>
-    <t>134518772</t>
-  </si>
-  <si>
-    <t>134519486</t>
-  </si>
-  <si>
-    <t>132332975</t>
-  </si>
-  <si>
-    <t>134372522</t>
-  </si>
-  <si>
-    <t>134386985</t>
-  </si>
-  <si>
-    <t>134396730</t>
-  </si>
-  <si>
-    <t>134404080</t>
-  </si>
-  <si>
-    <t>134522765</t>
-  </si>
-  <si>
-    <t>134518627</t>
-  </si>
-  <si>
-    <t>134372583</t>
-  </si>
-  <si>
-    <t>134373254</t>
-  </si>
-  <si>
-    <t>134374247</t>
-  </si>
-  <si>
-    <t>134528401</t>
-  </si>
-  <si>
-    <t>134376359</t>
-  </si>
-  <si>
-    <t>134376747</t>
-  </si>
-  <si>
-    <t>134385718</t>
-  </si>
-  <si>
-    <t>134387624</t>
-  </si>
-  <si>
-    <t>134388311</t>
-  </si>
-  <si>
-    <t>134530191</t>
-  </si>
-  <si>
-    <t>134389645</t>
-  </si>
-  <si>
-    <t>134390576</t>
-  </si>
-  <si>
-    <t>134391306</t>
+    <t>Relatório Recusa _ SICREDI_19.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 19/09/2025</t>
+  </si>
+  <si>
+    <t>134406499</t>
+  </si>
+  <si>
+    <t>134408866</t>
+  </si>
+  <si>
+    <t>134409848</t>
+  </si>
+  <si>
+    <t>134411382</t>
+  </si>
+  <si>
+    <t>134435863</t>
+  </si>
+  <si>
+    <t>134427963</t>
+  </si>
+  <si>
+    <t>134452027</t>
+  </si>
+  <si>
+    <t>134451330</t>
+  </si>
+  <si>
+    <t>134452185</t>
+  </si>
+  <si>
+    <t>134453916</t>
+  </si>
+  <si>
+    <t>134450477</t>
+  </si>
+  <si>
+    <t>134447206</t>
+  </si>
+  <si>
+    <t>134505250</t>
+  </si>
+  <si>
+    <t>134506376</t>
+  </si>
+  <si>
+    <t>134511596</t>
+  </si>
+  <si>
+    <t>131738740</t>
+  </si>
+  <si>
+    <t>131995280</t>
+  </si>
+  <si>
+    <t>133459264</t>
+  </si>
+  <si>
+    <t>133958845</t>
+  </si>
+  <si>
+    <t>134398802</t>
+  </si>
+  <si>
+    <t>134404708</t>
+  </si>
+  <si>
+    <t>134401673</t>
+  </si>
+  <si>
+    <t>134410680</t>
+  </si>
+  <si>
+    <t>134406562</t>
+  </si>
+  <si>
+    <t>134406777</t>
+  </si>
+  <si>
+    <t>134409400</t>
+  </si>
+  <si>
+    <t>134410240</t>
+  </si>
+  <si>
+    <t>134411525</t>
+  </si>
+  <si>
+    <t>134412191</t>
+  </si>
+  <si>
+    <t>131690888</t>
+  </si>
+  <si>
+    <t>134412724</t>
+  </si>
+  <si>
+    <t>134546744</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_20.09.2025</t>
+  </si>
+  <si>
+    <t>134496524</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 20/09/2025</t>
+  </si>
+  <si>
+    <t>134419261</t>
+  </si>
+  <si>
+    <t>134339679</t>
+  </si>
+  <si>
+    <t>134338595</t>
+  </si>
+  <si>
+    <t>131906701</t>
   </si>
 </sst>
 </file>
@@ -621,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -653,7 +611,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130119469</v>
+        <v>134412412</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1216,16 +1174,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1233,16 +1191,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1250,16 +1208,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1267,16 +1225,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1284,290 +1242,18 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D99594A-FCAF-409A-B22F-C32B832248CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE4EBD7-852F-4EEB-B805-99E9D183E31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,133 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_19.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 19/09/2025</t>
-  </si>
-  <si>
-    <t>134406499</t>
-  </si>
-  <si>
-    <t>134408866</t>
-  </si>
-  <si>
-    <t>134409848</t>
-  </si>
-  <si>
-    <t>134411382</t>
-  </si>
-  <si>
-    <t>134435863</t>
-  </si>
-  <si>
-    <t>134427963</t>
-  </si>
-  <si>
-    <t>134452027</t>
-  </si>
-  <si>
-    <t>134451330</t>
-  </si>
-  <si>
-    <t>134452185</t>
-  </si>
-  <si>
-    <t>134453916</t>
-  </si>
-  <si>
-    <t>134450477</t>
-  </si>
-  <si>
-    <t>134447206</t>
-  </si>
-  <si>
-    <t>134505250</t>
-  </si>
-  <si>
-    <t>134506376</t>
-  </si>
-  <si>
-    <t>134511596</t>
-  </si>
-  <si>
-    <t>131738740</t>
-  </si>
-  <si>
-    <t>131995280</t>
-  </si>
-  <si>
-    <t>133459264</t>
-  </si>
-  <si>
-    <t>133958845</t>
-  </si>
-  <si>
-    <t>134398802</t>
-  </si>
-  <si>
-    <t>134404708</t>
-  </si>
-  <si>
-    <t>134401673</t>
-  </si>
-  <si>
-    <t>134410680</t>
-  </si>
-  <si>
-    <t>134406562</t>
-  </si>
-  <si>
-    <t>134406777</t>
-  </si>
-  <si>
-    <t>134409400</t>
-  </si>
-  <si>
-    <t>134410240</t>
-  </si>
-  <si>
-    <t>134411525</t>
-  </si>
-  <si>
-    <t>134412191</t>
-  </si>
-  <si>
-    <t>131690888</t>
-  </si>
-  <si>
-    <t>134412724</t>
-  </si>
-  <si>
-    <t>134546744</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_20.09.2025</t>
-  </si>
-  <si>
-    <t>134496524</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 20/09/2025</t>
-  </si>
-  <si>
-    <t>134419261</t>
-  </si>
-  <si>
-    <t>134339679</t>
-  </si>
-  <si>
-    <t>134338595</t>
-  </si>
-  <si>
-    <t>131906701</t>
+    <t>Relatório Recusa _ SICREDI_22.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 22.09.2025</t>
+  </si>
+  <si>
+    <t>129796964</t>
+  </si>
+  <si>
+    <t>132044921</t>
+  </si>
+  <si>
+    <t>133791922</t>
+  </si>
+  <si>
+    <t>134435905</t>
+  </si>
+  <si>
+    <t>134432721</t>
+  </si>
+  <si>
+    <t>134435078</t>
+  </si>
+  <si>
+    <t>134455151</t>
+  </si>
+  <si>
+    <t>134445517</t>
+  </si>
+  <si>
+    <t>134456444</t>
+  </si>
+  <si>
+    <t>134478392</t>
+  </si>
+  <si>
+    <t>134481663</t>
+  </si>
+  <si>
+    <t>134493856</t>
+  </si>
+  <si>
+    <t>134504024</t>
+  </si>
+  <si>
+    <t>134503717</t>
+  </si>
+  <si>
+    <t>134518314</t>
+  </si>
+  <si>
+    <t>134520337</t>
+  </si>
+  <si>
+    <t>134518875</t>
+  </si>
+  <si>
+    <t>134535002</t>
+  </si>
+  <si>
+    <t>134538788</t>
+  </si>
+  <si>
+    <t>134539233</t>
+  </si>
+  <si>
+    <t>134547702</t>
+  </si>
+  <si>
+    <t>134554105</t>
+  </si>
+  <si>
+    <t>134544840</t>
+  </si>
+  <si>
+    <t>134366741</t>
+  </si>
+  <si>
+    <t>134453549</t>
+  </si>
+  <si>
+    <t>134457410</t>
+  </si>
+  <si>
+    <t>130906729</t>
+  </si>
+  <si>
+    <t>134424760</t>
+  </si>
+  <si>
+    <t>134434173</t>
+  </si>
+  <si>
+    <t>131796536</t>
+  </si>
+  <si>
+    <t>131943913</t>
+  </si>
+  <si>
+    <t>134418389</t>
+  </si>
+  <si>
+    <t>134421367</t>
+  </si>
+  <si>
+    <t>134424870</t>
+  </si>
+  <si>
+    <t>134428264</t>
+  </si>
+  <si>
+    <t>134430325</t>
+  </si>
+  <si>
+    <t>132584836</t>
+  </si>
+  <si>
+    <t>134437422</t>
+  </si>
+  <si>
+    <t>134515205</t>
+  </si>
+  <si>
+    <t>134408483</t>
+  </si>
+  <si>
+    <t>134455381</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -611,7 +617,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134412412</v>
+        <v>130505601</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1174,16 +1180,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1191,16 +1197,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1208,16 +1214,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1225,16 +1231,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1242,18 +1248,86 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE4EBD7-852F-4EEB-B805-99E9D183E31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F990F90C-D178-4A58-81F6-3F7EE8B81221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,115 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_22.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 22.09.2025</t>
-  </si>
-  <si>
-    <t>129796964</t>
-  </si>
-  <si>
-    <t>132044921</t>
-  </si>
-  <si>
-    <t>133791922</t>
-  </si>
-  <si>
-    <t>134435905</t>
-  </si>
-  <si>
-    <t>134432721</t>
-  </si>
-  <si>
-    <t>134435078</t>
-  </si>
-  <si>
-    <t>134455151</t>
-  </si>
-  <si>
-    <t>134445517</t>
-  </si>
-  <si>
-    <t>134456444</t>
-  </si>
-  <si>
-    <t>134478392</t>
-  </si>
-  <si>
-    <t>134481663</t>
-  </si>
-  <si>
-    <t>134493856</t>
-  </si>
-  <si>
-    <t>134504024</t>
-  </si>
-  <si>
-    <t>134503717</t>
-  </si>
-  <si>
-    <t>134518314</t>
-  </si>
-  <si>
-    <t>134520337</t>
-  </si>
-  <si>
-    <t>134518875</t>
-  </si>
-  <si>
-    <t>134535002</t>
-  </si>
-  <si>
-    <t>134538788</t>
-  </si>
-  <si>
-    <t>134539233</t>
-  </si>
-  <si>
-    <t>134547702</t>
-  </si>
-  <si>
-    <t>134554105</t>
-  </si>
-  <si>
-    <t>134544840</t>
-  </si>
-  <si>
-    <t>134366741</t>
-  </si>
-  <si>
-    <t>134453549</t>
-  </si>
-  <si>
-    <t>134457410</t>
-  </si>
-  <si>
-    <t>130906729</t>
-  </si>
-  <si>
-    <t>134424760</t>
-  </si>
-  <si>
-    <t>134434173</t>
-  </si>
-  <si>
-    <t>131796536</t>
-  </si>
-  <si>
-    <t>131943913</t>
-  </si>
-  <si>
-    <t>134418389</t>
-  </si>
-  <si>
-    <t>134421367</t>
-  </si>
-  <si>
-    <t>134424870</t>
-  </si>
-  <si>
-    <t>134428264</t>
-  </si>
-  <si>
-    <t>134430325</t>
-  </si>
-  <si>
-    <t>132584836</t>
-  </si>
-  <si>
-    <t>134437422</t>
-  </si>
-  <si>
-    <t>134515205</t>
-  </si>
-  <si>
-    <t>134408483</t>
-  </si>
-  <si>
-    <t>134455381</t>
+    <t>Relatório Recusa _ SICREDI_23.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 23.09.2025</t>
+  </si>
+  <si>
+    <t>134504409</t>
+  </si>
+  <si>
+    <t>134506482</t>
+  </si>
+  <si>
+    <t>134504475</t>
+  </si>
+  <si>
+    <t>134504676</t>
+  </si>
+  <si>
+    <t>134536174</t>
+  </si>
+  <si>
+    <t>134539018</t>
+  </si>
+  <si>
+    <t>134555163</t>
+  </si>
+  <si>
+    <t>134568900</t>
+  </si>
+  <si>
+    <t>134472195</t>
+  </si>
+  <si>
+    <t>134578449</t>
+  </si>
+  <si>
+    <t>134577723</t>
+  </si>
+  <si>
+    <t>134565228</t>
+  </si>
+  <si>
+    <t>134571760</t>
+  </si>
+  <si>
+    <t>134357752</t>
+  </si>
+  <si>
+    <t>134357935</t>
+  </si>
+  <si>
+    <t>134388927</t>
+  </si>
+  <si>
+    <t>134580606</t>
+  </si>
+  <si>
+    <t>134589790</t>
+  </si>
+  <si>
+    <t>134482541</t>
+  </si>
+  <si>
+    <t>134445813</t>
+  </si>
+  <si>
+    <t>134444701</t>
+  </si>
+  <si>
+    <t>134447383</t>
+  </si>
+  <si>
+    <t>134450174</t>
+  </si>
+  <si>
+    <t>134451753</t>
+  </si>
+  <si>
+    <t>134452714</t>
+  </si>
+  <si>
+    <t>134453854</t>
+  </si>
+  <si>
+    <t>134456023</t>
+  </si>
+  <si>
+    <t>134458744</t>
+  </si>
+  <si>
+    <t>134459292</t>
+  </si>
+  <si>
+    <t>134460323</t>
+  </si>
+  <si>
+    <t>134461002</t>
+  </si>
+  <si>
+    <t>134461325</t>
+  </si>
+  <si>
+    <t>134601632</t>
+  </si>
+  <si>
+    <t>134502383</t>
+  </si>
+  <si>
+    <t>134363501</t>
   </si>
 </sst>
 </file>
@@ -585,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,7 +599,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130505601</v>
+        <v>134446864</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1226,108 +1208,6 @@
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F990F90C-D178-4A58-81F6-3F7EE8B81221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03DD2A7-BE88-48DC-91CA-C93F3EBD9F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,115 +54,163 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_23.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 23.09.2025</t>
-  </si>
-  <si>
-    <t>134504409</t>
-  </si>
-  <si>
-    <t>134506482</t>
-  </si>
-  <si>
-    <t>134504475</t>
-  </si>
-  <si>
-    <t>134504676</t>
-  </si>
-  <si>
-    <t>134536174</t>
-  </si>
-  <si>
-    <t>134539018</t>
-  </si>
-  <si>
-    <t>134555163</t>
-  </si>
-  <si>
-    <t>134568900</t>
-  </si>
-  <si>
-    <t>134472195</t>
-  </si>
-  <si>
-    <t>134578449</t>
-  </si>
-  <si>
-    <t>134577723</t>
-  </si>
-  <si>
-    <t>134565228</t>
-  </si>
-  <si>
-    <t>134571760</t>
-  </si>
-  <si>
-    <t>134357752</t>
-  </si>
-  <si>
-    <t>134357935</t>
-  </si>
-  <si>
-    <t>134388927</t>
-  </si>
-  <si>
-    <t>134580606</t>
-  </si>
-  <si>
-    <t>134589790</t>
-  </si>
-  <si>
-    <t>134482541</t>
-  </si>
-  <si>
-    <t>134445813</t>
-  </si>
-  <si>
-    <t>134444701</t>
-  </si>
-  <si>
-    <t>134447383</t>
-  </si>
-  <si>
-    <t>134450174</t>
-  </si>
-  <si>
-    <t>134451753</t>
-  </si>
-  <si>
-    <t>134452714</t>
-  </si>
-  <si>
-    <t>134453854</t>
-  </si>
-  <si>
-    <t>134456023</t>
-  </si>
-  <si>
-    <t>134458744</t>
-  </si>
-  <si>
-    <t>134459292</t>
-  </si>
-  <si>
-    <t>134460323</t>
-  </si>
-  <si>
-    <t>134461002</t>
-  </si>
-  <si>
-    <t>134461325</t>
-  </si>
-  <si>
-    <t>134601632</t>
-  </si>
-  <si>
-    <t>134502383</t>
-  </si>
-  <si>
-    <t>134363501</t>
+    <t>Relatório Recusa _ SICREDI_24.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 24.09.2025</t>
+  </si>
+  <si>
+    <t>134387957</t>
+  </si>
+  <si>
+    <t>134417808</t>
+  </si>
+  <si>
+    <t>134465483</t>
+  </si>
+  <si>
+    <t>134473463</t>
+  </si>
+  <si>
+    <t>134480548</t>
+  </si>
+  <si>
+    <t>134468506</t>
+  </si>
+  <si>
+    <t>134466008</t>
+  </si>
+  <si>
+    <t>134492086</t>
+  </si>
+  <si>
+    <t>134498824</t>
+  </si>
+  <si>
+    <t>134509343</t>
+  </si>
+  <si>
+    <t>134502754</t>
+  </si>
+  <si>
+    <t>134523297</t>
+  </si>
+  <si>
+    <t>134528892</t>
+  </si>
+  <si>
+    <t>134539681</t>
+  </si>
+  <si>
+    <t>134578421</t>
+  </si>
+  <si>
+    <t>134585253</t>
+  </si>
+  <si>
+    <t>134585061</t>
+  </si>
+  <si>
+    <t>134447517</t>
+  </si>
+  <si>
+    <t>134602421</t>
+  </si>
+  <si>
+    <t>134383696</t>
+  </si>
+  <si>
+    <t>134388315</t>
+  </si>
+  <si>
+    <t>132540767</t>
+  </si>
+  <si>
+    <t>134497646</t>
+  </si>
+  <si>
+    <t>131257636</t>
+  </si>
+  <si>
+    <t>134399119</t>
+  </si>
+  <si>
+    <t>134406346</t>
+  </si>
+  <si>
+    <t>134410173</t>
+  </si>
+  <si>
+    <t>134482648</t>
+  </si>
+  <si>
+    <t>134519216</t>
+  </si>
+  <si>
+    <t>134421136</t>
+  </si>
+  <si>
+    <t>134519263</t>
+  </si>
+  <si>
+    <t>134467844</t>
+  </si>
+  <si>
+    <t>134470210</t>
+  </si>
+  <si>
+    <t>134471308</t>
+  </si>
+  <si>
+    <t>134471695</t>
+  </si>
+  <si>
+    <t>134473447</t>
+  </si>
+  <si>
+    <t>134473614</t>
+  </si>
+  <si>
+    <t>134474264</t>
+  </si>
+  <si>
+    <t>134475752</t>
+  </si>
+  <si>
+    <t>134476331</t>
+  </si>
+  <si>
+    <t>134478265</t>
+  </si>
+  <si>
+    <t>134478856</t>
+  </si>
+  <si>
+    <t>134479869</t>
+  </si>
+  <si>
+    <t>134480995</t>
+  </si>
+  <si>
+    <t>134619523</t>
+  </si>
+  <si>
+    <t>133708268</t>
+  </si>
+  <si>
+    <t>134433746</t>
+  </si>
+  <si>
+    <t>134460934</t>
+  </si>
+  <si>
+    <t>134409671</t>
+  </si>
+  <si>
+    <t>134625312</t>
+  </si>
+  <si>
+    <t>134625618</t>
   </si>
 </sst>
 </file>
@@ -567,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -599,7 +647,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134446864</v>
+        <v>134386198</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1208,6 +1256,278 @@
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03DD2A7-BE88-48DC-91CA-C93F3EBD9F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E9D431-938F-4217-B522-71D85E690B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,163 +54,169 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_24.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 24.09.2025</t>
-  </si>
-  <si>
-    <t>134387957</t>
-  </si>
-  <si>
-    <t>134417808</t>
-  </si>
-  <si>
-    <t>134465483</t>
-  </si>
-  <si>
-    <t>134473463</t>
-  </si>
-  <si>
-    <t>134480548</t>
-  </si>
-  <si>
-    <t>134468506</t>
-  </si>
-  <si>
-    <t>134466008</t>
-  </si>
-  <si>
-    <t>134492086</t>
-  </si>
-  <si>
-    <t>134498824</t>
-  </si>
-  <si>
-    <t>134509343</t>
-  </si>
-  <si>
-    <t>134502754</t>
-  </si>
-  <si>
-    <t>134523297</t>
-  </si>
-  <si>
-    <t>134528892</t>
-  </si>
-  <si>
-    <t>134539681</t>
-  </si>
-  <si>
-    <t>134578421</t>
-  </si>
-  <si>
-    <t>134585253</t>
-  </si>
-  <si>
-    <t>134585061</t>
-  </si>
-  <si>
-    <t>134447517</t>
-  </si>
-  <si>
-    <t>134602421</t>
-  </si>
-  <si>
-    <t>134383696</t>
-  </si>
-  <si>
-    <t>134388315</t>
-  </si>
-  <si>
-    <t>132540767</t>
-  </si>
-  <si>
-    <t>134497646</t>
-  </si>
-  <si>
     <t>131257636</t>
   </si>
   <si>
-    <t>134399119</t>
-  </si>
-  <si>
-    <t>134406346</t>
-  </si>
-  <si>
-    <t>134410173</t>
-  </si>
-  <si>
-    <t>134482648</t>
-  </si>
-  <si>
-    <t>134519216</t>
-  </si>
-  <si>
-    <t>134421136</t>
-  </si>
-  <si>
-    <t>134519263</t>
-  </si>
-  <si>
-    <t>134467844</t>
-  </si>
-  <si>
-    <t>134470210</t>
-  </si>
-  <si>
-    <t>134471308</t>
-  </si>
-  <si>
-    <t>134471695</t>
-  </si>
-  <si>
-    <t>134473447</t>
-  </si>
-  <si>
-    <t>134473614</t>
-  </si>
-  <si>
-    <t>134474264</t>
-  </si>
-  <si>
-    <t>134475752</t>
-  </si>
-  <si>
-    <t>134476331</t>
-  </si>
-  <si>
-    <t>134478265</t>
-  </si>
-  <si>
-    <t>134478856</t>
-  </si>
-  <si>
-    <t>134479869</t>
-  </si>
-  <si>
-    <t>134480995</t>
-  </si>
-  <si>
-    <t>134619523</t>
-  </si>
-  <si>
-    <t>133708268</t>
-  </si>
-  <si>
-    <t>134433746</t>
-  </si>
-  <si>
-    <t>134460934</t>
-  </si>
-  <si>
-    <t>134409671</t>
-  </si>
-  <si>
-    <t>134625312</t>
-  </si>
-  <si>
-    <t>134625618</t>
+    <t>Relatório de Recusa Sicredi 06/10/2025</t>
+  </si>
+  <si>
+    <t>134658580</t>
+  </si>
+  <si>
+    <t>134661512</t>
+  </si>
+  <si>
+    <t>134666693</t>
+  </si>
+  <si>
+    <t>134664036</t>
+  </si>
+  <si>
+    <t>134665589</t>
+  </si>
+  <si>
+    <t>134669761</t>
+  </si>
+  <si>
+    <t>134652326</t>
+  </si>
+  <si>
+    <t>134670309</t>
+  </si>
+  <si>
+    <t>134662718</t>
+  </si>
+  <si>
+    <t>134669526</t>
+  </si>
+  <si>
+    <t>134688483</t>
+  </si>
+  <si>
+    <t>134703946</t>
+  </si>
+  <si>
+    <t>134655842</t>
+  </si>
+  <si>
+    <t>134663893</t>
+  </si>
+  <si>
+    <t>131154405</t>
+  </si>
+  <si>
+    <t>134659727</t>
+  </si>
+  <si>
+    <t>134749354</t>
+  </si>
+  <si>
+    <t>134768193</t>
+  </si>
+  <si>
+    <t>134782820</t>
+  </si>
+  <si>
+    <t>134595759</t>
+  </si>
+  <si>
+    <t>134666738</t>
+  </si>
+  <si>
+    <t>134790804</t>
+  </si>
+  <si>
+    <t>134653547</t>
+  </si>
+  <si>
+    <t>134790957</t>
+  </si>
+  <si>
+    <t>134622809</t>
+  </si>
+  <si>
+    <t>134791195</t>
+  </si>
+  <si>
+    <t>134684140</t>
+  </si>
+  <si>
+    <t>134797260</t>
+  </si>
+  <si>
+    <t>134688473</t>
+  </si>
+  <si>
+    <t>134797102</t>
+  </si>
+  <si>
+    <t>134712014</t>
+  </si>
+  <si>
+    <t>134801904</t>
+  </si>
+  <si>
+    <t>134803095</t>
+  </si>
+  <si>
+    <t>134613569</t>
+  </si>
+  <si>
+    <t>131446406</t>
+  </si>
+  <si>
+    <t>132359571</t>
+  </si>
+  <si>
+    <t>134655702</t>
+  </si>
+  <si>
+    <t>134657108</t>
+  </si>
+  <si>
+    <t>134658853</t>
+  </si>
+  <si>
+    <t>134659151</t>
+  </si>
+  <si>
+    <t>134659397</t>
+  </si>
+  <si>
+    <t>134660110</t>
+  </si>
+  <si>
+    <t>134662791</t>
+  </si>
+  <si>
+    <t>134666521</t>
+  </si>
+  <si>
+    <t>134666586</t>
+  </si>
+  <si>
+    <t>134666893</t>
+  </si>
+  <si>
+    <t>134668406</t>
+  </si>
+  <si>
+    <t>134668899</t>
+  </si>
+  <si>
+    <t>134668970</t>
+  </si>
+  <si>
+    <t>134669666</t>
+  </si>
+  <si>
+    <t>134670561</t>
+  </si>
+  <si>
+    <t>134564973</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -615,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -647,7 +653,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134386198</v>
+        <v>134598702</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -656,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -674,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -692,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -709,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -726,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -743,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -760,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -777,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -794,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -811,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -828,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -845,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -862,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -879,7 +885,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -896,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -913,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -930,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -947,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -964,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -981,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -998,7 +1004,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1015,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1023,7 +1029,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1032,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1046,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1049,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1057,7 +1063,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1066,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1074,7 +1080,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1083,7 +1089,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1097,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1100,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1108,7 +1114,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1117,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1125,7 +1131,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1134,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1148,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1151,7 +1157,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1159,7 +1165,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1168,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1176,7 +1182,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1185,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1199,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1202,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1210,7 +1216,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1219,7 +1225,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1227,7 +1233,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1236,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1244,7 +1250,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1253,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1261,7 +1267,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1270,7 +1276,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1278,7 +1284,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1287,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1295,7 +1301,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1304,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1312,7 +1318,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1321,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1329,7 +1335,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -1338,7 +1344,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1346,7 +1352,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1355,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1363,7 +1369,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -1372,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1380,7 +1386,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
@@ -1389,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1397,7 +1403,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
@@ -1406,7 +1412,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1414,7 +1420,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
@@ -1423,7 +1429,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1431,7 +1437,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -1440,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1448,7 +1454,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
@@ -1457,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1465,7 +1471,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
@@ -1474,7 +1480,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1482,7 +1488,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
@@ -1491,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1499,7 +1505,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
@@ -1508,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1516,18 +1522,52 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1545,31 +1585,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E9D431-938F-4217-B522-71D85E690B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A32ED-1833-4365-9944-6C5B2AECDB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1585,31 +1585,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A32ED-1833-4365-9944-6C5B2AECDB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46667D85-717C-4C2B-95E6-45ADE586B7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,139 @@
     <t>971</t>
   </si>
   <si>
-    <t>131257636</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 06/10/2025</t>
-  </si>
-  <si>
-    <t>134658580</t>
-  </si>
-  <si>
-    <t>134661512</t>
-  </si>
-  <si>
-    <t>134666693</t>
-  </si>
-  <si>
-    <t>134664036</t>
-  </si>
-  <si>
-    <t>134665589</t>
-  </si>
-  <si>
-    <t>134669761</t>
-  </si>
-  <si>
-    <t>134652326</t>
-  </si>
-  <si>
-    <t>134670309</t>
-  </si>
-  <si>
-    <t>134662718</t>
-  </si>
-  <si>
-    <t>134669526</t>
-  </si>
-  <si>
-    <t>134688483</t>
-  </si>
-  <si>
-    <t>134703946</t>
-  </si>
-  <si>
-    <t>134655842</t>
-  </si>
-  <si>
-    <t>134663893</t>
-  </si>
-  <si>
-    <t>131154405</t>
-  </si>
-  <si>
-    <t>134659727</t>
-  </si>
-  <si>
-    <t>134749354</t>
-  </si>
-  <si>
-    <t>134768193</t>
-  </si>
-  <si>
-    <t>134782820</t>
-  </si>
-  <si>
-    <t>134595759</t>
-  </si>
-  <si>
-    <t>134666738</t>
-  </si>
-  <si>
-    <t>134790804</t>
-  </si>
-  <si>
-    <t>134653547</t>
-  </si>
-  <si>
-    <t>134790957</t>
-  </si>
-  <si>
-    <t>134622809</t>
-  </si>
-  <si>
-    <t>134791195</t>
-  </si>
-  <si>
-    <t>134684140</t>
-  </si>
-  <si>
-    <t>134797260</t>
-  </si>
-  <si>
-    <t>134688473</t>
-  </si>
-  <si>
-    <t>134797102</t>
-  </si>
-  <si>
-    <t>134712014</t>
-  </si>
-  <si>
-    <t>134801904</t>
-  </si>
-  <si>
-    <t>134803095</t>
-  </si>
-  <si>
-    <t>134613569</t>
-  </si>
-  <si>
-    <t>131446406</t>
-  </si>
-  <si>
-    <t>132359571</t>
-  </si>
-  <si>
-    <t>134655702</t>
-  </si>
-  <si>
-    <t>134657108</t>
-  </si>
-  <si>
-    <t>134658853</t>
-  </si>
-  <si>
-    <t>134659151</t>
-  </si>
-  <si>
-    <t>134659397</t>
-  </si>
-  <si>
-    <t>134660110</t>
-  </si>
-  <si>
-    <t>134662791</t>
-  </si>
-  <si>
-    <t>134666521</t>
-  </si>
-  <si>
-    <t>134666586</t>
-  </si>
-  <si>
-    <t>134666893</t>
-  </si>
-  <si>
-    <t>134668406</t>
-  </si>
-  <si>
-    <t>134668899</t>
-  </si>
-  <si>
-    <t>134668970</t>
-  </si>
-  <si>
-    <t>134669666</t>
-  </si>
-  <si>
-    <t>134670561</t>
-  </si>
-  <si>
-    <t>134564973</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_06.10.2025</t>
+    <t>Relatório de Recusa Sicredi 07.10.2025</t>
+  </si>
+  <si>
+    <t>134642886</t>
+  </si>
+  <si>
+    <t>134641046</t>
+  </si>
+  <si>
+    <t>134688811</t>
+  </si>
+  <si>
+    <t>134680931</t>
+  </si>
+  <si>
+    <t>134687631</t>
+  </si>
+  <si>
+    <t>134676441</t>
+  </si>
+  <si>
+    <t>134701227</t>
+  </si>
+  <si>
+    <t>134709794</t>
+  </si>
+  <si>
+    <t>134727838</t>
+  </si>
+  <si>
+    <t>134730351</t>
+  </si>
+  <si>
+    <t>134687019</t>
+  </si>
+  <si>
+    <t>134720477</t>
+  </si>
+  <si>
+    <t>134736438</t>
+  </si>
+  <si>
+    <t>133459264</t>
+  </si>
+  <si>
+    <t>134729011</t>
+  </si>
+  <si>
+    <t>132024777</t>
+  </si>
+  <si>
+    <t>134746278</t>
+  </si>
+  <si>
+    <t>134743900</t>
+  </si>
+  <si>
+    <t>134798865</t>
+  </si>
+  <si>
+    <t>134613766</t>
+  </si>
+  <si>
+    <t>134705453</t>
+  </si>
+  <si>
+    <t>134812696</t>
+  </si>
+  <si>
+    <t>134709599</t>
+  </si>
+  <si>
+    <t>134633186</t>
+  </si>
+  <si>
+    <t>133628000</t>
+  </si>
+  <si>
+    <t>131001194</t>
+  </si>
+  <si>
+    <t>134676833</t>
+  </si>
+  <si>
+    <t>134678211</t>
+  </si>
+  <si>
+    <t>134679980</t>
+  </si>
+  <si>
+    <t>134681499</t>
+  </si>
+  <si>
+    <t>134640631</t>
+  </si>
+  <si>
+    <t>134685008</t>
+  </si>
+  <si>
+    <t>134685182</t>
+  </si>
+  <si>
+    <t>134686673</t>
+  </si>
+  <si>
+    <t>134687260</t>
+  </si>
+  <si>
+    <t>134711871</t>
+  </si>
+  <si>
+    <t>134691112</t>
+  </si>
+  <si>
+    <t>134693022</t>
+  </si>
+  <si>
+    <t>134698912</t>
+  </si>
+  <si>
+    <t>134708575</t>
+  </si>
+  <si>
+    <t>134826085</t>
+  </si>
+  <si>
+    <t>134727327</t>
+  </si>
+  <si>
+    <t>134712114</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_07.10.2025</t>
   </si>
 </sst>
 </file>
@@ -621,7 +591,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -653,16 +623,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134598702</v>
+        <v>134586308</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -671,16 +641,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -689,16 +659,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -706,16 +676,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -723,16 +693,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -740,16 +710,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -757,16 +727,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -774,16 +744,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -791,16 +761,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -808,16 +778,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -825,16 +795,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -842,16 +812,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -859,16 +829,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -876,16 +846,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -893,16 +863,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -910,16 +880,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -927,16 +897,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -944,16 +914,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -961,16 +931,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -978,16 +948,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -995,16 +965,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1012,16 +982,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1029,16 +999,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1052,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1069,10 +1039,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1086,10 +1056,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1103,10 +1073,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1120,10 +1090,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1137,10 +1107,10 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1154,10 +1124,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1171,10 +1141,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1188,10 +1158,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1205,10 +1175,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1222,10 +1192,10 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1239,10 +1209,10 @@
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1256,10 +1226,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1273,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1290,10 +1260,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1307,10 +1277,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1324,10 +1294,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1341,10 +1311,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1358,10 +1328,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1375,10 +1345,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1392,182 +1362,12 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1585,31 +1385,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46667D85-717C-4C2B-95E6-45ADE586B7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD07D0C6-F07C-4CB8-BCA2-AC79B39931A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1385,31 +1385,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD07D0C6-F07C-4CB8-BCA2-AC79B39931A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8D2F10-6ADA-4023-AF9B-3B9BECC29B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,139 +54,142 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 07.10.2025</t>
-  </si>
-  <si>
-    <t>134642886</t>
-  </si>
-  <si>
-    <t>134641046</t>
-  </si>
-  <si>
-    <t>134688811</t>
-  </si>
-  <si>
-    <t>134680931</t>
-  </si>
-  <si>
-    <t>134687631</t>
-  </si>
-  <si>
-    <t>134676441</t>
-  </si>
-  <si>
-    <t>134701227</t>
-  </si>
-  <si>
-    <t>134709794</t>
-  </si>
-  <si>
-    <t>134727838</t>
-  </si>
-  <si>
-    <t>134730351</t>
-  </si>
-  <si>
-    <t>134687019</t>
-  </si>
-  <si>
-    <t>134720477</t>
-  </si>
-  <si>
-    <t>134736438</t>
-  </si>
-  <si>
-    <t>133459264</t>
-  </si>
-  <si>
-    <t>134729011</t>
-  </si>
-  <si>
-    <t>132024777</t>
-  </si>
-  <si>
-    <t>134746278</t>
-  </si>
-  <si>
-    <t>134743900</t>
-  </si>
-  <si>
-    <t>134798865</t>
-  </si>
-  <si>
-    <t>134613766</t>
-  </si>
-  <si>
-    <t>134705453</t>
-  </si>
-  <si>
-    <t>134812696</t>
-  </si>
-  <si>
-    <t>134709599</t>
-  </si>
-  <si>
-    <t>134633186</t>
-  </si>
-  <si>
-    <t>133628000</t>
-  </si>
-  <si>
-    <t>131001194</t>
-  </si>
-  <si>
-    <t>134676833</t>
-  </si>
-  <si>
-    <t>134678211</t>
-  </si>
-  <si>
-    <t>134679980</t>
-  </si>
-  <si>
-    <t>134681499</t>
-  </si>
-  <si>
-    <t>134640631</t>
-  </si>
-  <si>
-    <t>134685008</t>
-  </si>
-  <si>
-    <t>134685182</t>
-  </si>
-  <si>
-    <t>134686673</t>
-  </si>
-  <si>
-    <t>134687260</t>
-  </si>
-  <si>
-    <t>134711871</t>
-  </si>
-  <si>
-    <t>134691112</t>
-  </si>
-  <si>
-    <t>134693022</t>
-  </si>
-  <si>
-    <t>134698912</t>
-  </si>
-  <si>
-    <t>134708575</t>
-  </si>
-  <si>
-    <t>134826085</t>
-  </si>
-  <si>
-    <t>134727327</t>
-  </si>
-  <si>
-    <t>134712114</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_07.10.2025</t>
+    <t>Relatório de Recusa Sicredi 08.10.2025</t>
+  </si>
+  <si>
+    <t>134705178</t>
+  </si>
+  <si>
+    <t>134623454</t>
+  </si>
+  <si>
+    <t>134734383</t>
+  </si>
+  <si>
+    <t>134755693</t>
+  </si>
+  <si>
+    <t>134744812</t>
+  </si>
+  <si>
+    <t>134755620</t>
+  </si>
+  <si>
+    <t>134724250</t>
+  </si>
+  <si>
+    <t>134752855</t>
+  </si>
+  <si>
+    <t>134764475</t>
+  </si>
+  <si>
+    <t>134749365</t>
+  </si>
+  <si>
+    <t>134773517</t>
+  </si>
+  <si>
+    <t>134741747</t>
+  </si>
+  <si>
+    <t>134774182</t>
+  </si>
+  <si>
+    <t>134783404</t>
+  </si>
+  <si>
+    <t>134771323</t>
+  </si>
+  <si>
+    <t>134781296</t>
+  </si>
+  <si>
+    <t>134791606</t>
+  </si>
+  <si>
+    <t>134801591</t>
+  </si>
+  <si>
+    <t>134811721</t>
+  </si>
+  <si>
+    <t>134823333</t>
+  </si>
+  <si>
+    <t>134803175</t>
+  </si>
+  <si>
+    <t>134621560</t>
+  </si>
+  <si>
+    <t>134705214</t>
+  </si>
+  <si>
+    <t>134833443</t>
+  </si>
+  <si>
+    <t>134700922</t>
+  </si>
+  <si>
+    <t>134837350</t>
+  </si>
+  <si>
+    <t>134796037</t>
+  </si>
+  <si>
+    <t>134831548</t>
+  </si>
+  <si>
+    <t>134839691</t>
+  </si>
+  <si>
+    <t>134835509</t>
+  </si>
+  <si>
+    <t>134430025</t>
+  </si>
+  <si>
+    <t>134842451</t>
+  </si>
+  <si>
+    <t>134726893</t>
+  </si>
+  <si>
+    <t>134663300</t>
+  </si>
+  <si>
+    <t>134843348</t>
+  </si>
+  <si>
+    <t>134698048</t>
+  </si>
+  <si>
+    <t>134830251</t>
+  </si>
+  <si>
+    <t>134724690</t>
+  </si>
+  <si>
+    <t>134836020</t>
+  </si>
+  <si>
+    <t>134842216</t>
+  </si>
+  <si>
+    <t>134815842</t>
+  </si>
+  <si>
+    <t>134715172</t>
+  </si>
+  <si>
+    <t>134703911</t>
+  </si>
+  <si>
+    <t>133453537</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_08.10.2025</t>
   </si>
 </sst>
 </file>
@@ -591,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -623,7 +626,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134586308</v>
+        <v>134619898</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -632,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -650,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -668,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -685,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -702,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -719,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -736,7 +739,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -753,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -770,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -787,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -804,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -838,7 +841,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -855,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -889,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -906,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -923,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -940,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -957,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -974,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -991,7 +994,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1008,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1025,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1042,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1059,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1093,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1110,7 +1113,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1144,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1161,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1178,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1195,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1212,7 +1215,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1229,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1246,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1263,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1280,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1297,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1314,7 +1317,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1331,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1348,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1365,10 +1368,32 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1048576" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1048576" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1385,31 +1410,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8D2F10-6ADA-4023-AF9B-3B9BECC29B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A8A05D-A1D2-4FCC-8EDD-0D358914DA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="93">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,142 +54,259 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 08.10.2025</t>
-  </si>
-  <si>
-    <t>134705178</t>
-  </si>
-  <si>
-    <t>134623454</t>
-  </si>
-  <si>
-    <t>134734383</t>
-  </si>
-  <si>
-    <t>134755693</t>
-  </si>
-  <si>
-    <t>134744812</t>
-  </si>
-  <si>
-    <t>134755620</t>
-  </si>
-  <si>
-    <t>134724250</t>
-  </si>
-  <si>
-    <t>134752855</t>
-  </si>
-  <si>
-    <t>134764475</t>
-  </si>
-  <si>
-    <t>134749365</t>
-  </si>
-  <si>
-    <t>134773517</t>
-  </si>
-  <si>
-    <t>134741747</t>
-  </si>
-  <si>
-    <t>134774182</t>
-  </si>
-  <si>
-    <t>134783404</t>
-  </si>
-  <si>
-    <t>134771323</t>
-  </si>
-  <si>
-    <t>134781296</t>
-  </si>
-  <si>
-    <t>134791606</t>
-  </si>
-  <si>
-    <t>134801591</t>
-  </si>
-  <si>
-    <t>134811721</t>
-  </si>
-  <si>
-    <t>134823333</t>
-  </si>
-  <si>
-    <t>134803175</t>
-  </si>
-  <si>
-    <t>134621560</t>
-  </si>
-  <si>
-    <t>134705214</t>
-  </si>
-  <si>
-    <t>134833443</t>
-  </si>
-  <si>
-    <t>134700922</t>
-  </si>
-  <si>
-    <t>134837350</t>
-  </si>
-  <si>
-    <t>134796037</t>
-  </si>
-  <si>
-    <t>134831548</t>
-  </si>
-  <si>
-    <t>134839691</t>
-  </si>
-  <si>
-    <t>134835509</t>
-  </si>
-  <si>
-    <t>134430025</t>
-  </si>
-  <si>
-    <t>134842451</t>
-  </si>
-  <si>
-    <t>134726893</t>
-  </si>
-  <si>
-    <t>134663300</t>
-  </si>
-  <si>
-    <t>134843348</t>
-  </si>
-  <si>
-    <t>134698048</t>
-  </si>
-  <si>
-    <t>134830251</t>
-  </si>
-  <si>
-    <t>134724690</t>
-  </si>
-  <si>
-    <t>134836020</t>
-  </si>
-  <si>
-    <t>134842216</t>
-  </si>
-  <si>
-    <t>134815842</t>
-  </si>
-  <si>
-    <t>134715172</t>
-  </si>
-  <si>
-    <t>134703911</t>
-  </si>
-  <si>
-    <t>133453537</t>
-  </si>
-  <si>
     <t>Relatório Recusa _ SICREDI_08.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 09.10.2025</t>
+  </si>
+  <si>
+    <t>134709632</t>
+  </si>
+  <si>
+    <t>134703023</t>
+  </si>
+  <si>
+    <t>130930621</t>
+  </si>
+  <si>
+    <t>134718950</t>
+  </si>
+  <si>
+    <t>134734990</t>
+  </si>
+  <si>
+    <t>134735890</t>
+  </si>
+  <si>
+    <t>134725955</t>
+  </si>
+  <si>
+    <t>134733692</t>
+  </si>
+  <si>
+    <t>134735925</t>
+  </si>
+  <si>
+    <t>134727035</t>
+  </si>
+  <si>
+    <t>134726676</t>
+  </si>
+  <si>
+    <t>134735885</t>
+  </si>
+  <si>
+    <t>134736197</t>
+  </si>
+  <si>
+    <t>134744876</t>
+  </si>
+  <si>
+    <t>134753238</t>
+  </si>
+  <si>
+    <t>134751622</t>
+  </si>
+  <si>
+    <t>134741792</t>
+  </si>
+  <si>
+    <t>134749916</t>
+  </si>
+  <si>
+    <t>134753702</t>
+  </si>
+  <si>
+    <t>134765245</t>
+  </si>
+  <si>
+    <t>134762100</t>
+  </si>
+  <si>
+    <t>134775004</t>
+  </si>
+  <si>
+    <t>134745618</t>
+  </si>
+  <si>
+    <t>134778673</t>
+  </si>
+  <si>
+    <t>134773266</t>
+  </si>
+  <si>
+    <t>134775184</t>
+  </si>
+  <si>
+    <t>134770573</t>
+  </si>
+  <si>
+    <t>134767352</t>
+  </si>
+  <si>
+    <t>134762607</t>
+  </si>
+  <si>
+    <t>134805931</t>
+  </si>
+  <si>
+    <t>134831025</t>
+  </si>
+  <si>
+    <t>134848131</t>
+  </si>
+  <si>
+    <t>134847927</t>
+  </si>
+  <si>
+    <t>134640565</t>
+  </si>
+  <si>
+    <t>134754427</t>
+  </si>
+  <si>
+    <t>134634134</t>
+  </si>
+  <si>
+    <t>134772531</t>
+  </si>
+  <si>
+    <t>134854577</t>
+  </si>
+  <si>
+    <t>134856178</t>
+  </si>
+  <si>
+    <t>133963508</t>
+  </si>
+  <si>
+    <t>134859685</t>
+  </si>
+  <si>
+    <t>134702457</t>
+  </si>
+  <si>
+    <t>134701024</t>
+  </si>
+  <si>
+    <t>134705830</t>
+  </si>
+  <si>
+    <t>134706140</t>
+  </si>
+  <si>
+    <t>134706806</t>
+  </si>
+  <si>
+    <t>131369526</t>
+  </si>
+  <si>
+    <t>134707627</t>
+  </si>
+  <si>
+    <t>134708350</t>
+  </si>
+  <si>
+    <t>134709764</t>
+  </si>
+  <si>
+    <t>134711662</t>
+  </si>
+  <si>
+    <t>134711761</t>
+  </si>
+  <si>
+    <t>134713751</t>
+  </si>
+  <si>
+    <t>134713970</t>
+  </si>
+  <si>
+    <t>134714162</t>
+  </si>
+  <si>
+    <t>134862106</t>
+  </si>
+  <si>
+    <t>134750035</t>
+  </si>
+  <si>
+    <t>130496860</t>
+  </si>
+  <si>
+    <t>134720422</t>
+  </si>
+  <si>
+    <t>134724226</t>
+  </si>
+  <si>
+    <t>134678972</t>
+  </si>
+  <si>
+    <t>134863819</t>
+  </si>
+  <si>
+    <t>134726390</t>
+  </si>
+  <si>
+    <t>134726584</t>
+  </si>
+  <si>
+    <t>134743194</t>
+  </si>
+  <si>
+    <t>134727976</t>
+  </si>
+  <si>
+    <t>134728509</t>
+  </si>
+  <si>
+    <t>134728609</t>
+  </si>
+  <si>
+    <t>134729101</t>
+  </si>
+  <si>
+    <t>134731279</t>
+  </si>
+  <si>
+    <t>134731834</t>
+  </si>
+  <si>
+    <t>134732077</t>
+  </si>
+  <si>
+    <t>133038530</t>
+  </si>
+  <si>
+    <t>134771005</t>
+  </si>
+  <si>
+    <t>134778788</t>
+  </si>
+  <si>
+    <t>134791032</t>
+  </si>
+  <si>
+    <t>134734482</t>
+  </si>
+  <si>
+    <t>134736854</t>
+  </si>
+  <si>
+    <t>134756625</t>
+  </si>
+  <si>
+    <t>134855387</t>
+  </si>
+  <si>
+    <t>134780420</t>
+  </si>
+  <si>
+    <t>134642827</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_09.10.2025</t>
   </si>
 </sst>
 </file>
@@ -626,16 +743,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134619898</v>
+        <v>129634207</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -644,16 +761,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -662,16 +779,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -679,16 +796,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -696,16 +813,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -713,16 +830,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -730,16 +847,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -747,16 +864,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,16 +881,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -781,16 +898,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -798,16 +915,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -815,16 +932,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -832,16 +949,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -849,16 +966,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -866,16 +983,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -883,16 +1000,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -900,16 +1017,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -917,16 +1034,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -934,16 +1051,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -951,16 +1068,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -968,16 +1085,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -985,16 +1102,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1002,16 +1119,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1019,16 +1136,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1036,16 +1153,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1053,16 +1170,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1187,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1087,16 +1204,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1104,16 +1221,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1121,16 +1238,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1138,16 +1255,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1155,16 +1272,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1172,16 +1289,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1189,16 +1306,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1206,16 +1323,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1223,16 +1340,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1240,16 +1357,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1257,16 +1374,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1274,16 +1391,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1291,16 +1408,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1308,16 +1425,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1325,16 +1442,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1342,16 +1459,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1359,16 +1476,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1376,24 +1493,670 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="1048576" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D1048576" s="2" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1410,31 +2173,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A8A05D-A1D2-4FCC-8EDD-0D358914DA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADBE5DD-40CB-4890-8F5F-BA9CF96EAE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="105">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,259 +54,295 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_08.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 09.10.2025</t>
-  </si>
-  <si>
-    <t>134709632</t>
-  </si>
-  <si>
-    <t>134703023</t>
-  </si>
-  <si>
-    <t>130930621</t>
-  </si>
-  <si>
-    <t>134718950</t>
-  </si>
-  <si>
-    <t>134734990</t>
-  </si>
-  <si>
-    <t>134735890</t>
-  </si>
-  <si>
-    <t>134725955</t>
-  </si>
-  <si>
-    <t>134733692</t>
-  </si>
-  <si>
-    <t>134735925</t>
-  </si>
-  <si>
-    <t>134727035</t>
-  </si>
-  <si>
-    <t>134726676</t>
-  </si>
-  <si>
-    <t>134735885</t>
-  </si>
-  <si>
-    <t>134736197</t>
-  </si>
-  <si>
-    <t>134744876</t>
-  </si>
-  <si>
-    <t>134753238</t>
-  </si>
-  <si>
-    <t>134751622</t>
-  </si>
-  <si>
-    <t>134741792</t>
-  </si>
-  <si>
-    <t>134749916</t>
-  </si>
-  <si>
-    <t>134753702</t>
-  </si>
-  <si>
-    <t>134765245</t>
-  </si>
-  <si>
-    <t>134762100</t>
-  </si>
-  <si>
-    <t>134775004</t>
-  </si>
-  <si>
-    <t>134745618</t>
-  </si>
-  <si>
-    <t>134778673</t>
-  </si>
-  <si>
-    <t>134773266</t>
-  </si>
-  <si>
-    <t>134775184</t>
-  </si>
-  <si>
-    <t>134770573</t>
-  </si>
-  <si>
-    <t>134767352</t>
-  </si>
-  <si>
-    <t>134762607</t>
-  </si>
-  <si>
-    <t>134805931</t>
-  </si>
-  <si>
-    <t>134831025</t>
-  </si>
-  <si>
-    <t>134848131</t>
-  </si>
-  <si>
-    <t>134847927</t>
-  </si>
-  <si>
-    <t>134640565</t>
-  </si>
-  <si>
-    <t>134754427</t>
-  </si>
-  <si>
-    <t>134634134</t>
-  </si>
-  <si>
-    <t>134772531</t>
-  </si>
-  <si>
-    <t>134854577</t>
-  </si>
-  <si>
-    <t>134856178</t>
-  </si>
-  <si>
-    <t>133963508</t>
-  </si>
-  <si>
-    <t>134859685</t>
-  </si>
-  <si>
-    <t>134702457</t>
-  </si>
-  <si>
-    <t>134701024</t>
-  </si>
-  <si>
-    <t>134705830</t>
-  </si>
-  <si>
-    <t>134706140</t>
-  </si>
-  <si>
-    <t>134706806</t>
-  </si>
-  <si>
-    <t>131369526</t>
-  </si>
-  <si>
-    <t>134707627</t>
-  </si>
-  <si>
-    <t>134708350</t>
-  </si>
-  <si>
-    <t>134709764</t>
-  </si>
-  <si>
-    <t>134711662</t>
-  </si>
-  <si>
-    <t>134711761</t>
-  </si>
-  <si>
-    <t>134713751</t>
-  </si>
-  <si>
-    <t>134713970</t>
-  </si>
-  <si>
-    <t>134714162</t>
-  </si>
-  <si>
-    <t>134862106</t>
-  </si>
-  <si>
-    <t>134750035</t>
-  </si>
-  <si>
-    <t>130496860</t>
-  </si>
-  <si>
-    <t>134720422</t>
-  </si>
-  <si>
-    <t>134724226</t>
-  </si>
-  <si>
-    <t>134678972</t>
-  </si>
-  <si>
-    <t>134863819</t>
-  </si>
-  <si>
-    <t>134726390</t>
-  </si>
-  <si>
-    <t>134726584</t>
-  </si>
-  <si>
-    <t>134743194</t>
-  </si>
-  <si>
-    <t>134727976</t>
-  </si>
-  <si>
-    <t>134728509</t>
-  </si>
-  <si>
-    <t>134728609</t>
-  </si>
-  <si>
-    <t>134729101</t>
-  </si>
-  <si>
-    <t>134731279</t>
-  </si>
-  <si>
-    <t>134731834</t>
-  </si>
-  <si>
-    <t>134732077</t>
-  </si>
-  <si>
-    <t>133038530</t>
-  </si>
-  <si>
-    <t>134771005</t>
-  </si>
-  <si>
-    <t>134778788</t>
-  </si>
-  <si>
-    <t>134791032</t>
-  </si>
-  <si>
-    <t>134734482</t>
-  </si>
-  <si>
-    <t>134736854</t>
-  </si>
-  <si>
-    <t>134756625</t>
-  </si>
-  <si>
-    <t>134855387</t>
-  </si>
-  <si>
-    <t>134780420</t>
-  </si>
-  <si>
-    <t>134642827</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_09.10.2025</t>
+    <t>Relatório Recusa _ SICREDI_11.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 11.10.2025</t>
+  </si>
+  <si>
+    <t>134616863</t>
+  </si>
+  <si>
+    <t>134634076</t>
+  </si>
+  <si>
+    <t>134890652</t>
+  </si>
+  <si>
+    <t>134687130</t>
+  </si>
+  <si>
+    <t>130105752</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 10.10.2025</t>
+  </si>
+  <si>
+    <t>134661563</t>
+  </si>
+  <si>
+    <t>134753023</t>
+  </si>
+  <si>
+    <t>134753099</t>
+  </si>
+  <si>
+    <t>134757710</t>
+  </si>
+  <si>
+    <t>134752176</t>
+  </si>
+  <si>
+    <t>134740901</t>
+  </si>
+  <si>
+    <t>134743475</t>
+  </si>
+  <si>
+    <t>134753424</t>
+  </si>
+  <si>
+    <t>134756891</t>
+  </si>
+  <si>
+    <t>134758096</t>
+  </si>
+  <si>
+    <t>134756365</t>
+  </si>
+  <si>
+    <t>134755978</t>
+  </si>
+  <si>
+    <t>134756242</t>
+  </si>
+  <si>
+    <t>134768150</t>
+  </si>
+  <si>
+    <t>134749859</t>
+  </si>
+  <si>
+    <t>134757899</t>
+  </si>
+  <si>
+    <t>134768836</t>
+  </si>
+  <si>
+    <t>134741424</t>
+  </si>
+  <si>
+    <t>134776484</t>
+  </si>
+  <si>
+    <t>134778242</t>
+  </si>
+  <si>
+    <t>134782265</t>
+  </si>
+  <si>
+    <t>134802787</t>
+  </si>
+  <si>
+    <t>134799641</t>
+  </si>
+  <si>
+    <t>133928289</t>
+  </si>
+  <si>
+    <t>134796131</t>
+  </si>
+  <si>
+    <t>134800093</t>
+  </si>
+  <si>
+    <t>134825649</t>
+  </si>
+  <si>
+    <t>134824171</t>
+  </si>
+  <si>
+    <t>134824783</t>
+  </si>
+  <si>
+    <t>134756660</t>
+  </si>
+  <si>
+    <t>134733627</t>
+  </si>
+  <si>
+    <t>134757462</t>
+  </si>
+  <si>
+    <t>134818020</t>
+  </si>
+  <si>
+    <t>134816322</t>
+  </si>
+  <si>
+    <t>134824211</t>
+  </si>
+  <si>
+    <t>134708461</t>
+  </si>
+  <si>
+    <t>134836746</t>
+  </si>
+  <si>
+    <t>134841383</t>
+  </si>
+  <si>
+    <t>134853710</t>
+  </si>
+  <si>
+    <t>134748111</t>
+  </si>
+  <si>
+    <t>134867628</t>
+  </si>
+  <si>
+    <t>134868043</t>
+  </si>
+  <si>
+    <t>134866807</t>
+  </si>
+  <si>
+    <t>134867812</t>
+  </si>
+  <si>
+    <t>134868735</t>
+  </si>
+  <si>
+    <t>134868571</t>
+  </si>
+  <si>
+    <t>134868480</t>
+  </si>
+  <si>
+    <t>134642175</t>
+  </si>
+  <si>
+    <t>134662267</t>
+  </si>
+  <si>
+    <t>134741190</t>
+  </si>
+  <si>
+    <t>131937829</t>
+  </si>
+  <si>
+    <t>130265262</t>
+  </si>
+  <si>
+    <t>134776455</t>
+  </si>
+  <si>
+    <t>134778545</t>
+  </si>
+  <si>
+    <t>134753613</t>
+  </si>
+  <si>
+    <t>134208028</t>
+  </si>
+  <si>
+    <t>134882590</t>
+  </si>
+  <si>
+    <t>134737199</t>
+  </si>
+  <si>
+    <t>134798411</t>
+  </si>
+  <si>
+    <t>134741517</t>
+  </si>
+  <si>
+    <t>134884905</t>
+  </si>
+  <si>
+    <t>134728083</t>
+  </si>
+  <si>
+    <t>134743503</t>
+  </si>
+  <si>
+    <t>134744471</t>
+  </si>
+  <si>
+    <t>134745291</t>
+  </si>
+  <si>
+    <t>134745337</t>
+  </si>
+  <si>
+    <t>134747203</t>
+  </si>
+  <si>
+    <t>134747381</t>
+  </si>
+  <si>
+    <t>134747639</t>
+  </si>
+  <si>
+    <t>134304099</t>
+  </si>
+  <si>
+    <t>134749144</t>
+  </si>
+  <si>
+    <t>134749799</t>
+  </si>
+  <si>
+    <t>134750346</t>
+  </si>
+  <si>
+    <t>134751482</t>
+  </si>
+  <si>
+    <t>133949015</t>
+  </si>
+  <si>
+    <t>134753873</t>
+  </si>
+  <si>
+    <t>134755524</t>
+  </si>
+  <si>
+    <t>134755955</t>
+  </si>
+  <si>
+    <t>134755966</t>
+  </si>
+  <si>
+    <t>134794588</t>
+  </si>
+  <si>
+    <t>134756752</t>
+  </si>
+  <si>
+    <t>134757690</t>
+  </si>
+  <si>
+    <t>134884896</t>
+  </si>
+  <si>
+    <t>130768994</t>
+  </si>
+  <si>
+    <t>134755463</t>
+  </si>
+  <si>
+    <t>134775279</t>
+  </si>
+  <si>
+    <t>134651066</t>
+  </si>
+  <si>
+    <t>134772506</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_10.10.2025</t>
   </si>
 </sst>
 </file>
@@ -711,7 +747,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -743,7 +779,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>129634207</v>
+        <v>134685000</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -752,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -770,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -788,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -805,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -822,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -836,10 +872,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -847,16 +883,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -864,16 +900,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -881,16 +917,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -898,16 +934,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -915,16 +951,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -932,16 +968,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -949,16 +985,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -966,16 +1002,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -983,16 +1019,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1000,16 +1036,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1017,16 +1053,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1070,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1051,16 +1087,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1068,16 +1104,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1085,16 +1121,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1102,16 +1138,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1119,16 +1155,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1136,16 +1172,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1153,16 +1189,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1170,16 +1206,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1187,16 +1223,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1204,16 +1240,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1221,16 +1257,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1238,16 +1274,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1255,16 +1291,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1272,16 +1308,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1289,16 +1325,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1306,16 +1342,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1323,16 +1359,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1340,16 +1376,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1357,16 +1393,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1374,16 +1410,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1391,16 +1427,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1408,16 +1444,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1425,16 +1461,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1442,16 +1478,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1459,16 +1495,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1476,16 +1512,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1493,16 +1529,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1510,16 +1546,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1527,16 +1563,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1544,16 +1580,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1561,16 +1597,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1578,16 +1614,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1595,16 +1631,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1612,16 +1648,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1629,16 +1665,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1646,16 +1682,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1663,16 +1699,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1680,16 +1716,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1697,16 +1733,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1714,16 +1750,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1731,16 +1767,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1748,16 +1784,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1765,16 +1801,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1782,16 +1818,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1799,16 +1835,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1816,16 +1852,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1833,16 +1869,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1850,16 +1886,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1867,16 +1903,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -1884,16 +1920,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -1901,16 +1937,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -1918,16 +1954,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -1935,16 +1971,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -1952,16 +1988,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -1969,16 +2005,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -1986,16 +2022,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2003,16 +2039,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2020,16 +2056,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2037,16 +2073,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2054,16 +2090,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2071,16 +2107,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2088,16 +2124,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2105,16 +2141,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2122,16 +2158,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2139,24 +2175,206 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="1048576" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1048576" s="2" t="s">
-        <v>8</v>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADBE5DD-40CB-4890-8F5F-BA9CF96EAE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1037152C-83EB-4630-85FD-9B8A2E8F40EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="72">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,295 +54,196 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_11.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 11.10.2025</t>
-  </si>
-  <si>
-    <t>134616863</t>
-  </si>
-  <si>
-    <t>134634076</t>
-  </si>
-  <si>
-    <t>134890652</t>
-  </si>
-  <si>
-    <t>134687130</t>
-  </si>
-  <si>
-    <t>130105752</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 10.10.2025</t>
-  </si>
-  <si>
-    <t>134661563</t>
-  </si>
-  <si>
-    <t>134753023</t>
-  </si>
-  <si>
-    <t>134753099</t>
-  </si>
-  <si>
-    <t>134757710</t>
-  </si>
-  <si>
-    <t>134752176</t>
-  </si>
-  <si>
-    <t>134740901</t>
-  </si>
-  <si>
-    <t>134743475</t>
-  </si>
-  <si>
-    <t>134753424</t>
-  </si>
-  <si>
-    <t>134756891</t>
-  </si>
-  <si>
-    <t>134758096</t>
-  </si>
-  <si>
-    <t>134756365</t>
-  </si>
-  <si>
-    <t>134755978</t>
-  </si>
-  <si>
-    <t>134756242</t>
-  </si>
-  <si>
-    <t>134768150</t>
-  </si>
-  <si>
-    <t>134749859</t>
-  </si>
-  <si>
-    <t>134757899</t>
-  </si>
-  <si>
-    <t>134768836</t>
-  </si>
-  <si>
-    <t>134741424</t>
-  </si>
-  <si>
-    <t>134776484</t>
-  </si>
-  <si>
-    <t>134778242</t>
-  </si>
-  <si>
-    <t>134782265</t>
-  </si>
-  <si>
-    <t>134802787</t>
-  </si>
-  <si>
-    <t>134799641</t>
-  </si>
-  <si>
-    <t>133928289</t>
-  </si>
-  <si>
-    <t>134796131</t>
-  </si>
-  <si>
-    <t>134800093</t>
-  </si>
-  <si>
-    <t>134825649</t>
-  </si>
-  <si>
-    <t>134824171</t>
-  </si>
-  <si>
-    <t>134824783</t>
-  </si>
-  <si>
-    <t>134756660</t>
-  </si>
-  <si>
-    <t>134733627</t>
-  </si>
-  <si>
-    <t>134757462</t>
-  </si>
-  <si>
-    <t>134818020</t>
-  </si>
-  <si>
-    <t>134816322</t>
-  </si>
-  <si>
-    <t>134824211</t>
-  </si>
-  <si>
-    <t>134708461</t>
-  </si>
-  <si>
-    <t>134836746</t>
-  </si>
-  <si>
-    <t>134841383</t>
-  </si>
-  <si>
-    <t>134853710</t>
-  </si>
-  <si>
-    <t>134748111</t>
-  </si>
-  <si>
-    <t>134867628</t>
-  </si>
-  <si>
-    <t>134868043</t>
-  </si>
-  <si>
-    <t>134866807</t>
-  </si>
-  <si>
-    <t>134867812</t>
-  </si>
-  <si>
-    <t>134868735</t>
-  </si>
-  <si>
-    <t>134868571</t>
-  </si>
-  <si>
-    <t>134868480</t>
-  </si>
-  <si>
-    <t>134642175</t>
-  </si>
-  <si>
-    <t>134662267</t>
-  </si>
-  <si>
-    <t>134741190</t>
-  </si>
-  <si>
-    <t>131937829</t>
-  </si>
-  <si>
-    <t>130265262</t>
-  </si>
-  <si>
-    <t>134776455</t>
-  </si>
-  <si>
-    <t>134778545</t>
-  </si>
-  <si>
-    <t>134753613</t>
-  </si>
-  <si>
-    <t>134208028</t>
-  </si>
-  <si>
-    <t>134882590</t>
-  </si>
-  <si>
-    <t>134737199</t>
-  </si>
-  <si>
-    <t>134798411</t>
-  </si>
-  <si>
-    <t>134741517</t>
-  </si>
-  <si>
-    <t>134884905</t>
-  </si>
-  <si>
-    <t>134728083</t>
-  </si>
-  <si>
-    <t>134743503</t>
-  </si>
-  <si>
-    <t>134744471</t>
-  </si>
-  <si>
-    <t>134745291</t>
-  </si>
-  <si>
-    <t>134745337</t>
-  </si>
-  <si>
-    <t>134747203</t>
-  </si>
-  <si>
-    <t>134747381</t>
-  </si>
-  <si>
-    <t>134747639</t>
-  </si>
-  <si>
-    <t>134304099</t>
-  </si>
-  <si>
-    <t>134749144</t>
-  </si>
-  <si>
-    <t>134749799</t>
-  </si>
-  <si>
-    <t>134750346</t>
-  </si>
-  <si>
-    <t>134751482</t>
-  </si>
-  <si>
-    <t>133949015</t>
-  </si>
-  <si>
-    <t>134753873</t>
-  </si>
-  <si>
-    <t>134755524</t>
-  </si>
-  <si>
-    <t>134755955</t>
-  </si>
-  <si>
-    <t>134755966</t>
-  </si>
-  <si>
-    <t>134794588</t>
-  </si>
-  <si>
-    <t>134756752</t>
-  </si>
-  <si>
-    <t>134757690</t>
-  </si>
-  <si>
-    <t>134884896</t>
-  </si>
-  <si>
-    <t>130768994</t>
-  </si>
-  <si>
-    <t>134755463</t>
-  </si>
-  <si>
-    <t>134775279</t>
-  </si>
-  <si>
-    <t>134651066</t>
-  </si>
-  <si>
-    <t>134772506</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_10.10.2025</t>
+    <t>Relatório de Recusa Sicredi 13.10.2025</t>
+  </si>
+  <si>
+    <t>132962680</t>
+  </si>
+  <si>
+    <t>134767956</t>
+  </si>
+  <si>
+    <t>134769059</t>
+  </si>
+  <si>
+    <t>134770103</t>
+  </si>
+  <si>
+    <t>134775581</t>
+  </si>
+  <si>
+    <t>134782380</t>
+  </si>
+  <si>
+    <t>134780500</t>
+  </si>
+  <si>
+    <t>134777234</t>
+  </si>
+  <si>
+    <t>134766284</t>
+  </si>
+  <si>
+    <t>134801039</t>
+  </si>
+  <si>
+    <t>134802351</t>
+  </si>
+  <si>
+    <t>134802415</t>
+  </si>
+  <si>
+    <t>134791707</t>
+  </si>
+  <si>
+    <t>134811076</t>
+  </si>
+  <si>
+    <t>134814646</t>
+  </si>
+  <si>
+    <t>134814133</t>
+  </si>
+  <si>
+    <t>134778558</t>
+  </si>
+  <si>
+    <t>134777428</t>
+  </si>
+  <si>
+    <t>134822647</t>
+  </si>
+  <si>
+    <t>134843062</t>
+  </si>
+  <si>
+    <t>134768648</t>
+  </si>
+  <si>
+    <t>134781302</t>
+  </si>
+  <si>
+    <t>134889360</t>
+  </si>
+  <si>
+    <t>134888387</t>
+  </si>
+  <si>
+    <t>134884365</t>
+  </si>
+  <si>
+    <t>134884785</t>
+  </si>
+  <si>
+    <t>134891706</t>
+  </si>
+  <si>
+    <t>134879323</t>
+  </si>
+  <si>
+    <t>134774112</t>
+  </si>
+  <si>
+    <t>134692413</t>
+  </si>
+  <si>
+    <t>130726264</t>
+  </si>
+  <si>
+    <t>134746945</t>
+  </si>
+  <si>
+    <t>134797980</t>
+  </si>
+  <si>
+    <t>134799355</t>
+  </si>
+  <si>
+    <t>134840181</t>
+  </si>
+  <si>
+    <t>134815388</t>
+  </si>
+  <si>
+    <t>134765407</t>
+  </si>
+  <si>
+    <t>132859779</t>
+  </si>
+  <si>
+    <t>134713513</t>
+  </si>
+  <si>
+    <t>134733433</t>
+  </si>
+  <si>
+    <t>131450066</t>
+  </si>
+  <si>
+    <t>133203383</t>
+  </si>
+  <si>
+    <t>134764418</t>
+  </si>
+  <si>
+    <t>134799465</t>
+  </si>
+  <si>
+    <t>134764962</t>
+  </si>
+  <si>
+    <t>134910105</t>
+  </si>
+  <si>
+    <t>134766424</t>
+  </si>
+  <si>
+    <t>134767489</t>
+  </si>
+  <si>
+    <t>134769674</t>
+  </si>
+  <si>
+    <t>134770357</t>
+  </si>
+  <si>
+    <t>134771010</t>
+  </si>
+  <si>
+    <t>134771582</t>
+  </si>
+  <si>
+    <t>134776883</t>
+  </si>
+  <si>
+    <t>134776982</t>
+  </si>
+  <si>
+    <t>134777084</t>
+  </si>
+  <si>
+    <t>134818229</t>
+  </si>
+  <si>
+    <t>134777622</t>
+  </si>
+  <si>
+    <t>134779754</t>
+  </si>
+  <si>
+    <t>134780685</t>
+  </si>
+  <si>
+    <t>134780719</t>
+  </si>
+  <si>
+    <t>134782253</t>
+  </si>
+  <si>
+    <t>134783058</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_13.10.2025</t>
   </si>
 </sst>
 </file>
@@ -747,7 +648,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -779,16 +680,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134685000</v>
+        <v>130927102</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -797,16 +698,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -815,16 +716,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -832,16 +733,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -849,16 +750,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -866,16 +767,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -883,16 +784,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -900,16 +801,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -917,16 +818,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -934,16 +835,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -951,16 +852,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -968,16 +869,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -985,16 +886,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1002,16 +903,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1019,16 +920,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1036,16 +937,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1053,16 +954,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1070,16 +971,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1087,16 +988,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1104,16 +1005,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1121,16 +1022,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1138,16 +1039,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1155,16 +1056,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1172,16 +1073,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1189,16 +1090,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1206,16 +1107,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1223,16 +1124,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1240,16 +1141,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1257,16 +1158,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1274,16 +1175,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1291,16 +1192,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1308,16 +1209,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1325,16 +1226,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1342,16 +1243,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1359,16 +1260,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1376,16 +1277,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1393,16 +1294,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1410,16 +1311,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1427,16 +1328,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1444,16 +1345,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1461,16 +1362,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1478,16 +1379,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1495,16 +1396,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1512,16 +1413,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1529,16 +1430,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1546,16 +1447,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1563,16 +1464,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1580,16 +1481,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1597,16 +1498,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1614,16 +1515,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1631,16 +1532,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1648,16 +1549,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1665,16 +1566,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1682,16 +1583,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1699,16 +1600,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1716,16 +1617,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1733,16 +1634,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1750,16 +1651,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1767,16 +1668,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1784,16 +1685,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1801,16 +1702,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1818,16 +1719,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1835,545 +1736,18 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E95" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2391,31 +1765,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1037152C-83EB-4630-85FD-9B8A2E8F40EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE12C837-3B42-4004-853D-9EF3E5F01AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="115">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,196 +54,325 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 13.10.2025</t>
-  </si>
-  <si>
-    <t>132962680</t>
-  </si>
-  <si>
-    <t>134767956</t>
-  </si>
-  <si>
-    <t>134769059</t>
-  </si>
-  <si>
-    <t>134770103</t>
-  </si>
-  <si>
-    <t>134775581</t>
-  </si>
-  <si>
-    <t>134782380</t>
-  </si>
-  <si>
-    <t>134780500</t>
-  </si>
-  <si>
-    <t>134777234</t>
-  </si>
-  <si>
-    <t>134766284</t>
-  </si>
-  <si>
-    <t>134801039</t>
-  </si>
-  <si>
-    <t>134802351</t>
-  </si>
-  <si>
-    <t>134802415</t>
-  </si>
-  <si>
-    <t>134791707</t>
-  </si>
-  <si>
-    <t>134811076</t>
-  </si>
-  <si>
-    <t>134814646</t>
-  </si>
-  <si>
-    <t>134814133</t>
-  </si>
-  <si>
-    <t>134778558</t>
-  </si>
-  <si>
-    <t>134777428</t>
-  </si>
-  <si>
-    <t>134822647</t>
-  </si>
-  <si>
-    <t>134843062</t>
-  </si>
-  <si>
-    <t>134768648</t>
-  </si>
-  <si>
-    <t>134781302</t>
-  </si>
-  <si>
-    <t>134889360</t>
-  </si>
-  <si>
-    <t>134888387</t>
-  </si>
-  <si>
-    <t>134884365</t>
-  </si>
-  <si>
-    <t>134884785</t>
-  </si>
-  <si>
-    <t>134891706</t>
-  </si>
-  <si>
-    <t>134879323</t>
-  </si>
-  <si>
-    <t>134774112</t>
-  </si>
-  <si>
-    <t>134692413</t>
-  </si>
-  <si>
-    <t>130726264</t>
-  </si>
-  <si>
-    <t>134746945</t>
-  </si>
-  <si>
-    <t>134797980</t>
-  </si>
-  <si>
-    <t>134799355</t>
-  </si>
-  <si>
-    <t>134840181</t>
-  </si>
-  <si>
-    <t>134815388</t>
-  </si>
-  <si>
-    <t>134765407</t>
-  </si>
-  <si>
-    <t>132859779</t>
-  </si>
-  <si>
-    <t>134713513</t>
-  </si>
-  <si>
-    <t>134733433</t>
-  </si>
-  <si>
-    <t>131450066</t>
-  </si>
-  <si>
-    <t>133203383</t>
-  </si>
-  <si>
-    <t>134764418</t>
-  </si>
-  <si>
-    <t>134799465</t>
-  </si>
-  <si>
-    <t>134764962</t>
-  </si>
-  <si>
-    <t>134910105</t>
-  </si>
-  <si>
-    <t>134766424</t>
-  </si>
-  <si>
-    <t>134767489</t>
-  </si>
-  <si>
-    <t>134769674</t>
-  </si>
-  <si>
-    <t>134770357</t>
-  </si>
-  <si>
-    <t>134771010</t>
-  </si>
-  <si>
-    <t>134771582</t>
-  </si>
-  <si>
-    <t>134776883</t>
-  </si>
-  <si>
-    <t>134776982</t>
-  </si>
-  <si>
-    <t>134777084</t>
-  </si>
-  <si>
-    <t>134818229</t>
-  </si>
-  <si>
-    <t>134777622</t>
-  </si>
-  <si>
-    <t>134779754</t>
-  </si>
-  <si>
-    <t>134780685</t>
-  </si>
-  <si>
-    <t>134780719</t>
-  </si>
-  <si>
-    <t>134782253</t>
-  </si>
-  <si>
-    <t>134783058</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_13.10.2025</t>
+    <t>Relatório de Recusa Sicredi 15.10.2025</t>
+  </si>
+  <si>
+    <t>134806424</t>
+  </si>
+  <si>
+    <t>134806897</t>
+  </si>
+  <si>
+    <t>134798555</t>
+  </si>
+  <si>
+    <t>134812217</t>
+  </si>
+  <si>
+    <t>134730459</t>
+  </si>
+  <si>
+    <t>134798049</t>
+  </si>
+  <si>
+    <t>134835412</t>
+  </si>
+  <si>
+    <t>134793823</t>
+  </si>
+  <si>
+    <t>134839046</t>
+  </si>
+  <si>
+    <t>134844418</t>
+  </si>
+  <si>
+    <t>134832335</t>
+  </si>
+  <si>
+    <t>134840838</t>
+  </si>
+  <si>
+    <t>134852987</t>
+  </si>
+  <si>
+    <t>134729977</t>
+  </si>
+  <si>
+    <t>134866022</t>
+  </si>
+  <si>
+    <t>134822752</t>
+  </si>
+  <si>
+    <t>134891886</t>
+  </si>
+  <si>
+    <t>134907404</t>
+  </si>
+  <si>
+    <t>134758403</t>
+  </si>
+  <si>
+    <t>134906477</t>
+  </si>
+  <si>
+    <t>134705744</t>
+  </si>
+  <si>
+    <t>134805663</t>
+  </si>
+  <si>
+    <t>134774936</t>
+  </si>
+  <si>
+    <t>134917257</t>
+  </si>
+  <si>
+    <t>134906071</t>
+  </si>
+  <si>
+    <t>134825873</t>
+  </si>
+  <si>
+    <t>134839271</t>
+  </si>
+  <si>
+    <t>134823538</t>
+  </si>
+  <si>
+    <t>134099847</t>
+  </si>
+  <si>
+    <t>134824128</t>
+  </si>
+  <si>
+    <t>134817881</t>
+  </si>
+  <si>
+    <t>134922911</t>
+  </si>
+  <si>
+    <t>134706200</t>
+  </si>
+  <si>
+    <t>134804196</t>
+  </si>
+  <si>
+    <t>134823232</t>
+  </si>
+  <si>
+    <t>134918717</t>
+  </si>
+  <si>
+    <t>134822102</t>
+  </si>
+  <si>
+    <t>134821858</t>
+  </si>
+  <si>
+    <t>134746460</t>
+  </si>
+  <si>
+    <t>134822737</t>
+  </si>
+  <si>
+    <t>134817458</t>
+  </si>
+  <si>
+    <t>134838327</t>
+  </si>
+  <si>
+    <t>134837728</t>
+  </si>
+  <si>
+    <t>134830287</t>
+  </si>
+  <si>
+    <t>131154405</t>
+  </si>
+  <si>
+    <t>134792759</t>
+  </si>
+  <si>
+    <t>134793285</t>
+  </si>
+  <si>
+    <t>134798989</t>
+  </si>
+  <si>
+    <t>134803387</t>
+  </si>
+  <si>
+    <t>134804220</t>
+  </si>
+  <si>
+    <t>134804532</t>
+  </si>
+  <si>
+    <t>134804548</t>
+  </si>
+  <si>
+    <t>134804615</t>
+  </si>
+  <si>
+    <t>134805834</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_14.10.2025</t>
+  </si>
+  <si>
+    <t>134736404</t>
+  </si>
+  <si>
+    <t>134778515</t>
+  </si>
+  <si>
+    <t>134812842</t>
+  </si>
+  <si>
+    <t>134827027</t>
+  </si>
+  <si>
+    <t>134848605</t>
+  </si>
+  <si>
+    <t>134835109</t>
+  </si>
+  <si>
+    <t>134855639</t>
+  </si>
+  <si>
+    <t>134855999</t>
+  </si>
+  <si>
+    <t>134863639</t>
+  </si>
+  <si>
+    <t>134854679</t>
+  </si>
+  <si>
+    <t>134854172</t>
+  </si>
+  <si>
+    <t>134862373</t>
+  </si>
+  <si>
+    <t>134881656</t>
+  </si>
+  <si>
+    <t>134891539</t>
+  </si>
+  <si>
+    <t>134883217</t>
+  </si>
+  <si>
+    <t>134907683</t>
+  </si>
+  <si>
+    <t>134906510</t>
+  </si>
+  <si>
+    <t>134917220</t>
+  </si>
+  <si>
+    <t>134882123</t>
+  </si>
+  <si>
+    <t>134930058</t>
+  </si>
+  <si>
+    <t>134922269</t>
+  </si>
+  <si>
+    <t>134934027</t>
+  </si>
+  <si>
+    <t>134917521</t>
+  </si>
+  <si>
+    <t>134937657</t>
+  </si>
+  <si>
+    <t>134719833</t>
+  </si>
+  <si>
+    <t>134721064</t>
+  </si>
+  <si>
+    <t>134724921</t>
+  </si>
+  <si>
+    <t>134729376</t>
+  </si>
+  <si>
+    <t>134738013</t>
+  </si>
+  <si>
+    <t>134867224</t>
+  </si>
+  <si>
+    <t>134866845</t>
+  </si>
+  <si>
+    <t>134845112</t>
+  </si>
+  <si>
+    <t>134816687</t>
+  </si>
+  <si>
+    <t>134945320</t>
+  </si>
+  <si>
+    <t>134945121</t>
+  </si>
+  <si>
+    <t>134862055</t>
+  </si>
+  <si>
+    <t>134942003</t>
+  </si>
+  <si>
+    <t>134945318</t>
+  </si>
+  <si>
+    <t>134865046</t>
+  </si>
+  <si>
+    <t>134844647</t>
+  </si>
+  <si>
+    <t>134863848</t>
+  </si>
+  <si>
+    <t>134944305</t>
+  </si>
+  <si>
+    <t>134844714</t>
+  </si>
+  <si>
+    <t>134032460</t>
+  </si>
+  <si>
+    <t>134821961</t>
+  </si>
+  <si>
+    <t>134951486</t>
+  </si>
+  <si>
+    <t>134848403</t>
+  </si>
+  <si>
+    <t>134878423</t>
+  </si>
+  <si>
+    <t>131744635</t>
+  </si>
+  <si>
+    <t>134748751</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_15.10.2025</t>
   </si>
 </sst>
 </file>
@@ -648,7 +777,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -680,7 +809,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130927102</v>
+        <v>134716214</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -689,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -707,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -725,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -742,7 +871,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -759,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -776,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -793,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -810,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -827,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -844,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -861,7 +990,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -878,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -895,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -912,7 +1041,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -929,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -946,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -963,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -980,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -997,7 +1126,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1014,7 +1143,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1031,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1048,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1065,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1099,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1116,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1150,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1167,7 +1296,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1201,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1218,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1252,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1269,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1286,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1303,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1320,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1337,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1354,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1371,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1388,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1405,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1422,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1439,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1456,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1473,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1490,7 +1619,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1507,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1524,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1541,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1558,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1575,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1592,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1609,7 +1738,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1617,7 +1746,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
@@ -1626,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1634,7 +1763,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
@@ -1643,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1651,7 +1780,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
@@ -1660,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1668,7 +1797,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
@@ -1677,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1685,7 +1814,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
@@ -1694,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1702,7 +1831,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
@@ -1711,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1719,7 +1848,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
@@ -1728,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1736,7 +1865,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
@@ -1745,9 +1874,723 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE12C837-3B42-4004-853D-9EF3E5F01AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1546D9-66BD-4C85-9863-CBF06FA3E70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="166">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -373,6 +373,159 @@
   </si>
   <si>
     <t>Relatório Recusa _ SICREDI_15.10.2025</t>
+  </si>
+  <si>
+    <t>130736305</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 16.10.2025</t>
+  </si>
+  <si>
+    <t>134803720</t>
+  </si>
+  <si>
+    <t>134848803</t>
+  </si>
+  <si>
+    <t>134848588</t>
+  </si>
+  <si>
+    <t>134847316</t>
+  </si>
+  <si>
+    <t>134848897</t>
+  </si>
+  <si>
+    <t>134848155</t>
+  </si>
+  <si>
+    <t>134850030</t>
+  </si>
+  <si>
+    <t>134858054</t>
+  </si>
+  <si>
+    <t>134856152</t>
+  </si>
+  <si>
+    <t>134857206</t>
+  </si>
+  <si>
+    <t>134864132</t>
+  </si>
+  <si>
+    <t>134868776</t>
+  </si>
+  <si>
+    <t>134888892</t>
+  </si>
+  <si>
+    <t>134889873</t>
+  </si>
+  <si>
+    <t>134879840</t>
+  </si>
+  <si>
+    <t>134886911</t>
+  </si>
+  <si>
+    <t>134879278</t>
+  </si>
+  <si>
+    <t>134927887</t>
+  </si>
+  <si>
+    <t>134934370</t>
+  </si>
+  <si>
+    <t>134941306</t>
+  </si>
+  <si>
+    <t>134803876</t>
+  </si>
+  <si>
+    <t>134945706</t>
+  </si>
+  <si>
+    <t>134954794</t>
+  </si>
+  <si>
+    <t>134951294</t>
+  </si>
+  <si>
+    <t>134845619</t>
+  </si>
+  <si>
+    <t>134849003</t>
+  </si>
+  <si>
+    <t>134757265</t>
+  </si>
+  <si>
+    <t>134886830</t>
+  </si>
+  <si>
+    <t>132642520</t>
+  </si>
+  <si>
+    <t>134960489</t>
+  </si>
+  <si>
+    <t>134957962</t>
+  </si>
+  <si>
+    <t>132131431</t>
+  </si>
+  <si>
+    <t>134962917</t>
+  </si>
+  <si>
+    <t>134965008</t>
+  </si>
+  <si>
+    <t>134782705</t>
+  </si>
+  <si>
+    <t>134967627</t>
+  </si>
+  <si>
+    <t>134775070</t>
+  </si>
+  <si>
+    <t>134880049</t>
+  </si>
+  <si>
+    <t>134890320</t>
+  </si>
+  <si>
+    <t>134970994</t>
+  </si>
+  <si>
+    <t>134971220</t>
+  </si>
+  <si>
+    <t>134742045</t>
+  </si>
+  <si>
+    <t>134844672</t>
+  </si>
+  <si>
+    <t>134964218</t>
+  </si>
+  <si>
+    <t>134846245</t>
+  </si>
+  <si>
+    <t>134975001</t>
+  </si>
+  <si>
+    <t>134975574</t>
+  </si>
+  <si>
+    <t>134974428</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_16.10.2025</t>
   </si>
 </sst>
 </file>
@@ -777,7 +930,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -2591,6 +2744,839 @@
         <v>114</v>
       </c>
       <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2608,31 +3594,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1546D9-66BD-4C85-9863-CBF06FA3E70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F5E03-618A-4675-80FB-CF7D072160FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="132">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,485 +54,383 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 15.10.2025</t>
-  </si>
-  <si>
-    <t>134806424</t>
-  </si>
-  <si>
-    <t>134806897</t>
-  </si>
-  <si>
-    <t>134798555</t>
-  </si>
-  <si>
-    <t>134812217</t>
-  </si>
-  <si>
-    <t>134730459</t>
-  </si>
-  <si>
-    <t>134798049</t>
-  </si>
-  <si>
-    <t>134835412</t>
-  </si>
-  <si>
-    <t>134793823</t>
-  </si>
-  <si>
-    <t>134839046</t>
-  </si>
-  <si>
-    <t>134844418</t>
-  </si>
-  <si>
-    <t>134832335</t>
-  </si>
-  <si>
-    <t>134840838</t>
-  </si>
-  <si>
-    <t>134852987</t>
-  </si>
-  <si>
-    <t>134729977</t>
-  </si>
-  <si>
-    <t>134866022</t>
-  </si>
-  <si>
-    <t>134822752</t>
-  </si>
-  <si>
-    <t>134891886</t>
-  </si>
-  <si>
-    <t>134907404</t>
-  </si>
-  <si>
-    <t>134758403</t>
-  </si>
-  <si>
-    <t>134906477</t>
-  </si>
-  <si>
-    <t>134705744</t>
-  </si>
-  <si>
-    <t>134805663</t>
-  </si>
-  <si>
-    <t>134774936</t>
-  </si>
-  <si>
-    <t>134917257</t>
-  </si>
-  <si>
-    <t>134906071</t>
-  </si>
-  <si>
-    <t>134825873</t>
-  </si>
-  <si>
-    <t>134839271</t>
-  </si>
-  <si>
-    <t>134823538</t>
-  </si>
-  <si>
-    <t>134099847</t>
-  </si>
-  <si>
-    <t>134824128</t>
-  </si>
-  <si>
-    <t>134817881</t>
-  </si>
-  <si>
-    <t>134922911</t>
-  </si>
-  <si>
-    <t>134706200</t>
-  </si>
-  <si>
-    <t>134804196</t>
-  </si>
-  <si>
-    <t>134823232</t>
-  </si>
-  <si>
-    <t>134918717</t>
-  </si>
-  <si>
-    <t>134822102</t>
-  </si>
-  <si>
-    <t>134821858</t>
-  </si>
-  <si>
-    <t>134746460</t>
-  </si>
-  <si>
-    <t>134822737</t>
-  </si>
-  <si>
-    <t>134817458</t>
-  </si>
-  <si>
-    <t>134838327</t>
-  </si>
-  <si>
-    <t>134837728</t>
-  </si>
-  <si>
-    <t>134830287</t>
-  </si>
-  <si>
-    <t>131154405</t>
-  </si>
-  <si>
-    <t>134792759</t>
-  </si>
-  <si>
-    <t>134793285</t>
-  </si>
-  <si>
-    <t>134798989</t>
-  </si>
-  <si>
-    <t>134803387</t>
-  </si>
-  <si>
-    <t>134804220</t>
-  </si>
-  <si>
-    <t>134804532</t>
-  </si>
-  <si>
-    <t>134804548</t>
-  </si>
-  <si>
-    <t>134804615</t>
-  </si>
-  <si>
-    <t>134805834</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_14.10.2025</t>
-  </si>
-  <si>
-    <t>134736404</t>
-  </si>
-  <si>
-    <t>134778515</t>
-  </si>
-  <si>
-    <t>134812842</t>
-  </si>
-  <si>
-    <t>134827027</t>
-  </si>
-  <si>
-    <t>134848605</t>
-  </si>
-  <si>
-    <t>134835109</t>
-  </si>
-  <si>
-    <t>134855639</t>
-  </si>
-  <si>
-    <t>134855999</t>
-  </si>
-  <si>
-    <t>134863639</t>
-  </si>
-  <si>
-    <t>134854679</t>
-  </si>
-  <si>
-    <t>134854172</t>
-  </si>
-  <si>
-    <t>134862373</t>
-  </si>
-  <si>
-    <t>134881656</t>
-  </si>
-  <si>
-    <t>134891539</t>
-  </si>
-  <si>
-    <t>134883217</t>
-  </si>
-  <si>
-    <t>134907683</t>
-  </si>
-  <si>
-    <t>134906510</t>
-  </si>
-  <si>
-    <t>134917220</t>
-  </si>
-  <si>
-    <t>134882123</t>
-  </si>
-  <si>
-    <t>134930058</t>
-  </si>
-  <si>
-    <t>134922269</t>
-  </si>
-  <si>
-    <t>134934027</t>
-  </si>
-  <si>
-    <t>134917521</t>
-  </si>
-  <si>
-    <t>134937657</t>
-  </si>
-  <si>
-    <t>134719833</t>
-  </si>
-  <si>
-    <t>134721064</t>
-  </si>
-  <si>
-    <t>134724921</t>
-  </si>
-  <si>
-    <t>134729376</t>
-  </si>
-  <si>
-    <t>134738013</t>
-  </si>
-  <si>
-    <t>134867224</t>
-  </si>
-  <si>
-    <t>134866845</t>
-  </si>
-  <si>
-    <t>134845112</t>
-  </si>
-  <si>
-    <t>134816687</t>
-  </si>
-  <si>
-    <t>134945320</t>
-  </si>
-  <si>
-    <t>134945121</t>
-  </si>
-  <si>
-    <t>134862055</t>
-  </si>
-  <si>
-    <t>134942003</t>
-  </si>
-  <si>
-    <t>134945318</t>
-  </si>
-  <si>
-    <t>134865046</t>
-  </si>
-  <si>
-    <t>134844647</t>
-  </si>
-  <si>
-    <t>134863848</t>
-  </si>
-  <si>
-    <t>134944305</t>
-  </si>
-  <si>
-    <t>134844714</t>
-  </si>
-  <si>
-    <t>134032460</t>
-  </si>
-  <si>
-    <t>134821961</t>
-  </si>
-  <si>
-    <t>134951486</t>
-  </si>
-  <si>
-    <t>134848403</t>
-  </si>
-  <si>
-    <t>134878423</t>
-  </si>
-  <si>
-    <t>131744635</t>
-  </si>
-  <si>
-    <t>134748751</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_15.10.2025</t>
-  </si>
-  <si>
-    <t>130736305</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 16.10.2025</t>
-  </si>
-  <si>
-    <t>134803720</t>
-  </si>
-  <si>
-    <t>134848803</t>
-  </si>
-  <si>
-    <t>134848588</t>
-  </si>
-  <si>
-    <t>134847316</t>
-  </si>
-  <si>
-    <t>134848897</t>
-  </si>
-  <si>
-    <t>134848155</t>
-  </si>
-  <si>
-    <t>134850030</t>
-  </si>
-  <si>
-    <t>134858054</t>
-  </si>
-  <si>
-    <t>134856152</t>
-  </si>
-  <si>
-    <t>134857206</t>
-  </si>
-  <si>
-    <t>134864132</t>
-  </si>
-  <si>
-    <t>134868776</t>
-  </si>
-  <si>
-    <t>134888892</t>
-  </si>
-  <si>
-    <t>134889873</t>
-  </si>
-  <si>
-    <t>134879840</t>
-  </si>
-  <si>
-    <t>134886911</t>
-  </si>
-  <si>
-    <t>134879278</t>
-  </si>
-  <si>
-    <t>134927887</t>
-  </si>
-  <si>
-    <t>134934370</t>
-  </si>
-  <si>
-    <t>134941306</t>
-  </si>
-  <si>
-    <t>134803876</t>
-  </si>
-  <si>
-    <t>134945706</t>
-  </si>
-  <si>
-    <t>134954794</t>
-  </si>
-  <si>
-    <t>134951294</t>
-  </si>
-  <si>
-    <t>134845619</t>
-  </si>
-  <si>
-    <t>134849003</t>
-  </si>
-  <si>
-    <t>134757265</t>
-  </si>
-  <si>
-    <t>134886830</t>
-  </si>
-  <si>
-    <t>132642520</t>
-  </si>
-  <si>
-    <t>134960489</t>
-  </si>
-  <si>
-    <t>134957962</t>
-  </si>
-  <si>
-    <t>132131431</t>
-  </si>
-  <si>
-    <t>134962917</t>
-  </si>
-  <si>
-    <t>134965008</t>
-  </si>
-  <si>
-    <t>134782705</t>
-  </si>
-  <si>
-    <t>134967627</t>
-  </si>
-  <si>
-    <t>134775070</t>
-  </si>
-  <si>
-    <t>134880049</t>
-  </si>
-  <si>
-    <t>134890320</t>
-  </si>
-  <si>
-    <t>134970994</t>
-  </si>
-  <si>
-    <t>134971220</t>
-  </si>
-  <si>
-    <t>134742045</t>
-  </si>
-  <si>
-    <t>134844672</t>
-  </si>
-  <si>
-    <t>134964218</t>
-  </si>
-  <si>
-    <t>134846245</t>
-  </si>
-  <si>
-    <t>134975001</t>
-  </si>
-  <si>
-    <t>134975574</t>
-  </si>
-  <si>
-    <t>134974428</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_16.10.2025</t>
+    <t>Relatório de Recusa Sicredi 20.10.2025</t>
+  </si>
+  <si>
+    <t>134920719</t>
+  </si>
+  <si>
+    <t>134949135</t>
+  </si>
+  <si>
+    <t>134950206</t>
+  </si>
+  <si>
+    <t>134955442</t>
+  </si>
+  <si>
+    <t>134948725</t>
+  </si>
+  <si>
+    <t>134947549</t>
+  </si>
+  <si>
+    <t>134948737</t>
+  </si>
+  <si>
+    <t>134947654</t>
+  </si>
+  <si>
+    <t>134941125</t>
+  </si>
+  <si>
+    <t>134955110</t>
+  </si>
+  <si>
+    <t>134994698</t>
+  </si>
+  <si>
+    <t>134997966</t>
+  </si>
+  <si>
+    <t>134995137</t>
+  </si>
+  <si>
+    <t>132101065</t>
+  </si>
+  <si>
+    <t>134926039</t>
+  </si>
+  <si>
+    <t>134903793</t>
+  </si>
+  <si>
+    <t>134938071</t>
+  </si>
+  <si>
+    <t>132723100</t>
+  </si>
+  <si>
+    <t>134940370</t>
+  </si>
+  <si>
+    <t>134902146</t>
+  </si>
+  <si>
+    <t>134924142</t>
+  </si>
+  <si>
+    <t>135008133</t>
+  </si>
+  <si>
+    <t>134938047</t>
+  </si>
+  <si>
+    <t>134950794</t>
+  </si>
+  <si>
+    <t>135013302</t>
+  </si>
+  <si>
+    <t>135016647</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_20.10.2025</t>
+  </si>
+  <si>
+    <t>134779137</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 17/10/2025</t>
+  </si>
+  <si>
+    <t>134814811</t>
+  </si>
+  <si>
+    <t>134824003</t>
+  </si>
+  <si>
+    <t>134825564</t>
+  </si>
+  <si>
+    <t>133453537</t>
+  </si>
+  <si>
+    <t>134839316</t>
+  </si>
+  <si>
+    <t>134833199</t>
+  </si>
+  <si>
+    <t>134836495</t>
+  </si>
+  <si>
+    <t>134853205</t>
+  </si>
+  <si>
+    <t>134852522</t>
+  </si>
+  <si>
+    <t>134852584</t>
+  </si>
+  <si>
+    <t>134858817</t>
+  </si>
+  <si>
+    <t>134883844</t>
+  </si>
+  <si>
+    <t>134892837</t>
+  </si>
+  <si>
+    <t>134881725</t>
+  </si>
+  <si>
+    <t>134900275</t>
+  </si>
+  <si>
+    <t>134910204</t>
+  </si>
+  <si>
+    <t>134911381</t>
+  </si>
+  <si>
+    <t>134910581</t>
+  </si>
+  <si>
+    <t>134914096</t>
+  </si>
+  <si>
+    <t>134930533</t>
+  </si>
+  <si>
+    <t>134864634</t>
+  </si>
+  <si>
+    <t>134859698</t>
+  </si>
+  <si>
+    <t>134947660</t>
+  </si>
+  <si>
+    <t>134970913</t>
+  </si>
+  <si>
+    <t>134772327</t>
+  </si>
+  <si>
+    <t>134777300</t>
+  </si>
+  <si>
+    <t>134762759</t>
+  </si>
+  <si>
+    <t>134934530</t>
+  </si>
+  <si>
+    <t>134980117</t>
+  </si>
+  <si>
+    <t>134811343</t>
+  </si>
+  <si>
+    <t>134862927</t>
+  </si>
+  <si>
+    <t>134855115</t>
+  </si>
+  <si>
+    <t>134842537</t>
+  </si>
+  <si>
+    <t>134908282</t>
+  </si>
+  <si>
+    <t>132527833</t>
+  </si>
+  <si>
+    <t>134855214</t>
+  </si>
+  <si>
+    <t>134912899</t>
+  </si>
+  <si>
+    <t>134907826</t>
+  </si>
+  <si>
+    <t>134906619</t>
+  </si>
+  <si>
+    <t>134754859</t>
+  </si>
+  <si>
+    <t>134754276</t>
+  </si>
+  <si>
+    <t>134820204</t>
+  </si>
+  <si>
+    <t>134932891</t>
+  </si>
+  <si>
+    <t>134912175</t>
+  </si>
+  <si>
+    <t>134912437</t>
+  </si>
+  <si>
+    <t>134862105</t>
+  </si>
+  <si>
+    <t>134993643</t>
+  </si>
+  <si>
+    <t>134987575</t>
+  </si>
+  <si>
+    <t>134990880</t>
+  </si>
+  <si>
+    <t>134991550</t>
+  </si>
+  <si>
+    <t>129887257</t>
+  </si>
+  <si>
+    <t>134993290</t>
+  </si>
+  <si>
+    <t>134832066</t>
+  </si>
+  <si>
+    <t>134858454</t>
+  </si>
+  <si>
+    <t>134838874</t>
+  </si>
+  <si>
+    <t>134839146</t>
+  </si>
+  <si>
+    <t>134839249</t>
+  </si>
+  <si>
+    <t>134841259</t>
+  </si>
+  <si>
+    <t>134842432</t>
+  </si>
+  <si>
+    <t>134848394</t>
+  </si>
+  <si>
+    <t>134849459</t>
+  </si>
+  <si>
+    <t>131353766</t>
+  </si>
+  <si>
+    <t>134994720</t>
+  </si>
+  <si>
+    <t>131996367</t>
+  </si>
+  <si>
+    <t>134853633</t>
+  </si>
+  <si>
+    <t>134854753</t>
+  </si>
+  <si>
+    <t>134855861</t>
+  </si>
+  <si>
+    <t>134995460</t>
+  </si>
+  <si>
+    <t>134858158</t>
+  </si>
+  <si>
+    <t>134858397</t>
+  </si>
+  <si>
+    <t>134858935</t>
+  </si>
+  <si>
+    <t>134859780</t>
+  </si>
+  <si>
+    <t>134863989</t>
+  </si>
+  <si>
+    <t>134867391</t>
+  </si>
+  <si>
+    <t>134867553</t>
+  </si>
+  <si>
+    <t>134867898</t>
+  </si>
+  <si>
+    <t>134868295</t>
+  </si>
+  <si>
+    <t>134870033</t>
+  </si>
+  <si>
+    <t>134813143</t>
+  </si>
+  <si>
+    <t>134821727</t>
+  </si>
+  <si>
+    <t>134821951</t>
+  </si>
+  <si>
+    <t>134822392</t>
+  </si>
+  <si>
+    <t>134822778</t>
+  </si>
+  <si>
+    <t>134823588</t>
+  </si>
+  <si>
+    <t>134824078</t>
+  </si>
+  <si>
+    <t>134824212</t>
+  </si>
+  <si>
+    <t>134827196</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_17.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 18.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_18.10.2025</t>
+  </si>
+  <si>
+    <t>134954804</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 19/10/2025</t>
+  </si>
+  <si>
+    <t>134932184</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_19.10.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +456,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -593,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -613,11 +517,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -930,7 +843,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -962,7 +875,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134716214</v>
+        <v>134882092</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -971,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -989,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -1007,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -1024,7 +937,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -1041,7 +954,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -1058,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -1075,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -1092,7 +1005,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -1126,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -1143,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1177,7 +1090,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1194,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1211,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1228,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1245,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1262,7 +1175,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1279,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1296,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1313,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1330,7 +1243,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1347,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1364,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1381,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1398,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1415,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1423,16 +1336,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1440,16 +1353,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1457,16 +1370,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1474,16 +1387,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1491,16 +1404,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1508,16 +1421,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1525,16 +1438,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1542,16 +1455,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1559,16 +1472,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1576,16 +1489,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1593,16 +1506,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1610,16 +1523,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1627,16 +1540,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1644,16 +1557,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1661,16 +1574,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1678,16 +1591,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1695,16 +1608,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1712,16 +1625,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1729,16 +1642,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1746,16 +1659,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1763,16 +1676,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1780,16 +1693,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1797,16 +1710,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1814,16 +1727,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1831,16 +1744,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1848,16 +1761,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1865,16 +1778,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1882,16 +1795,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1899,16 +1812,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1916,16 +1829,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1933,16 +1846,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1950,16 +1863,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1967,16 +1880,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1984,16 +1897,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -2001,16 +1914,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -2018,16 +1931,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -2035,16 +1948,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -2052,16 +1965,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -2069,16 +1982,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -2086,16 +1999,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -2103,16 +2016,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -2120,16 +2033,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2137,16 +2050,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2154,16 +2067,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2171,16 +2084,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2188,16 +2101,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2205,16 +2118,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2222,16 +2135,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2239,16 +2152,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2256,16 +2169,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2273,16 +2186,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2290,16 +2203,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2307,16 +2220,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2324,16 +2237,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2341,16 +2254,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2358,16 +2271,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
@@ -2375,16 +2288,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
@@ -2392,16 +2305,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
@@ -2409,16 +2322,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
@@ -2426,16 +2339,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
@@ -2443,16 +2356,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
@@ -2460,16 +2373,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
@@ -2477,16 +2390,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
@@ -2494,16 +2407,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
@@ -2511,16 +2424,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
@@ -2528,16 +2441,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
@@ -2545,16 +2458,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
@@ -2562,16 +2475,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
@@ -2579,16 +2492,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
@@ -2596,16 +2509,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
@@ -2613,16 +2526,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
@@ -2630,16 +2543,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
@@ -2647,16 +2560,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
@@ -2664,16 +2577,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
@@ -2681,16 +2594,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
@@ -2698,16 +2611,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>6</v>
@@ -2715,16 +2628,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>6</v>
@@ -2732,16 +2645,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>6</v>
@@ -2755,10 +2668,10 @@
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>6</v>
@@ -2766,16 +2679,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
@@ -2783,16 +2696,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>6</v>
@@ -2800,16 +2713,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>6</v>
@@ -2817,16 +2730,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>6</v>
@@ -2834,16 +2747,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>6</v>
@@ -2851,16 +2764,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>6</v>
@@ -2868,16 +2781,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>6</v>
@@ -2885,16 +2798,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>6</v>
@@ -2902,135 +2815,135 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="2">
+        <v>134778039</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="D117" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="2">
+        <v>134803049</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="E118" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>128</v>
+      <c r="A119" s="2">
+        <v>134888932</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>116</v>
+      <c r="C119" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>129</v>
+      <c r="A120" s="2">
+        <v>134898424</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>116</v>
+      <c r="C120" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>130</v>
+      <c r="A121" s="2">
+        <v>134802880</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>116</v>
+      <c r="C121" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>131</v>
+      <c r="A122" s="2">
+        <v>134880167</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>116</v>
+      <c r="C122" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>132</v>
+      <c r="A123" s="2">
+        <v>134889091</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>116</v>
+      <c r="C123" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>6</v>
@@ -3038,16 +2951,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>6</v>
@@ -3055,534 +2968,27 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E155" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A117:A123">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -3594,31 +3000,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F5E03-618A-4675-80FB-CF7D072160FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F697EE7E-7E4F-4499-AFD8-7D380A511E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="83">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,383 +54,236 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 20.10.2025</t>
-  </si>
-  <si>
-    <t>134920719</t>
-  </si>
-  <si>
-    <t>134949135</t>
-  </si>
-  <si>
-    <t>134950206</t>
-  </si>
-  <si>
-    <t>134955442</t>
-  </si>
-  <si>
-    <t>134948725</t>
-  </si>
-  <si>
-    <t>134947549</t>
-  </si>
-  <si>
-    <t>134948737</t>
-  </si>
-  <si>
-    <t>134947654</t>
-  </si>
-  <si>
-    <t>134941125</t>
-  </si>
-  <si>
-    <t>134955110</t>
-  </si>
-  <si>
-    <t>134994698</t>
-  </si>
-  <si>
-    <t>134997966</t>
-  </si>
-  <si>
-    <t>134995137</t>
-  </si>
-  <si>
-    <t>132101065</t>
-  </si>
-  <si>
-    <t>134926039</t>
-  </si>
-  <si>
-    <t>134903793</t>
-  </si>
-  <si>
-    <t>134938071</t>
-  </si>
-  <si>
-    <t>132723100</t>
-  </si>
-  <si>
-    <t>134940370</t>
-  </si>
-  <si>
-    <t>134902146</t>
-  </si>
-  <si>
-    <t>134924142</t>
-  </si>
-  <si>
-    <t>135008133</t>
-  </si>
-  <si>
-    <t>134938047</t>
-  </si>
-  <si>
-    <t>134950794</t>
-  </si>
-  <si>
-    <t>135013302</t>
-  </si>
-  <si>
-    <t>135016647</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_20.10.2025</t>
-  </si>
-  <si>
-    <t>134779137</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 17/10/2025</t>
-  </si>
-  <si>
-    <t>134814811</t>
-  </si>
-  <si>
-    <t>134824003</t>
-  </si>
-  <si>
-    <t>134825564</t>
-  </si>
-  <si>
-    <t>133453537</t>
-  </si>
-  <si>
-    <t>134839316</t>
-  </si>
-  <si>
-    <t>134833199</t>
-  </si>
-  <si>
-    <t>134836495</t>
-  </si>
-  <si>
-    <t>134853205</t>
-  </si>
-  <si>
-    <t>134852522</t>
-  </si>
-  <si>
-    <t>134852584</t>
-  </si>
-  <si>
-    <t>134858817</t>
-  </si>
-  <si>
-    <t>134883844</t>
-  </si>
-  <si>
-    <t>134892837</t>
-  </si>
-  <si>
-    <t>134881725</t>
-  </si>
-  <si>
-    <t>134900275</t>
-  </si>
-  <si>
-    <t>134910204</t>
-  </si>
-  <si>
-    <t>134911381</t>
-  </si>
-  <si>
-    <t>134910581</t>
-  </si>
-  <si>
-    <t>134914096</t>
-  </si>
-  <si>
-    <t>134930533</t>
-  </si>
-  <si>
-    <t>134864634</t>
-  </si>
-  <si>
-    <t>134859698</t>
-  </si>
-  <si>
-    <t>134947660</t>
-  </si>
-  <si>
-    <t>134970913</t>
-  </si>
-  <si>
-    <t>134772327</t>
-  </si>
-  <si>
-    <t>134777300</t>
-  </si>
-  <si>
-    <t>134762759</t>
-  </si>
-  <si>
-    <t>134934530</t>
-  </si>
-  <si>
-    <t>134980117</t>
-  </si>
-  <si>
-    <t>134811343</t>
-  </si>
-  <si>
-    <t>134862927</t>
-  </si>
-  <si>
-    <t>134855115</t>
-  </si>
-  <si>
-    <t>134842537</t>
-  </si>
-  <si>
-    <t>134908282</t>
-  </si>
-  <si>
-    <t>132527833</t>
-  </si>
-  <si>
-    <t>134855214</t>
-  </si>
-  <si>
-    <t>134912899</t>
-  </si>
-  <si>
-    <t>134907826</t>
-  </si>
-  <si>
-    <t>134906619</t>
-  </si>
-  <si>
-    <t>134754859</t>
-  </si>
-  <si>
-    <t>134754276</t>
-  </si>
-  <si>
-    <t>134820204</t>
-  </si>
-  <si>
-    <t>134932891</t>
-  </si>
-  <si>
-    <t>134912175</t>
-  </si>
-  <si>
-    <t>134912437</t>
-  </si>
-  <si>
-    <t>134862105</t>
-  </si>
-  <si>
-    <t>134993643</t>
-  </si>
-  <si>
-    <t>134987575</t>
-  </si>
-  <si>
-    <t>134990880</t>
-  </si>
-  <si>
-    <t>134991550</t>
-  </si>
-  <si>
-    <t>129887257</t>
-  </si>
-  <si>
-    <t>134993290</t>
-  </si>
-  <si>
-    <t>134832066</t>
-  </si>
-  <si>
-    <t>134858454</t>
-  </si>
-  <si>
-    <t>134838874</t>
-  </si>
-  <si>
-    <t>134839146</t>
-  </si>
-  <si>
-    <t>134839249</t>
-  </si>
-  <si>
-    <t>134841259</t>
-  </si>
-  <si>
-    <t>134842432</t>
-  </si>
-  <si>
-    <t>134848394</t>
-  </si>
-  <si>
-    <t>134849459</t>
-  </si>
-  <si>
-    <t>131353766</t>
-  </si>
-  <si>
-    <t>134994720</t>
-  </si>
-  <si>
-    <t>131996367</t>
-  </si>
-  <si>
-    <t>134853633</t>
-  </si>
-  <si>
-    <t>134854753</t>
-  </si>
-  <si>
-    <t>134855861</t>
-  </si>
-  <si>
-    <t>134995460</t>
-  </si>
-  <si>
-    <t>134858158</t>
-  </si>
-  <si>
-    <t>134858397</t>
-  </si>
-  <si>
-    <t>134858935</t>
-  </si>
-  <si>
-    <t>134859780</t>
-  </si>
-  <si>
-    <t>134863989</t>
-  </si>
-  <si>
-    <t>134867391</t>
-  </si>
-  <si>
-    <t>134867553</t>
-  </si>
-  <si>
-    <t>134867898</t>
-  </si>
-  <si>
-    <t>134868295</t>
-  </si>
-  <si>
-    <t>134870033</t>
-  </si>
-  <si>
-    <t>134813143</t>
-  </si>
-  <si>
-    <t>134821727</t>
-  </si>
-  <si>
-    <t>134821951</t>
-  </si>
-  <si>
-    <t>134822392</t>
-  </si>
-  <si>
-    <t>134822778</t>
-  </si>
-  <si>
-    <t>134823588</t>
-  </si>
-  <si>
-    <t>134824078</t>
-  </si>
-  <si>
-    <t>134824212</t>
-  </si>
-  <si>
-    <t>134827196</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_17.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 18.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_18.10.2025</t>
-  </si>
-  <si>
-    <t>134954804</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 19/10/2025</t>
-  </si>
-  <si>
-    <t>134932184</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_19.10.2025</t>
+    <t>Relatório de Recusa Sicredi 21.10.2025</t>
+  </si>
+  <si>
+    <t>134835126</t>
+  </si>
+  <si>
+    <t>134870826</t>
+  </si>
+  <si>
+    <t>134881477</t>
+  </si>
+  <si>
+    <t>134890457</t>
+  </si>
+  <si>
+    <t>134886104</t>
+  </si>
+  <si>
+    <t>134888870</t>
+  </si>
+  <si>
+    <t>134892433</t>
+  </si>
+  <si>
+    <t>134881130</t>
+  </si>
+  <si>
+    <t>134892144</t>
+  </si>
+  <si>
+    <t>134904234</t>
+  </si>
+  <si>
+    <t>134903186</t>
+  </si>
+  <si>
+    <t>134913988</t>
+  </si>
+  <si>
+    <t>134916658</t>
+  </si>
+  <si>
+    <t>134921827</t>
+  </si>
+  <si>
+    <t>134929908</t>
+  </si>
+  <si>
+    <t>134950111</t>
+  </si>
+  <si>
+    <t>134940595</t>
+  </si>
+  <si>
+    <t>134958354</t>
+  </si>
+  <si>
+    <t>134970284</t>
+  </si>
+  <si>
+    <t>134975936</t>
+  </si>
+  <si>
+    <t>134966840</t>
+  </si>
+  <si>
+    <t>134981751</t>
+  </si>
+  <si>
+    <t>134994739</t>
+  </si>
+  <si>
+    <t>134930766</t>
+  </si>
+  <si>
+    <t>134981760</t>
+  </si>
+  <si>
+    <t>134934159</t>
+  </si>
+  <si>
+    <t>135016025</t>
+  </si>
+  <si>
+    <t>135011067</t>
+  </si>
+  <si>
+    <t>134798093</t>
+  </si>
+  <si>
+    <t>134798189</t>
+  </si>
+  <si>
+    <t>134900949</t>
+  </si>
+  <si>
+    <t>134931937</t>
+  </si>
+  <si>
+    <t>135023624</t>
+  </si>
+  <si>
+    <t>134909114</t>
+  </si>
+  <si>
+    <t>134913976</t>
+  </si>
+  <si>
+    <t>134832423</t>
+  </si>
+  <si>
+    <t>135022701</t>
+  </si>
+  <si>
+    <t>134861117</t>
+  </si>
+  <si>
+    <t>133038530</t>
+  </si>
+  <si>
+    <t>135028852</t>
+  </si>
+  <si>
+    <t>134867129</t>
+  </si>
+  <si>
+    <t>134885228</t>
+  </si>
+  <si>
+    <t>133284346</t>
+  </si>
+  <si>
+    <t>135027036</t>
+  </si>
+  <si>
+    <t>130496860</t>
+  </si>
+  <si>
+    <t>130725874</t>
+  </si>
+  <si>
+    <t>131369526</t>
+  </si>
+  <si>
+    <t>133121298</t>
+  </si>
+  <si>
+    <t>134421709</t>
+  </si>
+  <si>
+    <t>134873684</t>
+  </si>
+  <si>
+    <t>134792714</t>
+  </si>
+  <si>
+    <t>134890334</t>
+  </si>
+  <si>
+    <t>134879191</t>
+  </si>
+  <si>
+    <t>134879281</t>
+  </si>
+  <si>
+    <t>134873581</t>
+  </si>
+  <si>
+    <t>134907690</t>
+  </si>
+  <si>
+    <t>134880037</t>
+  </si>
+  <si>
+    <t>134882343</t>
+  </si>
+  <si>
+    <t>134882443</t>
+  </si>
+  <si>
+    <t>134883954</t>
+  </si>
+  <si>
+    <t>134885990</t>
+  </si>
+  <si>
+    <t>134887459</t>
+  </si>
+  <si>
+    <t>134888193</t>
+  </si>
+  <si>
+    <t>134888259</t>
+  </si>
+  <si>
+    <t>134888768</t>
+  </si>
+  <si>
+    <t>134889853</t>
+  </si>
+  <si>
+    <t>134890330</t>
+  </si>
+  <si>
+    <t>135037026</t>
+  </si>
+  <si>
+    <t>134900971</t>
+  </si>
+  <si>
+    <t>134905665</t>
+  </si>
+  <si>
+    <t>134908133</t>
+  </si>
+  <si>
+    <t>134815556</t>
+  </si>
+  <si>
+    <t>134941410</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_21.10.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,12 +309,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -497,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -517,20 +364,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -843,7 +681,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -875,7 +713,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134882092</v>
+        <v>134823722</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -884,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -902,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -920,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -937,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -954,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -971,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -988,7 +826,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -1005,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -1022,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -1039,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -1056,7 +894,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1073,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1090,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1107,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1124,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1141,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1158,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1175,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1192,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1209,7 +1047,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1226,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1243,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1260,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1277,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1294,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1311,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1328,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1336,16 +1174,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1353,16 +1191,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1370,16 +1208,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1387,16 +1225,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1404,16 +1242,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1421,16 +1259,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1438,16 +1276,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1455,16 +1293,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1472,16 +1310,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1489,16 +1327,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1506,16 +1344,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1523,16 +1361,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1540,16 +1378,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1557,16 +1395,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1574,16 +1412,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1591,16 +1429,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1608,16 +1446,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1625,16 +1463,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1642,16 +1480,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1659,16 +1497,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1676,16 +1514,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1693,16 +1531,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1710,16 +1548,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1727,16 +1565,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1744,16 +1582,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1761,16 +1599,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1778,16 +1616,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1795,16 +1633,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1812,16 +1650,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1829,16 +1667,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1846,16 +1684,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1863,16 +1701,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1880,16 +1718,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1897,16 +1735,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1914,16 +1752,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1931,16 +1769,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1948,16 +1786,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1965,16 +1803,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1982,16 +1820,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1999,16 +1837,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -2016,16 +1854,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -2033,16 +1871,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2050,16 +1888,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2067,16 +1905,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2084,16 +1922,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2101,16 +1939,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2118,877 +1956,24 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
-        <v>134778039</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>134803049</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>134888932</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>134898424</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>134802880</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>134880167</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>134889091</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E125" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A117:A123">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -3000,31 +1985,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F697EE7E-7E4F-4499-AFD8-7D380A511E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11D4193-6995-4560-83B4-99C9C7803DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="78">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,229 +54,214 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 21.10.2025</t>
-  </si>
-  <si>
-    <t>134835126</t>
-  </si>
-  <si>
-    <t>134870826</t>
-  </si>
-  <si>
-    <t>134881477</t>
-  </si>
-  <si>
-    <t>134890457</t>
-  </si>
-  <si>
-    <t>134886104</t>
-  </si>
-  <si>
-    <t>134888870</t>
-  </si>
-  <si>
-    <t>134892433</t>
-  </si>
-  <si>
-    <t>134881130</t>
-  </si>
-  <si>
-    <t>134892144</t>
-  </si>
-  <si>
-    <t>134904234</t>
-  </si>
-  <si>
-    <t>134903186</t>
-  </si>
-  <si>
-    <t>134913988</t>
-  </si>
-  <si>
-    <t>134916658</t>
-  </si>
-  <si>
-    <t>134921827</t>
-  </si>
-  <si>
-    <t>134929908</t>
-  </si>
-  <si>
-    <t>134950111</t>
-  </si>
-  <si>
-    <t>134940595</t>
-  </si>
-  <si>
-    <t>134958354</t>
-  </si>
-  <si>
-    <t>134970284</t>
-  </si>
-  <si>
-    <t>134975936</t>
-  </si>
-  <si>
-    <t>134966840</t>
-  </si>
-  <si>
-    <t>134981751</t>
-  </si>
-  <si>
-    <t>134994739</t>
-  </si>
-  <si>
-    <t>134930766</t>
-  </si>
-  <si>
-    <t>134981760</t>
-  </si>
-  <si>
-    <t>134934159</t>
-  </si>
-  <si>
-    <t>135016025</t>
-  </si>
-  <si>
-    <t>135011067</t>
-  </si>
-  <si>
-    <t>134798093</t>
-  </si>
-  <si>
-    <t>134798189</t>
-  </si>
-  <si>
-    <t>134900949</t>
-  </si>
-  <si>
-    <t>134931937</t>
-  </si>
-  <si>
-    <t>135023624</t>
-  </si>
-  <si>
-    <t>134909114</t>
-  </si>
-  <si>
-    <t>134913976</t>
-  </si>
-  <si>
-    <t>134832423</t>
-  </si>
-  <si>
-    <t>135022701</t>
-  </si>
-  <si>
-    <t>134861117</t>
-  </si>
-  <si>
-    <t>133038530</t>
-  </si>
-  <si>
-    <t>135028852</t>
-  </si>
-  <si>
-    <t>134867129</t>
-  </si>
-  <si>
-    <t>134885228</t>
-  </si>
-  <si>
-    <t>133284346</t>
-  </si>
-  <si>
-    <t>135027036</t>
-  </si>
-  <si>
-    <t>130496860</t>
-  </si>
-  <si>
-    <t>130725874</t>
-  </si>
-  <si>
-    <t>131369526</t>
-  </si>
-  <si>
-    <t>133121298</t>
-  </si>
-  <si>
-    <t>134421709</t>
-  </si>
-  <si>
-    <t>134873684</t>
-  </si>
-  <si>
-    <t>134792714</t>
-  </si>
-  <si>
-    <t>134890334</t>
-  </si>
-  <si>
-    <t>134879191</t>
-  </si>
-  <si>
-    <t>134879281</t>
-  </si>
-  <si>
-    <t>134873581</t>
-  </si>
-  <si>
-    <t>134907690</t>
-  </si>
-  <si>
-    <t>134880037</t>
-  </si>
-  <si>
-    <t>134882343</t>
-  </si>
-  <si>
-    <t>134882443</t>
-  </si>
-  <si>
-    <t>134883954</t>
-  </si>
-  <si>
-    <t>134885990</t>
-  </si>
-  <si>
-    <t>134887459</t>
-  </si>
-  <si>
-    <t>134888193</t>
-  </si>
-  <si>
-    <t>134888259</t>
-  </si>
-  <si>
-    <t>134888768</t>
-  </si>
-  <si>
-    <t>134889853</t>
-  </si>
-  <si>
-    <t>134890330</t>
-  </si>
-  <si>
-    <t>135037026</t>
-  </si>
-  <si>
-    <t>134900971</t>
-  </si>
-  <si>
-    <t>134905665</t>
-  </si>
-  <si>
-    <t>134908133</t>
-  </si>
-  <si>
-    <t>134815556</t>
-  </si>
-  <si>
-    <t>134941410</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_21.10.2025</t>
+    <t>Relatório de Recusa Sicredi 22.10.2025</t>
+  </si>
+  <si>
+    <t>134804428</t>
+  </si>
+  <si>
+    <t>133928289</t>
+  </si>
+  <si>
+    <t>134919705</t>
+  </si>
+  <si>
+    <t>134930573</t>
+  </si>
+  <si>
+    <t>134924207</t>
+  </si>
+  <si>
+    <t>134926675</t>
+  </si>
+  <si>
+    <t>134934466</t>
+  </si>
+  <si>
+    <t>134932688</t>
+  </si>
+  <si>
+    <t>134929317</t>
+  </si>
+  <si>
+    <t>134945343</t>
+  </si>
+  <si>
+    <t>134954769</t>
+  </si>
+  <si>
+    <t>134951396</t>
+  </si>
+  <si>
+    <t>134925335</t>
+  </si>
+  <si>
+    <t>134918464</t>
+  </si>
+  <si>
+    <t>134959387</t>
+  </si>
+  <si>
+    <t>134963932</t>
+  </si>
+  <si>
+    <t>134966726</t>
+  </si>
+  <si>
+    <t>134974339</t>
+  </si>
+  <si>
+    <t>134981207</t>
+  </si>
+  <si>
+    <t>134981626</t>
+  </si>
+  <si>
+    <t>134993812</t>
+  </si>
+  <si>
+    <t>134980266</t>
+  </si>
+  <si>
+    <t>134987080</t>
+  </si>
+  <si>
+    <t>134992658</t>
+  </si>
+  <si>
+    <t>134886239</t>
+  </si>
+  <si>
+    <t>135016293</t>
+  </si>
+  <si>
+    <t>135015597</t>
+  </si>
+  <si>
+    <t>134927007</t>
+  </si>
+  <si>
+    <t>134974614</t>
+  </si>
+  <si>
+    <t>135038663</t>
+  </si>
+  <si>
+    <t>135037546</t>
+  </si>
+  <si>
+    <t>134833397</t>
+  </si>
+  <si>
+    <t>134838871</t>
+  </si>
+  <si>
+    <t>134840672</t>
+  </si>
+  <si>
+    <t>134858541</t>
+  </si>
+  <si>
+    <t>131578702</t>
+  </si>
+  <si>
+    <t>130956880</t>
+  </si>
+  <si>
+    <t>133952637</t>
+  </si>
+  <si>
+    <t>135023851</t>
+  </si>
+  <si>
+    <t>135045320</t>
+  </si>
+  <si>
+    <t>134933562</t>
+  </si>
+  <si>
+    <t>133559080</t>
+  </si>
+  <si>
+    <t>134947982</t>
+  </si>
+  <si>
+    <t>131154405</t>
+  </si>
+  <si>
+    <t>134967988</t>
+  </si>
+  <si>
+    <t>134926661</t>
+  </si>
+  <si>
+    <t>134881214</t>
+  </si>
+  <si>
+    <t>135049014</t>
+  </si>
+  <si>
+    <t>135053435</t>
+  </si>
+  <si>
+    <t>135054884</t>
+  </si>
+  <si>
+    <t>134919702</t>
+  </si>
+  <si>
+    <t>135052355</t>
+  </si>
+  <si>
+    <t>134924511</t>
+  </si>
+  <si>
+    <t>134919254</t>
+  </si>
+  <si>
+    <t>134919532</t>
+  </si>
+  <si>
+    <t>134949899</t>
+  </si>
+  <si>
+    <t>134923906</t>
+  </si>
+  <si>
+    <t>134928254</t>
+  </si>
+  <si>
+    <t>134930164</t>
+  </si>
+  <si>
+    <t>134930565</t>
+  </si>
+  <si>
+    <t>134930664</t>
+  </si>
+  <si>
+    <t>134931545</t>
+  </si>
+  <si>
+    <t>134932982</t>
+  </si>
+  <si>
+    <t>134933614</t>
+  </si>
+  <si>
+    <t>134990946</t>
+  </si>
+  <si>
+    <t>135057871</t>
+  </si>
+  <si>
+    <t>134976445</t>
+  </si>
+  <si>
+    <t>134840628</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.10.2025</t>
   </si>
 </sst>
 </file>
@@ -681,7 +666,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -713,7 +698,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134823722</v>
+        <v>130388847</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -722,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -740,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -758,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -775,7 +760,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -792,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -809,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -826,7 +811,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -843,7 +828,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -860,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -877,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -894,7 +879,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -911,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -928,7 +913,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -945,7 +930,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -962,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -979,7 +964,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -996,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1013,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1030,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1047,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1081,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1098,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1132,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1149,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1151,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1183,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1200,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1234,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1251,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1268,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1285,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1302,7 +1287,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1319,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1336,7 +1321,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1353,7 +1338,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1370,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1387,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1404,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1421,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1438,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1455,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1472,7 +1457,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1489,7 +1474,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1506,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1523,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1540,7 +1525,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1557,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1574,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1591,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1608,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1625,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1642,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1659,7 +1644,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1676,7 +1661,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1693,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1710,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1727,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1744,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1761,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1778,7 +1763,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1795,7 +1780,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1812,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1829,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1846,7 +1831,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -1863,7 +1848,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -1880,94 +1865,9 @@
         <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1985,31 +1885,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11D4193-6995-4560-83B4-99C9C7803DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B79BE86-76B5-4486-BCD2-E53557D00DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,214 +54,214 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 22.10.2025</t>
-  </si>
-  <si>
-    <t>134804428</t>
-  </si>
-  <si>
-    <t>133928289</t>
-  </si>
-  <si>
-    <t>134919705</t>
-  </si>
-  <si>
-    <t>134930573</t>
-  </si>
-  <si>
-    <t>134924207</t>
-  </si>
-  <si>
-    <t>134926675</t>
-  </si>
-  <si>
-    <t>134934466</t>
-  </si>
-  <si>
-    <t>134932688</t>
-  </si>
-  <si>
-    <t>134929317</t>
-  </si>
-  <si>
-    <t>134945343</t>
-  </si>
-  <si>
-    <t>134954769</t>
-  </si>
-  <si>
-    <t>134951396</t>
-  </si>
-  <si>
-    <t>134925335</t>
-  </si>
-  <si>
-    <t>134918464</t>
-  </si>
-  <si>
-    <t>134959387</t>
-  </si>
-  <si>
-    <t>134963932</t>
-  </si>
-  <si>
-    <t>134966726</t>
-  </si>
-  <si>
-    <t>134974339</t>
-  </si>
-  <si>
-    <t>134981207</t>
-  </si>
-  <si>
-    <t>134981626</t>
-  </si>
-  <si>
-    <t>134993812</t>
-  </si>
-  <si>
-    <t>134980266</t>
-  </si>
-  <si>
-    <t>134987080</t>
-  </si>
-  <si>
-    <t>134992658</t>
-  </si>
-  <si>
-    <t>134886239</t>
-  </si>
-  <si>
-    <t>135016293</t>
-  </si>
-  <si>
-    <t>135015597</t>
-  </si>
-  <si>
-    <t>134927007</t>
-  </si>
-  <si>
-    <t>134974614</t>
-  </si>
-  <si>
-    <t>135038663</t>
-  </si>
-  <si>
-    <t>135037546</t>
-  </si>
-  <si>
-    <t>134833397</t>
-  </si>
-  <si>
-    <t>134838871</t>
-  </si>
-  <si>
-    <t>134840672</t>
-  </si>
-  <si>
-    <t>134858541</t>
-  </si>
-  <si>
-    <t>131578702</t>
-  </si>
-  <si>
-    <t>130956880</t>
-  </si>
-  <si>
-    <t>133952637</t>
-  </si>
-  <si>
-    <t>135023851</t>
-  </si>
-  <si>
-    <t>135045320</t>
-  </si>
-  <si>
-    <t>134933562</t>
-  </si>
-  <si>
-    <t>133559080</t>
-  </si>
-  <si>
-    <t>134947982</t>
-  </si>
-  <si>
-    <t>131154405</t>
-  </si>
-  <si>
-    <t>134967988</t>
-  </si>
-  <si>
-    <t>134926661</t>
-  </si>
-  <si>
-    <t>134881214</t>
-  </si>
-  <si>
-    <t>135049014</t>
-  </si>
-  <si>
-    <t>135053435</t>
-  </si>
-  <si>
-    <t>135054884</t>
-  </si>
-  <si>
-    <t>134919702</t>
-  </si>
-  <si>
-    <t>135052355</t>
-  </si>
-  <si>
-    <t>134924511</t>
-  </si>
-  <si>
-    <t>134919254</t>
-  </si>
-  <si>
-    <t>134919532</t>
-  </si>
-  <si>
-    <t>134949899</t>
-  </si>
-  <si>
-    <t>134923906</t>
-  </si>
-  <si>
-    <t>134928254</t>
-  </si>
-  <si>
-    <t>134930164</t>
-  </si>
-  <si>
-    <t>134930565</t>
-  </si>
-  <si>
-    <t>134930664</t>
-  </si>
-  <si>
-    <t>134931545</t>
-  </si>
-  <si>
-    <t>134932982</t>
-  </si>
-  <si>
-    <t>134933614</t>
-  </si>
-  <si>
-    <t>134990946</t>
-  </si>
-  <si>
-    <t>135057871</t>
-  </si>
-  <si>
-    <t>134976445</t>
-  </si>
-  <si>
-    <t>134840628</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.10.2025</t>
+    <t>Relatório de Recusa Sicredi 23.10.2025</t>
+  </si>
+  <si>
+    <t>131182054</t>
+  </si>
+  <si>
+    <t>134911984</t>
+  </si>
+  <si>
+    <t>134913587</t>
+  </si>
+  <si>
+    <t>134944369</t>
+  </si>
+  <si>
+    <t>134938790</t>
+  </si>
+  <si>
+    <t>134939522</t>
+  </si>
+  <si>
+    <t>134952745</t>
+  </si>
+  <si>
+    <t>134938343</t>
+  </si>
+  <si>
+    <t>134955100</t>
+  </si>
+  <si>
+    <t>134946448</t>
+  </si>
+  <si>
+    <t>134961010</t>
+  </si>
+  <si>
+    <t>134986103</t>
+  </si>
+  <si>
+    <t>134938266</t>
+  </si>
+  <si>
+    <t>134994389</t>
+  </si>
+  <si>
+    <t>134998414</t>
+  </si>
+  <si>
+    <t>135012742</t>
+  </si>
+  <si>
+    <t>135015642</t>
+  </si>
+  <si>
+    <t>135015098</t>
+  </si>
+  <si>
+    <t>133000281</t>
+  </si>
+  <si>
+    <t>134999102</t>
+  </si>
+  <si>
+    <t>134965189</t>
+  </si>
+  <si>
+    <t>135033201</t>
+  </si>
+  <si>
+    <t>135040695</t>
+  </si>
+  <si>
+    <t>135040498</t>
+  </si>
+  <si>
+    <t>135030248</t>
+  </si>
+  <si>
+    <t>135044282</t>
+  </si>
+  <si>
+    <t>135046061</t>
+  </si>
+  <si>
+    <t>135058399</t>
+  </si>
+  <si>
+    <t>135059504</t>
+  </si>
+  <si>
+    <t>135059421</t>
+  </si>
+  <si>
+    <t>135043503</t>
+  </si>
+  <si>
+    <t>135045804</t>
+  </si>
+  <si>
+    <t>135055248</t>
+  </si>
+  <si>
+    <t>134854588</t>
+  </si>
+  <si>
+    <t>134863704</t>
+  </si>
+  <si>
+    <t>134866461</t>
+  </si>
+  <si>
+    <t>134867551</t>
+  </si>
+  <si>
+    <t>134869484</t>
+  </si>
+  <si>
+    <t>134886427</t>
+  </si>
+  <si>
+    <t>134883780</t>
+  </si>
+  <si>
+    <t>132137878</t>
+  </si>
+  <si>
+    <t>134885076</t>
+  </si>
+  <si>
+    <t>135066098</t>
+  </si>
+  <si>
+    <t>134955710</t>
+  </si>
+  <si>
+    <t>134982929</t>
+  </si>
+  <si>
+    <t>134998639</t>
+  </si>
+  <si>
+    <t>134877071</t>
+  </si>
+  <si>
+    <t>135068402</t>
+  </si>
+  <si>
+    <t>135068533</t>
+  </si>
+  <si>
+    <t>135068532</t>
+  </si>
+  <si>
+    <t>135070318</t>
+  </si>
+  <si>
+    <t>134948045</t>
+  </si>
+  <si>
+    <t>133311618</t>
+  </si>
+  <si>
+    <t>135071440</t>
+  </si>
+  <si>
+    <t>135017687</t>
+  </si>
+  <si>
+    <t>134993330</t>
+  </si>
+  <si>
+    <t>134989780</t>
+  </si>
+  <si>
+    <t>134981880</t>
+  </si>
+  <si>
+    <t>133609393</t>
+  </si>
+  <si>
+    <t>134942068</t>
+  </si>
+  <si>
+    <t>134947094</t>
+  </si>
+  <si>
+    <t>134947919</t>
+  </si>
+  <si>
+    <t>134208028</t>
+  </si>
+  <si>
+    <t>134950384</t>
+  </si>
+  <si>
+    <t>134950987</t>
+  </si>
+  <si>
+    <t>134942125</t>
+  </si>
+  <si>
+    <t>135079975</t>
+  </si>
+  <si>
+    <t>135079145</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_23.10.2025</t>
   </si>
 </sst>
 </file>
@@ -698,7 +698,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130388847</v>
+        <v>132618037</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1885,31 +1885,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B79BE86-76B5-4486-BCD2-E53557D00DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203EEA43-D609-46A6-832A-ABC14BE45B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,214 +54,169 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 23.10.2025</t>
-  </si>
-  <si>
-    <t>131182054</t>
-  </si>
-  <si>
-    <t>134911984</t>
-  </si>
-  <si>
-    <t>134913587</t>
-  </si>
-  <si>
-    <t>134944369</t>
-  </si>
-  <si>
-    <t>134938790</t>
-  </si>
-  <si>
-    <t>134939522</t>
-  </si>
-  <si>
-    <t>134952745</t>
-  </si>
-  <si>
-    <t>134938343</t>
-  </si>
-  <si>
-    <t>134955100</t>
-  </si>
-  <si>
-    <t>134946448</t>
-  </si>
-  <si>
-    <t>134961010</t>
-  </si>
-  <si>
-    <t>134986103</t>
-  </si>
-  <si>
-    <t>134938266</t>
-  </si>
-  <si>
-    <t>134994389</t>
-  </si>
-  <si>
-    <t>134998414</t>
-  </si>
-  <si>
-    <t>135012742</t>
-  </si>
-  <si>
-    <t>135015642</t>
-  </si>
-  <si>
-    <t>135015098</t>
-  </si>
-  <si>
-    <t>133000281</t>
-  </si>
-  <si>
-    <t>134999102</t>
-  </si>
-  <si>
-    <t>134965189</t>
-  </si>
-  <si>
-    <t>135033201</t>
-  </si>
-  <si>
-    <t>135040695</t>
-  </si>
-  <si>
-    <t>135040498</t>
-  </si>
-  <si>
-    <t>135030248</t>
-  </si>
-  <si>
-    <t>135044282</t>
-  </si>
-  <si>
-    <t>135046061</t>
-  </si>
-  <si>
-    <t>135058399</t>
-  </si>
-  <si>
-    <t>135059504</t>
-  </si>
-  <si>
-    <t>135059421</t>
-  </si>
-  <si>
-    <t>135043503</t>
-  </si>
-  <si>
-    <t>135045804</t>
-  </si>
-  <si>
-    <t>135055248</t>
-  </si>
-  <si>
-    <t>134854588</t>
-  </si>
-  <si>
-    <t>134863704</t>
-  </si>
-  <si>
-    <t>134866461</t>
-  </si>
-  <si>
-    <t>134867551</t>
-  </si>
-  <si>
-    <t>134869484</t>
-  </si>
-  <si>
-    <t>134886427</t>
-  </si>
-  <si>
-    <t>134883780</t>
-  </si>
-  <si>
-    <t>132137878</t>
-  </si>
-  <si>
-    <t>134885076</t>
-  </si>
-  <si>
-    <t>135066098</t>
-  </si>
-  <si>
-    <t>134955710</t>
-  </si>
-  <si>
-    <t>134982929</t>
-  </si>
-  <si>
-    <t>134998639</t>
-  </si>
-  <si>
-    <t>134877071</t>
-  </si>
-  <si>
-    <t>135068402</t>
-  </si>
-  <si>
-    <t>135068533</t>
-  </si>
-  <si>
-    <t>135068532</t>
-  </si>
-  <si>
-    <t>135070318</t>
-  </si>
-  <si>
-    <t>134948045</t>
-  </si>
-  <si>
-    <t>133311618</t>
-  </si>
-  <si>
-    <t>135071440</t>
-  </si>
-  <si>
-    <t>135017687</t>
-  </si>
-  <si>
-    <t>134993330</t>
-  </si>
-  <si>
-    <t>134989780</t>
-  </si>
-  <si>
-    <t>134981880</t>
-  </si>
-  <si>
-    <t>133609393</t>
-  </si>
-  <si>
-    <t>134942068</t>
-  </si>
-  <si>
-    <t>134947094</t>
-  </si>
-  <si>
-    <t>134947919</t>
-  </si>
-  <si>
-    <t>134208028</t>
-  </si>
-  <si>
-    <t>134950384</t>
-  </si>
-  <si>
-    <t>134950987</t>
-  </si>
-  <si>
-    <t>134942125</t>
-  </si>
-  <si>
-    <t>135079975</t>
-  </si>
-  <si>
-    <t>135079145</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_23.10.2025</t>
+    <t>Relatório de Recusa Sicredi 24.10.2025</t>
+  </si>
+  <si>
+    <t>134887092</t>
+  </si>
+  <si>
+    <t>134903304</t>
+  </si>
+  <si>
+    <t>134875386</t>
+  </si>
+  <si>
+    <t>134950299</t>
+  </si>
+  <si>
+    <t>134967981</t>
+  </si>
+  <si>
+    <t>134958842</t>
+  </si>
+  <si>
+    <t>134964619</t>
+  </si>
+  <si>
+    <t>134973064</t>
+  </si>
+  <si>
+    <t>134958351</t>
+  </si>
+  <si>
+    <t>134968489</t>
+  </si>
+  <si>
+    <t>134988642</t>
+  </si>
+  <si>
+    <t>134996089</t>
+  </si>
+  <si>
+    <t>135008057</t>
+  </si>
+  <si>
+    <t>135007411</t>
+  </si>
+  <si>
+    <t>135006207</t>
+  </si>
+  <si>
+    <t>135038050</t>
+  </si>
+  <si>
+    <t>135034209</t>
+  </si>
+  <si>
+    <t>135030427</t>
+  </si>
+  <si>
+    <t>132374860</t>
+  </si>
+  <si>
+    <t>135053538</t>
+  </si>
+  <si>
+    <t>134876623</t>
+  </si>
+  <si>
+    <t>135071947</t>
+  </si>
+  <si>
+    <t>135090339</t>
+  </si>
+  <si>
+    <t>134996733</t>
+  </si>
+  <si>
+    <t>134946930</t>
+  </si>
+  <si>
+    <t>132546677</t>
+  </si>
+  <si>
+    <t>134989530</t>
+  </si>
+  <si>
+    <t>134994566</t>
+  </si>
+  <si>
+    <t>135008994</t>
+  </si>
+  <si>
+    <t>135010280</t>
+  </si>
+  <si>
+    <t>134994886</t>
+  </si>
+  <si>
+    <t>134997477</t>
+  </si>
+  <si>
+    <t>135094594</t>
+  </si>
+  <si>
+    <t>135096260</t>
+  </si>
+  <si>
+    <t>134878465</t>
+  </si>
+  <si>
+    <t>134882151</t>
+  </si>
+  <si>
+    <t>134907392</t>
+  </si>
+  <si>
+    <t>134908222</t>
+  </si>
+  <si>
+    <t>134950973</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_24.10.2025</t>
+  </si>
+  <si>
+    <t>134907375</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 25.10.2025</t>
+  </si>
+  <si>
+    <t>134921649</t>
+  </si>
+  <si>
+    <t>134951355</t>
+  </si>
+  <si>
+    <t>135069001</t>
+  </si>
+  <si>
+    <t>135076836</t>
+  </si>
+  <si>
+    <t>134981277</t>
+  </si>
+  <si>
+    <t>134876239</t>
+  </si>
+  <si>
+    <t>134883860</t>
+  </si>
+  <si>
+    <t>134904566</t>
+  </si>
+  <si>
+    <t>134904645</t>
+  </si>
+  <si>
+    <t>134907282</t>
+  </si>
+  <si>
+    <t>135009815</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.10.2025</t>
   </si>
 </sst>
 </file>
@@ -666,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -698,7 +653,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>132618037</v>
+        <v>134890224</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -707,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -725,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -743,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -760,7 +715,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -777,7 +732,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -794,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -811,7 +766,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -828,7 +783,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -845,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -862,7 +817,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -879,7 +834,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -896,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -913,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -930,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -947,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -964,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -981,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -998,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1015,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1032,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1049,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1066,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1083,7 +1038,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1117,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1134,7 +1089,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1168,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1185,7 +1140,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1219,7 +1174,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1236,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1253,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1270,7 +1225,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1287,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1304,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1321,7 +1276,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1338,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1355,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1372,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1380,16 +1335,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1397,16 +1352,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1414,16 +1369,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1431,16 +1386,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1448,16 +1403,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1465,16 +1420,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1482,16 +1437,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1499,16 +1454,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1516,16 +1471,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1533,16 +1488,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1550,16 +1505,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1567,307 +1522,18 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203EEA43-D609-46A6-832A-ABC14BE45B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A4CCB2-8159-4A08-B623-D5ED8FAB6DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,178 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 24.10.2025</t>
-  </si>
-  <si>
-    <t>134887092</t>
-  </si>
-  <si>
-    <t>134903304</t>
-  </si>
-  <si>
-    <t>134875386</t>
-  </si>
-  <si>
-    <t>134950299</t>
-  </si>
-  <si>
-    <t>134967981</t>
-  </si>
-  <si>
-    <t>134958842</t>
-  </si>
-  <si>
-    <t>134964619</t>
-  </si>
-  <si>
-    <t>134973064</t>
-  </si>
-  <si>
-    <t>134958351</t>
-  </si>
-  <si>
-    <t>134968489</t>
-  </si>
-  <si>
-    <t>134988642</t>
-  </si>
-  <si>
-    <t>134996089</t>
-  </si>
-  <si>
-    <t>135008057</t>
-  </si>
-  <si>
-    <t>135007411</t>
-  </si>
-  <si>
-    <t>135006207</t>
-  </si>
-  <si>
-    <t>135038050</t>
-  </si>
-  <si>
-    <t>135034209</t>
-  </si>
-  <si>
-    <t>135030427</t>
-  </si>
-  <si>
-    <t>132374860</t>
-  </si>
-  <si>
-    <t>135053538</t>
-  </si>
-  <si>
-    <t>134876623</t>
-  </si>
-  <si>
-    <t>135071947</t>
-  </si>
-  <si>
-    <t>135090339</t>
-  </si>
-  <si>
-    <t>134996733</t>
-  </si>
-  <si>
-    <t>134946930</t>
-  </si>
-  <si>
-    <t>132546677</t>
-  </si>
-  <si>
-    <t>134989530</t>
-  </si>
-  <si>
-    <t>134994566</t>
-  </si>
-  <si>
-    <t>135008994</t>
-  </si>
-  <si>
-    <t>135010280</t>
-  </si>
-  <si>
-    <t>134994886</t>
-  </si>
-  <si>
-    <t>134997477</t>
-  </si>
-  <si>
-    <t>135094594</t>
-  </si>
-  <si>
-    <t>135096260</t>
-  </si>
-  <si>
-    <t>134878465</t>
-  </si>
-  <si>
-    <t>134882151</t>
-  </si>
-  <si>
-    <t>134907392</t>
-  </si>
-  <si>
-    <t>134908222</t>
-  </si>
-  <si>
-    <t>134950973</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_24.10.2025</t>
-  </si>
-  <si>
-    <t>134907375</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 25.10.2025</t>
-  </si>
-  <si>
-    <t>134921649</t>
-  </si>
-  <si>
-    <t>134951355</t>
-  </si>
-  <si>
-    <t>135069001</t>
-  </si>
-  <si>
-    <t>135076836</t>
-  </si>
-  <si>
-    <t>134981277</t>
-  </si>
-  <si>
-    <t>134876239</t>
-  </si>
-  <si>
-    <t>134883860</t>
-  </si>
-  <si>
-    <t>134904566</t>
-  </si>
-  <si>
-    <t>134904645</t>
-  </si>
-  <si>
-    <t>134907282</t>
-  </si>
-  <si>
-    <t>135009815</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.10.2025</t>
+    <t>Relatório de Recusa Sicredi 27.10.2025</t>
+  </si>
+  <si>
+    <t>134984579</t>
+  </si>
+  <si>
+    <t>134995372</t>
+  </si>
+  <si>
+    <t>134991107</t>
+  </si>
+  <si>
+    <t>134998390</t>
+  </si>
+  <si>
+    <t>135006701</t>
+  </si>
+  <si>
+    <t>135018319</t>
+  </si>
+  <si>
+    <t>135032010</t>
+  </si>
+  <si>
+    <t>135056767</t>
+  </si>
+  <si>
+    <t>135058405</t>
+  </si>
+  <si>
+    <t>135050313</t>
+  </si>
+  <si>
+    <t>135054937</t>
+  </si>
+  <si>
+    <t>135056538</t>
+  </si>
+  <si>
+    <t>135053027</t>
+  </si>
+  <si>
+    <t>135039021</t>
+  </si>
+  <si>
+    <t>135047710</t>
+  </si>
+  <si>
+    <t>135062441</t>
+  </si>
+  <si>
+    <t>135064406</t>
+  </si>
+  <si>
+    <t>135070644</t>
+  </si>
+  <si>
+    <t>135078285</t>
+  </si>
+  <si>
+    <t>135063404</t>
+  </si>
+  <si>
+    <t>135079165</t>
+  </si>
+  <si>
+    <t>135063790</t>
+  </si>
+  <si>
+    <t>135078940</t>
+  </si>
+  <si>
+    <t>135077212</t>
+  </si>
+  <si>
+    <t>135063411</t>
+  </si>
+  <si>
+    <t>135098510</t>
+  </si>
+  <si>
+    <t>135102621</t>
+  </si>
+  <si>
+    <t>135091822</t>
+  </si>
+  <si>
+    <t>135096144</t>
+  </si>
+  <si>
+    <t>135091519</t>
+  </si>
+  <si>
+    <t>135073395</t>
+  </si>
+  <si>
+    <t>134926489</t>
+  </si>
+  <si>
+    <t>135047658</t>
+  </si>
+  <si>
+    <t>135029860</t>
+  </si>
+  <si>
+    <t>135055114</t>
+  </si>
+  <si>
+    <t>135113829</t>
+  </si>
+  <si>
+    <t>135023805</t>
+  </si>
+  <si>
+    <t>135114518</t>
+  </si>
+  <si>
+    <t>130972090</t>
+  </si>
+  <si>
+    <t>131954898</t>
+  </si>
+  <si>
+    <t>135016899</t>
+  </si>
+  <si>
+    <t>135014545</t>
+  </si>
+  <si>
+    <t>135117053</t>
+  </si>
+  <si>
+    <t>134994271</t>
+  </si>
+  <si>
+    <t>134995698</t>
+  </si>
+  <si>
+    <t>134996070</t>
+  </si>
+  <si>
+    <t>134997240</t>
+  </si>
+  <si>
+    <t>134997276</t>
+  </si>
+  <si>
+    <t>134998211</t>
+  </si>
+  <si>
+    <t>135118623</t>
+  </si>
+  <si>
+    <t>134938757</t>
+  </si>
+  <si>
+    <t>134945513</t>
+  </si>
+  <si>
+    <t>135119781</t>
+  </si>
+  <si>
+    <t>135059226</t>
+  </si>
+  <si>
+    <t>134987833</t>
+  </si>
+  <si>
+    <t>134481525</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_27.10.2025</t>
   </si>
 </sst>
 </file>
@@ -621,7 +630,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -653,7 +662,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134890224</v>
+        <v>134916660</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -662,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -680,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -698,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -715,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -732,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -749,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -766,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -783,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -800,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -817,7 +826,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -834,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -851,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -868,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -885,7 +894,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -902,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -919,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -936,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -953,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -970,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -987,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1021,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1038,7 +1047,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1072,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1089,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1123,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1140,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1174,7 +1183,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1191,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1208,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1225,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1242,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1276,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1293,7 +1302,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1310,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1327,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1335,16 +1344,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1352,16 +1361,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1369,16 +1378,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1386,16 +1395,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1403,16 +1412,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1420,16 +1429,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1437,16 +1446,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1454,16 +1463,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1471,16 +1480,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1488,16 +1497,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1505,16 +1514,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1522,18 +1531,103 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1551,31 +1645,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{7309EFA7-B4B7-4F7F-B1F1-E57F99AB7FC9}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A46CF07-FB81-4471-8599-C6B80D998BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
+    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="103">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -48,212 +48,301 @@
     <t xml:space="preserve">Anexo </t>
   </si>
   <si>
+    <t>971</t>
+  </si>
+  <si>
     <t>Processar</t>
   </si>
   <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 03.10.2025</t>
-  </si>
-  <si>
-    <t>134577469</t>
-  </si>
-  <si>
-    <t>134646433</t>
-  </si>
-  <si>
-    <t>134633022</t>
-  </si>
-  <si>
-    <t>134639041</t>
-  </si>
-  <si>
-    <t>134632578</t>
-  </si>
-  <si>
-    <t>134635635</t>
-  </si>
-  <si>
-    <t>134636654</t>
-  </si>
-  <si>
-    <t>134630300</t>
-  </si>
-  <si>
-    <t>134642584</t>
-  </si>
-  <si>
-    <t>134668387</t>
-  </si>
-  <si>
-    <t>134669555</t>
-  </si>
-  <si>
-    <t>134654305</t>
-  </si>
-  <si>
-    <t>134632125</t>
-  </si>
-  <si>
-    <t>134573241</t>
-  </si>
-  <si>
-    <t>134678006</t>
-  </si>
-  <si>
-    <t>134692441</t>
-  </si>
-  <si>
-    <t>134654507</t>
-  </si>
-  <si>
-    <t>134692743</t>
-  </si>
-  <si>
-    <t>134699568</t>
-  </si>
-  <si>
-    <t>134726752</t>
-  </si>
-  <si>
-    <t>134737835</t>
-  </si>
-  <si>
-    <t>134740580</t>
-  </si>
-  <si>
-    <t>134745488</t>
-  </si>
-  <si>
-    <t>134659721</t>
-  </si>
-  <si>
-    <t>134755498</t>
-  </si>
-  <si>
-    <t>134549061</t>
-  </si>
-  <si>
-    <t>132970129</t>
-  </si>
-  <si>
-    <t>129839675</t>
-  </si>
-  <si>
-    <t>134634026</t>
-  </si>
-  <si>
-    <t>134634404</t>
-  </si>
-  <si>
-    <t>134634564</t>
-  </si>
-  <si>
-    <t>134636701</t>
-  </si>
-  <si>
-    <t>134646065</t>
-  </si>
-  <si>
-    <t>132024777</t>
-  </si>
-  <si>
-    <t>134638731</t>
-  </si>
-  <si>
-    <t>134639062</t>
-  </si>
-  <si>
-    <t>134640329</t>
-  </si>
-  <si>
-    <t>134764905</t>
-  </si>
-  <si>
-    <t>134774564</t>
-  </si>
-  <si>
-    <t>134630841</t>
-  </si>
-  <si>
-    <t>131280425</t>
-  </si>
-  <si>
-    <t>134401158</t>
-  </si>
-  <si>
-    <t>134655050</t>
-  </si>
-  <si>
-    <t>134668505</t>
-  </si>
-  <si>
-    <t>134660055</t>
-  </si>
-  <si>
-    <t>134778552</t>
-  </si>
-  <si>
-    <t>134781897</t>
-  </si>
-  <si>
-    <t>134782319</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_03.10.2025</t>
-  </si>
-  <si>
-    <t>134693702</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 04.10.2025</t>
-  </si>
-  <si>
-    <t>134655411</t>
-  </si>
-  <si>
-    <t>134654943</t>
-  </si>
-  <si>
-    <t>134564272</t>
-  </si>
-  <si>
-    <t>134573504</t>
-  </si>
-  <si>
-    <t>134720689</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_04.10.2025</t>
-  </si>
-  <si>
-    <t>134727786</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 05.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_05.10.2025</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório Recusa _ SICREDI_03.10.2025.xlsx.</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório Recusa _ SICREDI_04.10.2025.xlsx.</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório Recusa _ SICREDI_05.10.2025.xlsx.</t>
+    <t>Recusas Sicredi 18/12/2025</t>
+  </si>
+  <si>
+    <t>135697136</t>
+  </si>
+  <si>
+    <t>135699274</t>
+  </si>
+  <si>
+    <t>135719328</t>
+  </si>
+  <si>
+    <t>135756732</t>
+  </si>
+  <si>
+    <t>135755334</t>
+  </si>
+  <si>
+    <t>135778143</t>
+  </si>
+  <si>
+    <t>135778650</t>
+  </si>
+  <si>
+    <t>135783261</t>
+  </si>
+  <si>
+    <t>135791028</t>
+  </si>
+  <si>
+    <t>135792760</t>
+  </si>
+  <si>
+    <t>135807554</t>
+  </si>
+  <si>
+    <t>135813412</t>
+  </si>
+  <si>
+    <t>135811008</t>
+  </si>
+  <si>
+    <t>135811456</t>
+  </si>
+  <si>
+    <t>135826675</t>
+  </si>
+  <si>
+    <t>135834185</t>
+  </si>
+  <si>
+    <t>135834487</t>
+  </si>
+  <si>
+    <t>135842667</t>
+  </si>
+  <si>
+    <t>135832917</t>
+  </si>
+  <si>
+    <t>135824581</t>
+  </si>
+  <si>
+    <t>135837995</t>
+  </si>
+  <si>
+    <t>135802880</t>
+  </si>
+  <si>
+    <t>135861351</t>
+  </si>
+  <si>
+    <t>135868218</t>
+  </si>
+  <si>
+    <t>135880423</t>
+  </si>
+  <si>
+    <t>135858463</t>
+  </si>
+  <si>
+    <t>135884477</t>
+  </si>
+  <si>
+    <t>135889501</t>
+  </si>
+  <si>
+    <t>135890698</t>
+  </si>
+  <si>
+    <t>135877249</t>
+  </si>
+  <si>
+    <t>135912963</t>
+  </si>
+  <si>
+    <t>135902053</t>
+  </si>
+  <si>
+    <t>135907636</t>
+  </si>
+  <si>
+    <t>135687958</t>
+  </si>
+  <si>
+    <t>135679993</t>
+  </si>
+  <si>
+    <t>135680218</t>
+  </si>
+  <si>
+    <t>135687252</t>
+  </si>
+  <si>
+    <t>135694038</t>
+  </si>
+  <si>
+    <t>135694960</t>
+  </si>
+  <si>
+    <t>135695990</t>
+  </si>
+  <si>
+    <t>135699286</t>
+  </si>
+  <si>
+    <t>135700097</t>
+  </si>
+  <si>
+    <t>135701411</t>
+  </si>
+  <si>
+    <t>135701983</t>
+  </si>
+  <si>
+    <t>135704480</t>
+  </si>
+  <si>
+    <t>135913204</t>
+  </si>
+  <si>
+    <t>135786629</t>
+  </si>
+  <si>
+    <t>135845763</t>
+  </si>
+  <si>
+    <t>135838655</t>
+  </si>
+  <si>
+    <t>135745030</t>
+  </si>
+  <si>
+    <t>135922060</t>
+  </si>
+  <si>
+    <t>135831353</t>
+  </si>
+  <si>
+    <t>135765431</t>
+  </si>
+  <si>
+    <t>135769949</t>
+  </si>
+  <si>
+    <t>135776526</t>
+  </si>
+  <si>
+    <t>135777415</t>
+  </si>
+  <si>
+    <t>135921490</t>
+  </si>
+  <si>
+    <t>135749555</t>
+  </si>
+  <si>
+    <t>135921185</t>
+  </si>
+  <si>
+    <t>135925479</t>
+  </si>
+  <si>
+    <t>135836871</t>
+  </si>
+  <si>
+    <t>135816889</t>
+  </si>
+  <si>
+    <t>135927602</t>
+  </si>
+  <si>
+    <t>135767266</t>
+  </si>
+  <si>
+    <t>135787630</t>
+  </si>
+  <si>
+    <t>135796294</t>
+  </si>
+  <si>
+    <t>135817492</t>
+  </si>
+  <si>
+    <t>135918491</t>
+  </si>
+  <si>
+    <t>135733788</t>
+  </si>
+  <si>
+    <t>135728639</t>
+  </si>
+  <si>
+    <t>135800307</t>
+  </si>
+  <si>
+    <t>135924758</t>
+  </si>
+  <si>
+    <t>135798379</t>
+  </si>
+  <si>
+    <t>135799315</t>
+  </si>
+  <si>
+    <t>135836273</t>
+  </si>
+  <si>
+    <t>134599207</t>
+  </si>
+  <si>
+    <t>135918534</t>
+  </si>
+  <si>
+    <t>135809693</t>
+  </si>
+  <si>
+    <t>135932996</t>
+  </si>
+  <si>
+    <t>135932860</t>
+  </si>
+  <si>
+    <t>131745850</t>
+  </si>
+  <si>
+    <t>135838256</t>
+  </si>
+  <si>
+    <t>135792352</t>
+  </si>
+  <si>
+    <t>135797895</t>
+  </si>
+  <si>
+    <t>135748586</t>
+  </si>
+  <si>
+    <t>135730924</t>
+  </si>
+  <si>
+    <t>135774164</t>
+  </si>
+  <si>
+    <t>135804452</t>
+  </si>
+  <si>
+    <t>135795897</t>
+  </si>
+  <si>
+    <t>135789390</t>
+  </si>
+  <si>
+    <t>135937845</t>
+  </si>
+  <si>
+    <t>135755705</t>
+  </si>
+  <si>
+    <t>135722179</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_18.12.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -313,34 +402,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -357,10 +446,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -395,7 +484,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -447,7 +536,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -558,21 +647,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -589,7 +678,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -641,25 +730,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
-    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -684,842 +773,757 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130736305</v>
+        <v>135411245</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F32"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F34" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F35"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F36" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F36"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F37" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F43" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1527,19 +1531,16 @@
         <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F44" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1547,19 +1548,16 @@
         <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1567,19 +1565,16 @@
         <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F46" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1587,19 +1582,16 @@
         <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F47" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1607,240 +1599,856 @@
         <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F48" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F50" t="s">
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F55" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>